--- a/tame_output/ON/bt/strategyON_20240828.xlsx
+++ b/tame_output/ON/bt/strategyON_20240828.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>16.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>73.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>108.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.9%</t>
+          <t>125.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.5%</t>
+          <t>-49.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.6%</t>
+          <t>419.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-699.1%</t>
+          <t>-701.5%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-189.4%</t>
+          <t>-190.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-14.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>119.7%</t>
+          <t>117.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-291.0%</t>
+          <t>-291.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-172.1%</t>
+          <t>-169.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-11.2%</t>
         </is>
       </c>
     </row>
@@ -48793,10 +48793,10 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.048139035186796</v>
+        <v>-5.224922017455148</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.982711250708571</v>
+        <v>1.91199805780123</v>
       </c>
       <c r="F2054" t="n">
         <v>0.8144913348996135</v>
@@ -48816,10 +48816,10 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.018893054731099</v>
+        <v>-5.195676036999451</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.992027698014345</v>
+        <v>1.921314505107004</v>
       </c>
       <c r="F2055" t="n">
         <v>0.8144913348996135</v>
@@ -48839,10 +48839,10 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.12581860260895</v>
+        <v>-5.302601584877302</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.946550718020839</v>
+        <v>1.875837525113499</v>
       </c>
       <c r="F2056" t="n">
         <v>0.7075657870217621</v>
@@ -48862,10 +48862,10 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.270837161116199</v>
+        <v>-5.447620143384551</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.889972096761174</v>
+        <v>1.819258903853834</v>
       </c>
       <c r="F2057" t="n">
         <v>0.5625472285145136</v>
@@ -48885,10 +48885,10 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.389178926900916</v>
+        <v>-5.565961909169268</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.94256662970504</v>
+        <v>1.8718534367977</v>
       </c>
       <c r="F2058" t="n">
         <v>0.5732332670774036</v>
@@ -48908,10 +48908,10 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.440589349221624</v>
+        <v>-5.617372331489976</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.919788157902696</v>
+        <v>1.849074964995355</v>
       </c>
       <c r="F2059" t="n">
         <v>0.5732332670774036</v>
@@ -48931,10 +48931,10 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.520008800429376</v>
+        <v>-5.696791782697728</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.887923505493885</v>
+        <v>1.817210312586544</v>
       </c>
       <c r="F2060" t="n">
         <v>0.5732332670774036</v>
@@ -48954,10 +48954,10 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.615471798346594</v>
+        <v>-5.792254780614946</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.849732199885041</v>
+        <v>1.7790190069777</v>
       </c>
       <c r="F2061" t="n">
         <v>0.5732332670774036</v>
@@ -48977,10 +48977,10 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.655491796390377</v>
+        <v>-5.832274778658729</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.831820597230138</v>
+        <v>1.761107404322797</v>
       </c>
       <c r="F2062" t="n">
         <v>0.5332132690336198</v>
@@ -49000,10 +49000,10 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.710860958522571</v>
+        <v>-5.887643940790923</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.815406750124987</v>
+        <v>1.744693557217647</v>
       </c>
       <c r="F2063" t="n">
         <v>0.5332132690336198</v>
@@ -49023,10 +49023,10 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.756298738353398</v>
+        <v>-5.93308172062175</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.796770001535589</v>
+        <v>1.726056808628249</v>
       </c>
       <c r="F2064" t="n">
         <v>0.4903682783554602</v>
@@ -49046,10 +49046,10 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.673073281505734</v>
+        <v>-5.849856263774086</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.849934577124974</v>
+        <v>1.779221384217633</v>
       </c>
       <c r="F2065" t="n">
         <v>0.4903682783554602</v>
@@ -49069,10 +49069,10 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.496783056900426</v>
+        <v>-5.673566039168779</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.904151367491825</v>
+        <v>1.833438174584484</v>
       </c>
       <c r="F2066" t="n">
         <v>0.4903682783554602</v>
@@ -49092,10 +49092,10 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.313571393767331</v>
+        <v>-5.490354376035683</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.979866982209109</v>
+        <v>1.909153789301768</v>
       </c>
       <c r="F2067" t="n">
         <v>0.4903682783554602</v>
@@ -49115,10 +49115,10 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.24184994675348</v>
+        <v>-5.418632929021832</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.974346746862538</v>
+        <v>1.903633553955197</v>
       </c>
       <c r="F2068" t="n">
         <v>0.5620897253693108</v>
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.882945987230764</v>
+        <v>3.445766695504546</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.375614952983425</v>
+        <v>-5.399036910612283</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.867756490291732</v>
+        <v>1.858387707240189</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.5186737042451025</v>
+        <v>0.5491045611932437</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.329563118345911</v>
+        <v>4.347821632514796</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240828.xlsx
+++ b/tame_output/ON/bt/strategyON_20240828.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>49.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>73.2%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.9%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-34.1%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.6%</t>
+          <t>-49.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>419.7%</t>
+          <t>423.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-701.5%</t>
+          <t>-689.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-190.4%</t>
+          <t>-185.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.2%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>117.3%</t>
+          <t>119.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-169.1%</t>
+          <t>-172.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-13.0%</t>
         </is>
       </c>
     </row>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955324</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311945</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409724</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017767</v>
+        <v>3.789311112017768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -47620,10 +47620,10 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.148644314846097</v>
+        <v>-3.058050489527874</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.066457708304443</v>
+        <v>2.102695238431733</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9894270841003656</v>
@@ -47643,10 +47643,10 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.171052432650969</v>
+        <v>-3.080458607332746</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.049611156085488</v>
+        <v>2.085848686212777</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9894270841003656</v>
@@ -47666,10 +47666,10 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.199276668228569</v>
+        <v>-3.108682842910346</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.040375461404085</v>
+        <v>2.076612991531374</v>
       </c>
       <c r="F2005" t="n">
         <v>1.007403836551674</v>
@@ -47689,10 +47689,10 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.208717594117099</v>
+        <v>-3.118123768798876</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.09285280877052</v>
+        <v>2.12909033889781</v>
       </c>
       <c r="F2006" t="n">
         <v>1.129830954095066</v>
@@ -47712,10 +47712,10 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.26099120145274</v>
+        <v>-3.170397376134518</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.074834460381565</v>
+        <v>2.111071990508854</v>
       </c>
       <c r="F2007" t="n">
         <v>1.077557346759424</v>
@@ -47735,10 +47735,10 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.337321179053646</v>
+        <v>-3.246727353735424</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.042414282234978</v>
+        <v>2.078651812362267</v>
       </c>
       <c r="F2008" t="n">
         <v>1.077557346759424</v>
@@ -47758,10 +47758,10 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.539574899378</v>
+        <v>-3.448981074059777</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.956333023708098</v>
+        <v>1.992570553835388</v>
       </c>
       <c r="F2009" t="n">
         <v>0.8753036264350709</v>
@@ -47781,10 +47781,10 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.701143324905255</v>
+        <v>-3.610549499587032</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.890139663707349</v>
+        <v>1.926377193834638</v>
       </c>
       <c r="F2010" t="n">
         <v>0.7485207026371915</v>
@@ -47804,10 +47804,10 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.809443986775374</v>
+        <v>-3.718850161457151</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.85989280582522</v>
+        <v>1.896130335952509</v>
       </c>
       <c r="F2011" t="n">
         <v>0.7485207026371915</v>
@@ -47827,10 +47827,10 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.902591458078741</v>
+        <v>-3.811997632760518</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.814639014086813</v>
+        <v>1.850876544214102</v>
       </c>
       <c r="F2012" t="n">
         <v>0.6256914913546587</v>
@@ -47850,10 +47850,10 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.930492245188214</v>
+        <v>-3.839898419869991</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.802002740370026</v>
+        <v>1.838240270497315</v>
       </c>
       <c r="F2013" t="n">
         <v>0.5910945672117239</v>
@@ -47873,10 +47873,10 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.053018347891108</v>
+        <v>-3.962424522572885</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.749756743266067</v>
+        <v>1.785994273393356</v>
       </c>
       <c r="F2014" t="n">
         <v>0.4685684645088301</v>
@@ -47896,10 +47896,10 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.283532844076697</v>
+        <v>-4.192939018758474</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.724256904382335</v>
+        <v>1.760494434509624</v>
       </c>
       <c r="F2015" t="n">
         <v>0.2380539683232413</v>
@@ -47919,10 +47919,10 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.63227792930114</v>
+        <v>-4.541684103982917</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.725070589294405</v>
+        <v>1.761308119421694</v>
       </c>
       <c r="F2016" t="n">
         <v>0.1293060144043435</v>
@@ -47942,10 +47942,10 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.786264347077281</v>
+        <v>-4.695670521759058</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.732456291329588</v>
+        <v>1.768693821456877</v>
       </c>
       <c r="F2017" t="n">
         <v>0.1293060144043435</v>
@@ -47965,10 +47965,10 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.735742443249615</v>
+        <v>-4.645148617931392</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.738716254980776</v>
+        <v>1.774953785108065</v>
       </c>
       <c r="F2018" t="n">
         <v>0.1293060144043435</v>
@@ -47988,10 +47988,10 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.988217597257339</v>
+        <v>-4.897623771939116</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.6495966824331</v>
+        <v>1.685834212560389</v>
       </c>
       <c r="F2019" t="n">
         <v>0.1293060144043435</v>
@@ -48011,10 +48011,10 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.281113353736751</v>
+        <v>-5.190519528418529</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.533648914360279</v>
+        <v>1.569886444487568</v>
       </c>
       <c r="F2020" t="n">
         <v>0.1293060144043435</v>
@@ -48034,10 +48034,10 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.467777481871559</v>
+        <v>-5.377183656553337</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.463105005333677</v>
+        <v>1.499342535460966</v>
       </c>
       <c r="F2021" t="n">
         <v>0.1025670435797836</v>
@@ -48057,10 +48057,10 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.613798168785522</v>
+        <v>-5.523204343467299</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.399774583304281</v>
+        <v>1.436012113431571</v>
       </c>
       <c r="F2022" t="n">
         <v>0.09348395178592667</v>
@@ -48080,10 +48080,10 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.705512177895107</v>
+        <v>-5.614918352576884</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.525293036359491</v>
+        <v>1.56153056648678</v>
       </c>
       <c r="F2023" t="n">
         <v>0.09348395178592667</v>
@@ -48103,10 +48103,10 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.737163836955077</v>
+        <v>-5.646570011636854</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.507479010699317</v>
+        <v>1.543716540826607</v>
       </c>
       <c r="F2024" t="n">
         <v>0.08831549454148646</v>
@@ -48126,10 +48126,10 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.81909865522396</v>
+        <v>-5.728504829905737</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.484934500960255</v>
+        <v>1.521172031087545</v>
       </c>
       <c r="F2025" t="n">
         <v>0.07838074895440628</v>
@@ -48149,10 +48149,10 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.921074777472367</v>
+        <v>-5.830480952154145</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.453069690516795</v>
+        <v>1.489307220644084</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.0235953732940013</v>
@@ -48172,10 +48172,10 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.811068493995146</v>
+        <v>-5.720474668676923</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.489225091151859</v>
+        <v>1.525462621279148</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.0003908013767260909</v>
@@ -48195,10 +48195,10 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.66800891825422</v>
+        <v>-5.577415092935997</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.550698932170204</v>
+        <v>1.586936462297493</v>
       </c>
       <c r="F2028" t="n">
         <v>0.007622625213253187</v>
@@ -48218,10 +48218,10 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.366562192782382</v>
+        <v>-5.275968367464159</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.678538505241475</v>
+        <v>1.714776035368764</v>
       </c>
       <c r="F2029" t="n">
         <v>0.3090693506850904</v>
@@ -48241,10 +48241,10 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.391152437017566</v>
+        <v>-5.300558611699343</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.669673585300112</v>
+        <v>1.705911115427401</v>
       </c>
       <c r="F2030" t="n">
         <v>0.3090693506850904</v>
@@ -48264,10 +48264,10 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.340114061011046</v>
+        <v>-5.249520235692823</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.690931840082476</v>
+        <v>1.727169370209765</v>
       </c>
       <c r="F2031" t="n">
         <v>0.3090693506850904</v>
@@ -48287,10 +48287,10 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.298974766144415</v>
+        <v>-5.208380940826192</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.726425656903273</v>
+        <v>1.762663187030562</v>
       </c>
       <c r="F2032" t="n">
         <v>0.3502086455517213</v>
@@ -48310,10 +48310,10 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.202339854125775</v>
+        <v>-5.111746028807552</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.581263617834664</v>
+        <v>1.617501147961953</v>
       </c>
       <c r="F2033" t="n">
         <v>0.4468435575703612</v>
@@ -48333,10 +48333,10 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.332920588656617</v>
+        <v>-5.242326763338395</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.532533368096291</v>
+        <v>1.56877089822358</v>
       </c>
       <c r="F2034" t="n">
         <v>0.3162628230395187</v>
@@ -48356,10 +48356,10 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.168424254465656</v>
+        <v>-5.077830429147433</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.582758720848758</v>
+        <v>1.618996250976047</v>
       </c>
       <c r="F2035" t="n">
         <v>0.4807591572304806</v>
@@ -48379,10 +48379,10 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.195794187150088</v>
+        <v>-5.105200361831865</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.570998458211415</v>
+        <v>1.607235988338704</v>
       </c>
       <c r="F2036" t="n">
         <v>0.4807591572304806</v>
@@ -48402,10 +48402,10 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.206179382039977</v>
+        <v>-5.115585556721754</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.576713159380532</v>
+        <v>1.612950689507821</v>
       </c>
       <c r="F2037" t="n">
         <v>0.4703739623405913</v>
@@ -48425,10 +48425,10 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.224767540762202</v>
+        <v>-5.134173715443979</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.640114901668067</v>
+        <v>1.676352431795356</v>
       </c>
       <c r="F2038" t="n">
         <v>0.4517858036183659</v>
@@ -48442,16 +48442,16 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.85512053549655</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.225066087458238</v>
+        <v>-5.134472262140015</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.636864493807951</v>
+        <v>1.67310202393524</v>
       </c>
       <c r="F2039" t="n">
         <v>0.45148725692233</v>
@@ -48471,10 +48471,10 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.12424295376781</v>
+        <v>-5.033649128449587</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.681724642223513</v>
+        <v>1.717962172350803</v>
       </c>
       <c r="F2040" t="n">
         <v>0.4639514724066838</v>
@@ -48494,10 +48494,10 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.933461593015403</v>
+        <v>-4.842867767697181</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.758166440003019</v>
+        <v>1.794403970130309</v>
       </c>
       <c r="F2041" t="n">
         <v>0.6547328331590911</v>
@@ -48517,10 +48517,10 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.914944738973583</v>
+        <v>-4.82435091365536</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.745410027357344</v>
+        <v>1.781647557484633</v>
       </c>
       <c r="F2042" t="n">
         <v>0.6676629625842994</v>
@@ -48540,10 +48540,10 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.85961415107182</v>
+        <v>-4.769020325753598</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.802509199130108</v>
+        <v>1.838746729257397</v>
       </c>
       <c r="F2043" t="n">
         <v>0.7229935504860615</v>
@@ -48563,10 +48563,10 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.847560024158858</v>
+        <v>-4.756966198840635</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.80101741779673</v>
+        <v>1.83725494792402</v>
       </c>
       <c r="F2044" t="n">
         <v>0.7350476773990243</v>
@@ -48586,10 +48586,10 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.888715143727079</v>
+        <v>-4.798121318408856</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.786436000153578</v>
+        <v>1.822673530280867</v>
       </c>
       <c r="F2045" t="n">
         <v>0.6938925578308034</v>
@@ -48609,10 +48609,10 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.785834554198486</v>
+        <v>-4.695240728880263</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.840439261842898</v>
+        <v>1.876676791970187</v>
       </c>
       <c r="F2046" t="n">
         <v>0.7967731473593963</v>
@@ -48632,10 +48632,10 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.017434947367986</v>
+        <v>-4.926841122049764</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.768001774748691</v>
+        <v>1.804239304875981</v>
       </c>
       <c r="F2047" t="n">
         <v>0.7967731473593963</v>
@@ -48655,10 +48655,10 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.035507455659598</v>
+        <v>-4.944913630341375</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.760772771432047</v>
+        <v>1.797010301559336</v>
       </c>
       <c r="F2048" t="n">
         <v>0.7967731473593963</v>
@@ -48678,10 +48678,10 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.210614288236043</v>
+        <v>-5.12002046291782</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.650981951994936</v>
+        <v>1.687219482122225</v>
       </c>
       <c r="F2049" t="n">
         <v>0.7967731473593963</v>
@@ -48701,10 +48701,10 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.179328267695587</v>
+        <v>-5.088734442377365</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.670518979208058</v>
+        <v>1.706756509335347</v>
       </c>
       <c r="F2050" t="n">
         <v>0.8280591678998517</v>
@@ -48724,10 +48724,10 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.026302875582303</v>
+        <v>-4.93570905026408</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.830900135626276</v>
+        <v>1.867137665753565</v>
       </c>
       <c r="F2051" t="n">
         <v>0.9810845600131358</v>
@@ -48747,10 +48747,10 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.054610189455573</v>
+        <v>-4.96401636413735</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.00704343498526</v>
+        <v>2.043280965112549</v>
       </c>
       <c r="F2052" t="n">
         <v>0.9810845600131358</v>
@@ -48770,10 +48770,10 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.221203414569096</v>
+        <v>-5.130609589250873</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.909809096293933</v>
+        <v>1.946046626421222</v>
       </c>
       <c r="F2053" t="n">
         <v>0.8144913348996135</v>
@@ -48793,10 +48793,10 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.224922017455148</v>
+        <v>-4.957545209868573</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.91199805780123</v>
+        <v>2.01894878083586</v>
       </c>
       <c r="F2054" t="n">
         <v>0.8144913348996135</v>
@@ -48816,10 +48816,10 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.195676036999451</v>
+        <v>-4.928299229412876</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.921314505107004</v>
+        <v>2.028265228141634</v>
       </c>
       <c r="F2055" t="n">
         <v>0.8144913348996135</v>
@@ -48839,10 +48839,10 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.302601584877302</v>
+        <v>-5.035224777290727</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.875837525113499</v>
+        <v>1.982788248148128</v>
       </c>
       <c r="F2056" t="n">
         <v>0.7075657870217621</v>
@@ -48862,10 +48862,10 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.447620143384551</v>
+        <v>-5.180243335797976</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.819258903853834</v>
+        <v>1.926209626888463</v>
       </c>
       <c r="F2057" t="n">
         <v>0.5625472285145136</v>
@@ -48885,10 +48885,10 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.565961909169268</v>
+        <v>-5.298585101582693</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.8718534367977</v>
+        <v>1.978804159832329</v>
       </c>
       <c r="F2058" t="n">
         <v>0.5732332670774036</v>
@@ -48908,10 +48908,10 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.617372331489976</v>
+        <v>-5.349995523903401</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.849074964995355</v>
+        <v>1.956025688029985</v>
       </c>
       <c r="F2059" t="n">
         <v>0.5732332670774036</v>
@@ -48931,10 +48931,10 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.696791782697728</v>
+        <v>-5.429414975111153</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.817210312586544</v>
+        <v>1.924161035621174</v>
       </c>
       <c r="F2060" t="n">
         <v>0.5732332670774036</v>
@@ -48954,10 +48954,10 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.792254780614946</v>
+        <v>-5.524877973028371</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.7790190069777</v>
+        <v>1.88596973001233</v>
       </c>
       <c r="F2061" t="n">
         <v>0.5732332670774036</v>
@@ -48977,10 +48977,10 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.832274778658729</v>
+        <v>-5.564897971072154</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.761107404322797</v>
+        <v>1.868058127357427</v>
       </c>
       <c r="F2062" t="n">
         <v>0.5332132690336198</v>
@@ -49000,10 +49000,10 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.887643940790923</v>
+        <v>-5.620267133204348</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.744693557217647</v>
+        <v>1.851644280252276</v>
       </c>
       <c r="F2063" t="n">
         <v>0.5332132690336198</v>
@@ -49023,10 +49023,10 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.93308172062175</v>
+        <v>-5.665704913035175</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.726056808628249</v>
+        <v>1.833007531662878</v>
       </c>
       <c r="F2064" t="n">
         <v>0.4903682783554602</v>
@@ -49046,10 +49046,10 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.849856263774086</v>
+        <v>-5.582479456187511</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.779221384217633</v>
+        <v>1.886172107252263</v>
       </c>
       <c r="F2065" t="n">
         <v>0.4903682783554602</v>
@@ -49069,10 +49069,10 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.673566039168779</v>
+        <v>-5.406189231582204</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.833438174584484</v>
+        <v>1.940388897619114</v>
       </c>
       <c r="F2066" t="n">
         <v>0.4903682783554602</v>
@@ -49092,10 +49092,10 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.490354376035683</v>
+        <v>-5.222977568449108</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.909153789301768</v>
+        <v>2.016104512336398</v>
       </c>
       <c r="F2067" t="n">
         <v>0.4903682783554602</v>
@@ -49115,10 +49115,10 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.418632929021832</v>
+        <v>-5.151256121435257</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.903633553955197</v>
+        <v>2.010584276989828</v>
       </c>
       <c r="F2068" t="n">
         <v>0.5620897253693108</v>
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.445766695504546</v>
+        <v>3.779153069968575</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.399036910612283</v>
+        <v>-5.280634904075035</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.858387707240189</v>
+        <v>1.905748509855088</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.5491045611932437</v>
+        <v>0.5199879526621074</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.347821632514796</v>
+        <v>4.330351667396114</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240828.xlsx
+++ b/tame_output/ON/bt/strategyON_20240828.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>18.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-80.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,12 +926,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.7%</t>
+          <t>126.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.1%</t>
+          <t>-39.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.5%</t>
+          <t>-49.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.6%</t>
+          <t>419.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-689.6%</t>
+          <t>-712.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>-32.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-185.6%</t>
+          <t>-194.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>119.0%</t>
+          <t>117.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-291.9%</t>
+          <t>-414.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-172.0%</t>
+          <t>-189.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-21.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-23.2%</t>
         </is>
       </c>
     </row>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017768</v>
+        <v>3.789311112017767</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.387179508203313</v>
+        <v>-4.539051668895209</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9153748702776623</v>
+        <v>0.8546260060009037</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3334542790038589</v>
+        <v>0.2117052213680753</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.87067566527505</v>
+        <v>2.79762623069358</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.471000729478011</v>
+        <v>-4.622872890169908</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8846400032992638</v>
+        <v>0.8238911390225052</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3334542790038589</v>
+        <v>0.2117052213680753</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.873469286806531</v>
+        <v>2.800419852225061</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.464848023425227</v>
+        <v>-4.616720184117123</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.887763434112036</v>
+        <v>0.8270145698352773</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3396069850566432</v>
+        <v>0.2178579274208596</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.87782325882986</v>
+        <v>2.80477382424839</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.481657321575729</v>
+        <v>-4.633529482267625</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8801201915919454</v>
+        <v>0.8193713273151868</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3227976869061415</v>
+        <v>0.2010486292703579</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.86681815667967</v>
+        <v>2.793768722098199</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.419359322799607</v>
+        <v>-4.571231483491503</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9713749448992153</v>
+        <v>0.9106260806224566</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3680919511805836</v>
+        <v>0.2463428935448</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.960330269041155</v>
+        <v>2.887280834459685</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.217569125134449</v>
+        <v>-4.369441285826345</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8543830256794054</v>
+        <v>0.793634161402647</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.566110143349738</v>
+        <v>0.4443610857139544</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.881433186056775</v>
+        <v>2.808383751475305</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.268455837820643</v>
+        <v>-4.42032799851254</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9043185729271028</v>
+        <v>0.8435697086503442</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5152234306635435</v>
+        <v>0.3934743730277598</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.921191390767234</v>
+        <v>2.848141956185763</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.181845095170837</v>
+        <v>-4.333717255862733</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9535906061030692</v>
+        <v>0.8928417418263106</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5938491618687017</v>
+        <v>0.4721001042329181</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.982994565606372</v>
+        <v>2.909945131024902</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.242054393176121</v>
+        <v>-4.393926553868018</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9280428677256269</v>
+        <v>0.8672940034488683</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5336398638634172</v>
+        <v>0.4118908062276336</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.945404967627873</v>
+        <v>2.872355533046403</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.165632346744195</v>
+        <v>-4.317504507436091</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9571033043383261</v>
+        <v>0.8963544400615677</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5336398638634172</v>
+        <v>0.4118908062276336</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.943896585667802</v>
+        <v>2.870847151086332</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.121259215105626</v>
+        <v>-4.273131375797522</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9747154244291898</v>
+        <v>0.9139665601524314</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5780129955019858</v>
+        <v>0.4562639378662022</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.970383332086379</v>
+        <v>2.897333897504909</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.143739565964511</v>
+        <v>-4.295611726656407</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9601170782242263</v>
+        <v>0.8993682139474679</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5780129955019858</v>
+        <v>0.4562639378662022</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.96477712622497</v>
+        <v>2.891727691643499</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.096083835403455</v>
+        <v>-4.247955996095351</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9855611274764533</v>
+        <v>0.9248122631996949</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6256687260630415</v>
+        <v>0.5039196684272578</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.999752321589408</v>
+        <v>2.926702887007937</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.9955656769047</v>
+        <v>-4.147437837596597</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.03066076425068</v>
+        <v>0.9699118999739216</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.726186884561796</v>
+        <v>0.6044378269260123</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.064955590063385</v>
+        <v>2.991906155481915</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.979660347472348</v>
+        <v>-4.131532508164244</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.023777568499493</v>
+        <v>0.9630287042227348</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6470742238525571</v>
+        <v>0.5253251662167735</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.004242666113714</v>
+        <v>2.931193231532244</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.93482194586395</v>
+        <v>-4.086694106555846</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.045810631753481</v>
+        <v>0.9850617674767228</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6516176567974266</v>
+        <v>0.529868599161643</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.011066428491264</v>
+        <v>2.938016993909794</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.954320402105958</v>
+        <v>-4.106192562797854</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.042172188887756</v>
+        <v>0.9814233246109976</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6035330155175223</v>
+        <v>0.4817839578817387</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.9863765833544</v>
+        <v>2.91332714877293</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.910117565020057</v>
+        <v>-4.061989725711953</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.065732926249953</v>
+        <v>1.004984061973195</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6477358526034227</v>
+        <v>0.5259867949676391</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.018777888133777</v>
+        <v>2.945728453552307</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.917677230857104</v>
+        <v>-4.069549391549</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.061119060384382</v>
+        <v>1.000370196107624</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.702539256613242</v>
+        <v>0.5807901989774584</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.050069931008916</v>
+        <v>2.977020496427446</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.759385813317832</v>
+        <v>-3.911257974009728</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.17568339258313</v>
+        <v>1.114934528306372</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.702539256613242</v>
+        <v>0.5807901989774584</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.101317696191956</v>
+        <v>3.028268261610486</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.551743809683356</v>
+        <v>-3.703615970375251</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.257180898631174</v>
+        <v>1.196432034354416</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9101812602477182</v>
+        <v>0.7884322026119346</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.224343602966895</v>
+        <v>3.151294168385425</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.500711716960828</v>
+        <v>-3.652583877652723</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.272541963958455</v>
+        <v>1.211793099681697</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9612133529702461</v>
+        <v>0.8394642953344625</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.249911086838682</v>
+        <v>3.176861652257212</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.435487535833622</v>
+        <v>-3.587359696525517</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.315819040502042</v>
+        <v>1.255070176225284</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.026437534097452</v>
+        <v>0.9046884764616682</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.30623299960771</v>
+        <v>3.23318356502624</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.398060515762488</v>
+        <v>-3.549932676454384</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.326750820829776</v>
+        <v>1.266001956553018</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.031689072126633</v>
+        <v>0.9099400144908498</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.305344894724499</v>
+        <v>3.232295460143029</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.418172171797197</v>
+        <v>-3.570044332489092</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.319962950747133</v>
+        <v>1.259214086470375</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.042716417124052</v>
+        <v>0.920967359488269</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.313218094054191</v>
+        <v>3.240168659472721</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.389758908697313</v>
+        <v>-3.541631069389208</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.491886027008298</v>
+        <v>1.431137162731539</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9837408543776236</v>
+        <v>0.8619917967418402</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.438390527427544</v>
+        <v>3.365341092846074</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.3149766476723</v>
+        <v>-3.466848808364196</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.64191184063612</v>
+        <v>1.581162976359362</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.058523115402636</v>
+        <v>0.9367740577668529</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.603372793260369</v>
+        <v>3.530323358678899</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.288892563408492</v>
+        <v>-3.440764724100388</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.644053450355502</v>
+        <v>1.583304586078744</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.058523115402636</v>
+        <v>0.9367740577668529</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.595080769274228</v>
+        <v>3.522031334692758</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.201014650299372</v>
+        <v>-3.352886810991267</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.67739781118293</v>
+        <v>1.616648946906172</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.174448757825987</v>
+        <v>1.052699700190204</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.662829350312018</v>
+        <v>3.589779915730548</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.192122188906088</v>
+        <v>-3.343994349597984</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.698509201467034</v>
+        <v>1.637760337190276</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.174448757825987</v>
+        <v>1.052699700190204</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.68038375603881</v>
+        <v>3.60733432145734</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.360598305875966</v>
+        <v>-3.512470466567862</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.622973802083667</v>
+        <v>1.562224937806909</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.146500922109406</v>
+        <v>1.024751864473623</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.655470102013445</v>
+        <v>3.582420667431975</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.914342113246526</v>
+        <v>-3.066214273938422</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.782745976323305</v>
+        <v>1.721997112046547</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.051782252439774</v>
+        <v>0.9300331948039906</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.579908597399527</v>
+        <v>3.506859162818058</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.891621009563374</v>
+        <v>-3.043493170255269</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.782498440293471</v>
+        <v>1.721749576016713</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.051782252439774</v>
+        <v>0.9300331948039906</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.570572619896432</v>
+        <v>3.497523185314962</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.020822822857416</v>
+        <v>-3.172694983549312</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.889723840827023</v>
+        <v>1.828974976550265</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9225804391457315</v>
+        <v>0.8008313815099484</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.651957657771176</v>
+        <v>3.578908223189706</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.046697221331442</v>
+        <v>-3.198569382023337</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.916451903931059</v>
+        <v>1.855703039654301</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9674920478574727</v>
+        <v>0.8457429902216895</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.715982445491867</v>
+        <v>3.642933010910397</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.039642531116268</v>
+        <v>-3.191514691808164</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.915949136006674</v>
+        <v>1.855200271729915</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9745467380726465</v>
+        <v>0.8527976804368633</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.716890615610517</v>
+        <v>3.643841181029047</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.01269130678978</v>
+        <v>-3.164563467481676</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.93673577938201</v>
+        <v>1.875986915105252</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9894270841003656</v>
+        <v>0.8676780264645825</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.735824976871889</v>
+        <v>3.66277554229042</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.058050489527874</v>
+        <v>-3.209922650219769</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.102695238431733</v>
+        <v>2.041946374154975</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9894270841003656</v>
+        <v>0.8676780264645825</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.919928109016849</v>
+        <v>3.846878674435379</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.080458607332746</v>
+        <v>-3.232330768024641</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.085848686212777</v>
+        <v>2.025099821936019</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9894270841003656</v>
+        <v>0.8676780264645825</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.912044803919843</v>
+        <v>3.838995369338372</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.108682842910346</v>
+        <v>-3.260555003602242</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.076612991531374</v>
+        <v>2.015864127254616</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.007403836551674</v>
+        <v>0.8856547789158911</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.924884854940265</v>
+        <v>3.851835420358795</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.118123768798876</v>
+        <v>-3.269995929490772</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.12909033889781</v>
+        <v>2.068341474621051</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.129830954095066</v>
+        <v>1.008081896459283</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.054594843188147</v>
+        <v>3.981545408606677</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.170397376134518</v>
+        <v>-3.322269536826413</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.111071990508854</v>
+        <v>2.050323126232096</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.077557346759424</v>
+        <v>0.9558082891236414</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.026121773332063</v>
+        <v>3.953072338750593</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.246727353735424</v>
+        <v>-3.398599514427319</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.078651812362267</v>
+        <v>2.017902948085508</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.077557346759424</v>
+        <v>0.9558082891236414</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.024233586225838</v>
+        <v>3.951184151644369</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.448981074059777</v>
+        <v>-3.600853234751672</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.992570553835388</v>
+        <v>1.93182168955863</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8753036264350709</v>
+        <v>0.7535545687992879</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.897701583634088</v>
+        <v>3.824652149052619</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.610549499587032</v>
+        <v>-3.762421660278927</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.926377193834638</v>
+        <v>1.86562832955788</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7485207026371915</v>
+        <v>0.6267716450014086</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.820065839565513</v>
+        <v>3.747016404984043</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.718850161457151</v>
+        <v>-3.870722322149047</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.896130335952509</v>
+        <v>1.835381471675751</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7485207026371915</v>
+        <v>0.6267716450014086</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.833139246431432</v>
+        <v>3.760089811849962</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.811997632760518</v>
+        <v>-3.963869793452413</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.850876544214102</v>
+        <v>1.790127679937344</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6256914913546587</v>
+        <v>0.5039424337188758</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.751446916444852</v>
+        <v>3.678397481863382</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.839898419869991</v>
+        <v>-3.991770580561886</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.838240270497315</v>
+        <v>1.777491406220557</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5910945672117239</v>
+        <v>0.469345509575941</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.729212803086093</v>
+        <v>3.656163368504624</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.962424522572885</v>
+        <v>-4.11429668326478</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.785994273393356</v>
+        <v>1.725245409116598</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4685684645088301</v>
+        <v>0.3468194068730471</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.652461585441555</v>
+        <v>3.579412150860086</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.192939018758474</v>
+        <v>-4.344811179450369</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.760494434509624</v>
+        <v>1.699745570232866</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2380539683232413</v>
+        <v>0.1163049106874584</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.580858847320706</v>
+        <v>3.507809412739237</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.541684103982917</v>
+        <v>-4.693556264674813</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.761308119421694</v>
+        <v>1.700559255144936</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1293060144043435</v>
+        <v>0.007556956768560608</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.655921793971214</v>
+        <v>3.582872359389745</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.695670521759058</v>
+        <v>-4.847542682450953</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.768693821456877</v>
+        <v>1.707944957180119</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1293060144043435</v>
+        <v>0.007556956768560608</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.724902063116854</v>
+        <v>3.651852628535385</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.645148617931392</v>
+        <v>-4.797020778623287</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.774953785108065</v>
+        <v>1.714204920831306</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1293060144043435</v>
+        <v>0.007556956768560608</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.710953265236975</v>
+        <v>3.637903830655505</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.897623771939116</v>
+        <v>-5.049495932631012</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.685834212560389</v>
+        <v>1.625085348283631</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1293060144043435</v>
+        <v>0.007556956768560608</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.722823754292389</v>
+        <v>3.649774319710919</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.190519528418529</v>
+        <v>-5.342391689110424</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.569886444487568</v>
+        <v>1.50913758021081</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1293060144043435</v>
+        <v>0.007556956768560608</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.724034288811333</v>
+        <v>3.650984854229863</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.377183656553337</v>
+        <v>-5.529055817245232</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.499342535460966</v>
+        <v>1.438593671184208</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1025670435797836</v>
+        <v>-0.01918201405599929</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.712112648543918</v>
+        <v>3.639063213962448</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.523204343467299</v>
+        <v>-5.675076504159194</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.436012113431571</v>
+        <v>1.375263249154812</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.09348395178592667</v>
+        <v>-0.02826510584985625</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.701740646203794</v>
+        <v>3.628691211622324</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.614918352576884</v>
+        <v>-5.766790513268779</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.56153056648678</v>
+        <v>1.500781702210022</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.09348395178592667</v>
+        <v>-0.02826510584985625</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.863944702902838</v>
+        <v>3.790895268321368</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.646570011636854</v>
+        <v>-5.798442172328748</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.543716540826607</v>
+        <v>1.482967676549849</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.08831549454148646</v>
+        <v>-0.03343356309429646</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.855690266519987</v>
+        <v>3.782640831938518</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.728504829905737</v>
+        <v>-5.880376990597632</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.521172031087545</v>
+        <v>1.460423166810787</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.07838074895440628</v>
+        <v>-0.04336830868137664</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.859958836736231</v>
+        <v>3.786909402154761</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.830480952154145</v>
+        <v>-5.982353112846039</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.489307220644084</v>
+        <v>1.428558356367326</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.0235953732940013</v>
+        <v>-0.1453444309297842</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.807698801843089</v>
+        <v>3.734649367261619</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.720474668676923</v>
+        <v>-5.872346829368817</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.525462621279148</v>
+        <v>1.46471375700239</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.0003908013767260909</v>
+        <v>-0.122139859012509</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.813774432237629</v>
+        <v>3.740724997656159</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.577415092935997</v>
+        <v>-5.729287253627891</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.586936462297493</v>
+        <v>1.526187598020735</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.007622625213253187</v>
+        <v>-0.1141264324225297</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.822832498913591</v>
+        <v>3.749783064332121</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.275968367464159</v>
+        <v>-5.427840528156054</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.714776035368764</v>
+        <v>1.654027171092006</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3090693506850904</v>
+        <v>0.1873202930493075</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.010961417079229</v>
+        <v>3.937911982497759</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.300558611699343</v>
+        <v>-5.452430772391238</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.705911115427401</v>
+        <v>1.645162251150643</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3090693506850904</v>
+        <v>0.1873202930493075</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.01193259483194</v>
+        <v>3.93888316025047</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.249520235692823</v>
+        <v>-5.401392396384717</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.727169370209765</v>
+        <v>1.666420505933007</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3090693506850904</v>
+        <v>0.1873202930493075</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.012775499211696</v>
+        <v>3.939726064630226</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.208380940826192</v>
+        <v>-5.360253101518087</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.762663187030562</v>
+        <v>1.701914322753804</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3502086455517213</v>
+        <v>0.2284595879159383</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.05649717500582</v>
+        <v>3.983447740424349</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.111746028807552</v>
+        <v>-5.263618189499446</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.617501147961953</v>
+        <v>1.556752283685195</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4468435575703612</v>
+        <v>0.3250944999345783</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.930662118340938</v>
+        <v>3.857612683759468</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.242326763338395</v>
+        <v>-5.394198924030289</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.56877089822358</v>
+        <v>1.508022033946822</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3162628230395187</v>
+        <v>0.1945137654037358</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.855815721696397</v>
+        <v>3.782766287114927</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.077830429147433</v>
+        <v>-5.229702589839327</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.618996250976047</v>
+        <v>1.55824738669929</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4807591572304806</v>
+        <v>0.3590100995946977</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.938940341287056</v>
+        <v>3.865890906705586</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.105200361831865</v>
+        <v>-5.257072522523759</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.607235988338704</v>
+        <v>1.546487124061946</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4807591572304806</v>
+        <v>0.3590100995946977</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.938128051723486</v>
+        <v>3.865078617142016</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.115585556721754</v>
+        <v>-5.267457717413649</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.612950689507821</v>
+        <v>1.552201825231063</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4703739623405913</v>
+        <v>0.3486249047048083</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.941765713914624</v>
+        <v>3.868716279333155</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.134173715443979</v>
+        <v>-5.286045876135874</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.676352431795356</v>
+        <v>1.615603567518598</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4517858036183659</v>
+        <v>0.330036745982583</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.001449824457715</v>
+        <v>3.928400389876245</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.85512053549655</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.134472262140015</v>
+        <v>-5.28634442283191</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.67310202393524</v>
+        <v>1.612353159658482</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.45148725692233</v>
+        <v>0.3297381992865471</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.998139707258392</v>
+        <v>3.925090272676922</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.033649128449587</v>
+        <v>-5.185521289141482</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.717962172350803</v>
+        <v>1.657213308074045</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4639514724066838</v>
+        <v>0.3422024147709009</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.010149131488395</v>
+        <v>3.937099696906926</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.842867767697181</v>
+        <v>-4.994739928389075</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.794403970130309</v>
+        <v>1.733655105853551</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6547328331590911</v>
+        <v>0.5329837755233082</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.124747201418383</v>
+        <v>4.051697766836913</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.82435091365536</v>
+        <v>-4.976223074347255</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.781647557484633</v>
+        <v>1.720898693207876</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6676629625842994</v>
+        <v>0.5459139049485164</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.112342124811105</v>
+        <v>4.039292690229635</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.769020325753598</v>
+        <v>-4.920892486445492</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.838746729257397</v>
+        <v>1.777997864980639</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7229935504860615</v>
+        <v>0.6012444928502786</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.180507414164221</v>
+        <v>4.10745797958275</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.756966198840635</v>
+        <v>-4.908838359532529</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.83725494792402</v>
+        <v>1.776506083647262</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7350476773990243</v>
+        <v>0.6132986197632414</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.181426458213435</v>
+        <v>4.108377023631966</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.798121318408856</v>
+        <v>-4.94999347910075</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.822673530280867</v>
+        <v>1.761924666004109</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6938925578308034</v>
+        <v>0.5721435001950205</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.158614016656639</v>
+        <v>4.085564582075169</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.695240728880263</v>
+        <v>-4.847112889572157</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.876676791970187</v>
+        <v>1.815927927693429</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7967731473593963</v>
+        <v>0.6750240897236134</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.233193396251677</v>
+        <v>4.160143961670207</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.926841122049764</v>
+        <v>-5.078713282741658</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.804239304875981</v>
+        <v>1.743490440599223</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7967731473593963</v>
+        <v>0.6750240897236134</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.253396066425271</v>
+        <v>4.180346631843801</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.944913630341375</v>
+        <v>-5.09678579103327</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.797010301559336</v>
+        <v>1.736261437282578</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7967731473593963</v>
+        <v>0.6750240897236134</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.253396066425271</v>
+        <v>4.180346631843801</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.12002046291782</v>
+        <v>-5.271892623609714</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.687219482122225</v>
+        <v>1.626470617845467</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7967731473593963</v>
+        <v>0.6750240897236134</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.213647980018738</v>
+        <v>4.140598545437268</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.088734442377365</v>
+        <v>-5.240606603069259</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.706756509335347</v>
+        <v>1.646007645058589</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8280591678998517</v>
+        <v>0.7063101102640688</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.239442211339951</v>
+        <v>4.166392776758482</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.93570905026408</v>
+        <v>-5.087581210955975</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.867137665753565</v>
+        <v>1.806388801476807</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9810845600131358</v>
+        <v>0.8593355023773529</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.430428446180827</v>
+        <v>4.357379011599356</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.96401636413735</v>
+        <v>-5.115888524829245</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.043280965112549</v>
+        <v>1.982532100835791</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9810845600131358</v>
+        <v>0.8593355023773529</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.617894671089118</v>
+        <v>4.544845236507649</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.130609589250873</v>
+        <v>-5.282481749942767</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.946046626421222</v>
+        <v>1.885297762144465</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8144913348996135</v>
+        <v>0.6927422772638305</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.487341687375087</v>
+        <v>4.414292252793618</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.957545209868573</v>
+        <v>-5.109417370560467</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.01894878083586</v>
+        <v>1.958199916559102</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8144913348996135</v>
+        <v>0.6927422772638305</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.491018090036805</v>
+        <v>4.417968655455335</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.928299229412876</v>
+        <v>-5.080171390104771</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.028265228141634</v>
+        <v>1.967516363864876</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8144913348996135</v>
+        <v>0.6927422772638305</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.4886361451603</v>
+        <v>4.415586710578831</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.035224777290727</v>
+        <v>-5.187096937982622</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.982788248148128</v>
+        <v>1.922039383871371</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7075657870217621</v>
+        <v>0.5858167293859792</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.421774055591224</v>
+        <v>4.348724621009755</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.180243335797976</v>
+        <v>-5.33211549648987</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.926209626888463</v>
+        <v>1.865460762611705</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5625472285145136</v>
+        <v>0.4407981708787306</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.33619172263011</v>
+        <v>4.263142288048639</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.298585101582693</v>
+        <v>-5.450457262274588</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.978804159832329</v>
+        <v>1.918055295555571</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5732332670774036</v>
+        <v>0.4514842094416207</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.442534585025596</v>
+        <v>4.369485150444127</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.349995523903401</v>
+        <v>-5.501867684595296</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.956025688029985</v>
+        <v>1.895276823753227</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5732332670774036</v>
+        <v>0.4514842094416207</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.440320282151535</v>
+        <v>4.367270847570065</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.429414975111153</v>
+        <v>-5.581287135803048</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.924161035621174</v>
+        <v>1.863412171344416</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5732332670774036</v>
+        <v>0.4514842094416207</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.440223410225824</v>
+        <v>4.367173975644355</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.524877973028371</v>
+        <v>-5.676750133720265</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.88596973001233</v>
+        <v>1.825220865735572</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5732332670774036</v>
+        <v>0.4514842094416207</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.440217303783868</v>
+        <v>4.367167869202398</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.564897971072154</v>
+        <v>-5.716770131764049</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.868058127357427</v>
+        <v>1.80730926308067</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.5332132690336198</v>
+        <v>0.4114642113978369</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.414301701520208</v>
+        <v>4.341252266938739</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.620267133204348</v>
+        <v>-5.772139293896243</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.851644280252276</v>
+        <v>1.790895415975519</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.5332132690336198</v>
+        <v>0.4114642113978369</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.420035519267935</v>
+        <v>4.346986084686465</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.665704913035175</v>
+        <v>-5.81757707372707</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.833007531662878</v>
+        <v>1.772258667386121</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.4903682783554602</v>
+        <v>0.3686192207196772</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.393866888203973</v>
+        <v>4.320817453622502</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.582479456187511</v>
+        <v>-5.734351616879406</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.886172107252263</v>
+        <v>1.825423242975506</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.4903682783554602</v>
+        <v>0.3686192207196772</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.413741281054292</v>
+        <v>4.340691846472821</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.406189231582204</v>
+        <v>-5.558061392274098</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.940388897619114</v>
+        <v>1.879640033342356</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.4903682783554602</v>
+        <v>0.3686192207196772</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.39744198157902</v>
+        <v>4.324392546997549</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.222977568449108</v>
+        <v>-5.374849729141003</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.016104512336398</v>
+        <v>1.95535564805964</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.4903682783554602</v>
+        <v>0.3686192207196772</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.399872931043065</v>
+        <v>4.326823496461595</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.151256121435257</v>
+        <v>-5.303128282127152</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.010584276989828</v>
+        <v>1.94983541271307</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.5620897253693108</v>
+        <v>0.4403406677335279</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.408696985099264</v>
+        <v>4.335647550517795</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.779153069968575</v>
+        <v>3.464538809209484</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.280634904075035</v>
+        <v>-5.508374562017834</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.905748509855088</v>
+        <v>1.814652646677969</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.5199879526621074</v>
+        <v>0.3494359513054088</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.330351667396114</v>
+        <v>4.228020466582095</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240828.xlsx
+++ b/tame_output/ON/bt/strategyON_20240828.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>56.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>108.2%</t>
         </is>
       </c>
     </row>
@@ -916,26 +916,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.7%</t>
+          <t>-80.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>126.0%</t>
+          <t>125.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-39.0%</t>
+          <t>-34.1%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-49.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>419.8%</t>
+          <t>423.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-712.4%</t>
+          <t>-699.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-35.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-194.8%</t>
+          <t>-189.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>117.6%</t>
+          <t>112.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-414.2%</t>
+          <t>-290.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-189.0%</t>
+          <t>-172.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>79.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.3%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-26.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2069"/>
+  <dimension ref="A1:G2070"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.999629369512789</v>
+        <v>-9.002246706699946</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4216946214411483</v>
+        <v>-0.4227415563160113</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.514814833504967</v>
+        <v>-1.517432170692126</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.269624650574735</v>
+        <v>2.268054248262439</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.906170335527564</v>
+        <v>-8.908787672714721</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.394194489159966</v>
+        <v>-0.395241424034829</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.514814833504967</v>
+        <v>-1.517432170692126</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.259741169261827</v>
+        <v>2.258170766949532</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.895517153974133</v>
+        <v>-8.89813449116129</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3917677770379671</v>
+        <v>-0.39281471191283</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.514814833504967</v>
+        <v>-1.517432170692126</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.257906608762453</v>
+        <v>2.256336206450158</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.797610115297642</v>
+        <v>-8.800227452484799</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3529052765408318</v>
+        <v>-0.3539522114156948</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.446829083644411</v>
+        <v>-1.44944642083157</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.298397743705326</v>
+        <v>2.296827341393031</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.773656574321684</v>
+        <v>-8.776273911508842</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3426553540049548</v>
+        <v>-0.3437022888798178</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.422875542668453</v>
+        <v>-1.425492879855612</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.313438374436394</v>
+        <v>2.311867972124099</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.509596635998887</v>
+        <v>-8.512213973186045</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2502916948375882</v>
+        <v>-0.2513386297124511</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.158815604345657</v>
+        <v>-1.161432941532816</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.45861402126832</v>
+        <v>2.457043618956025</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.802517012494049</v>
+        <v>-7.805134349681206</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.02975312090404625</v>
+        <v>0.02870618602918329</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.158815604345657</v>
+        <v>-1.161432941532816</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.455826987608019</v>
+        <v>2.454256585295724</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.762332714127859</v>
+        <v>-7.764950051315016</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.04617046413836379</v>
+        <v>0.04512352926350083</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.118631305979466</v>
+        <v>-1.121248643166625</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.480281190515575</v>
+        <v>2.47871078820328</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.598932843188496</v>
+        <v>-7.601550180375654</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1108972337348657</v>
+        <v>0.1098502988600027</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9552314350401039</v>
+        <v>-0.9578487722272624</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.577687934299949</v>
+        <v>2.576117531987654</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.365451620958898</v>
+        <v>-7.368068958146055</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2122141514645572</v>
+        <v>0.2111672165896943</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.7217502128105053</v>
+        <v>-0.7243675499976638</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.725701096475561</v>
+        <v>2.724130694163266</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.215785229951383</v>
+        <v>-7.21840256713854</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2691884975546044</v>
+        <v>0.2681415626797414</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.6288467215679694</v>
+        <v>-0.6314640587551279</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.778550980908123</v>
+        <v>2.776980578595828</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.083509756320496</v>
+        <v>-7.086127093507653</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2233594730141135</v>
+        <v>0.2223125381392506</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4965712479370827</v>
+        <v>-0.4991885851242412</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.75917705109381</v>
+        <v>2.757606648781515</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.927771423760754</v>
+        <v>-6.930388760947912</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2884698667256469</v>
+        <v>0.2874229318507839</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3408329153773412</v>
+        <v>-0.3434502525644997</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.855435111317292</v>
+        <v>2.853864709004997</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.842806757031434</v>
+        <v>-6.845424094218592</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3353620746410337</v>
+        <v>0.3343151397661708</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2558682486480216</v>
+        <v>-0.2584855858351801</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.919320252578542</v>
+        <v>2.917749850266247</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.948396746804539</v>
+        <v>-6.951014083991696</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.1651501491325731</v>
+        <v>0.1641032142577101</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.361458238421126</v>
+        <v>-0.3640755756082845</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.727990329115461</v>
+        <v>2.726419926803166</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.880162162179111</v>
+        <v>-6.882779499366269</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2409883248598303</v>
+        <v>0.2399413899849678</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.34304291554859</v>
+        <v>-0.3456602527357485</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.787583864716069</v>
+        <v>2.786013462403774</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.732222120771512</v>
+        <v>-6.734839457958669</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.183543532784463</v>
+        <v>0.1824965979096005</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3227219996400324</v>
+        <v>-0.3253393368271909</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.683155605622796</v>
+        <v>2.681585203310501</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.679252598517524</v>
+        <v>-6.681869935704681</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1960173554325806</v>
+        <v>0.1949704205577176</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2697524773860435</v>
+        <v>-0.272369814573202</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.706223332721711</v>
+        <v>2.704652930409416</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.513464402557233</v>
+        <v>-6.51608173974439</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2553720217216036</v>
+        <v>0.2543250868467406</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2697524773860435</v>
+        <v>-0.272369814573202</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.699262720626618</v>
+        <v>2.697692318314323</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.480101196078464</v>
+        <v>-6.482718533265621</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2831796586942543</v>
+        <v>0.2821327238193914</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2697524773860435</v>
+        <v>-0.272369814573202</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.713725075007761</v>
+        <v>2.712154672695466</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.371842058955942</v>
+        <v>-6.3744593961431</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.321015434002458</v>
+        <v>0.3199684991275951</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2697524773860435</v>
+        <v>-0.272369814573202</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.708257195466956</v>
+        <v>2.706686793154661</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.248550924138812</v>
+        <v>-6.251168261325969</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3678299819398871</v>
+        <v>0.3667830470650242</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.146461342568913</v>
+        <v>-0.1490786797560715</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.779729970367812</v>
+        <v>2.778159568055516</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.19585405700752</v>
+        <v>-6.198471394194677</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3966097070297288</v>
+        <v>0.3955627721548658</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.09376447543762184</v>
+        <v>-0.09638181262478035</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.819049068883911</v>
+        <v>2.817478666571616</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.952088615024076</v>
+        <v>-5.954705952211233</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4898965921701572</v>
+        <v>0.4888496572952943</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.09376447543762184</v>
+        <v>-0.09638181262478035</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.814829777230962</v>
+        <v>2.813259374918667</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.862312942647604</v>
+        <v>-5.864930279834761</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.527931175040762</v>
+        <v>0.5268842401658991</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.03216503052331182</v>
+        <v>-0.03478236771047033</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.853913758099564</v>
+        <v>2.852343355787269</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.612462548698529</v>
+        <v>-5.615079885885686</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6206134076040941</v>
+        <v>0.6195664727292312</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.03216503052331182</v>
+        <v>-0.03478236771047033</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.846655833083266</v>
+        <v>2.845085430770971</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.436570456231097</v>
+        <v>-5.439187793418254</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6945693681117158</v>
+        <v>0.6935224332368528</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.03216503052331182</v>
+        <v>-0.03478236771047033</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.850254956603915</v>
+        <v>2.84868455429162</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.265123993208634</v>
+        <v>-5.267741330395791</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7764754593752548</v>
+        <v>0.7754285245003918</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1392814324991513</v>
+        <v>0.1366640953119928</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.966450340471947</v>
+        <v>2.964879938159652</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.185101706099513</v>
+        <v>-5.18771904328667</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8075048518351999</v>
+        <v>0.8064579169603374</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2193037196082723</v>
+        <v>0.2166863824211138</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.013484190353716</v>
+        <v>3.011913788041421</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.121465963865578</v>
+        <v>-5.124083301052735</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8376539497830913</v>
+        <v>0.8366070149082283</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2829394618422068</v>
+        <v>0.2803221246550483</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.056360436748394</v>
+        <v>3.054790034436099</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.027768645649183</v>
+        <v>-5.03038598283634</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8563271358534448</v>
+        <v>0.8552802009785818</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2829394618422068</v>
+        <v>0.2803221246550483</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.03755469553219</v>
+        <v>3.035984293219895</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.038271268714472</v>
+        <v>-5.040888605901629</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8538691632522069</v>
+        <v>0.8528222283773439</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2724368387769179</v>
+        <v>0.2698195015897594</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.032996198317894</v>
+        <v>3.031425796005599</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.966028700543277</v>
+        <v>-4.968646037730434</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8866955043555047</v>
+        <v>0.885648569480642</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2724368387769179</v>
+        <v>0.2698195015897594</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.036925512152714</v>
+        <v>3.035355109840419</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.948315013665412</v>
+        <v>-4.950932350852569</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8944595630239909</v>
+        <v>0.8934126281491279</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2756181676738347</v>
+        <v>0.2730008304866762</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.039512893408204</v>
+        <v>3.037942491095909</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.839510128185685</v>
+        <v>-4.842127465372842</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9349795884358751</v>
+        <v>0.9339326535610124</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2756181676738347</v>
+        <v>0.2730008304866762</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.036510964628198</v>
+        <v>3.034940562315902</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.619489330148674</v>
+        <v>-4.622106667335832</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.024566944661293</v>
+        <v>1.023520009786431</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.416838012741815</v>
+        <v>0.4142206755546565</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.1228219086796</v>
+        <v>3.121251506367305</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.486621641085397</v>
+        <v>-4.489238978272554</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.093608203088428</v>
+        <v>1.092561268213565</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.416838012741815</v>
+        <v>0.4142206755546565</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.138716091481423</v>
+        <v>3.137145689169128</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.366448557720898</v>
+        <v>-4.369065894908055</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.142823280874529</v>
+        <v>1.141776345999666</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5370110961063139</v>
+        <v>0.5343937589191554</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.211965785940424</v>
+        <v>3.210395383628129</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.231195196390921</v>
+        <v>-4.233812533578078</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.20701272796796</v>
+        <v>1.205965793093097</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.672264457436291</v>
+        <v>0.6696471202491325</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.30320590529985</v>
+        <v>3.301635502987555</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.291070023748613</v>
+        <v>-4.29368736093577</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.169100288426309</v>
+        <v>1.168053353551446</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6123896300785989</v>
+        <v>0.6097722928914404</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.253318500286661</v>
+        <v>3.251748097974366</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.171249792837776</v>
+        <v>-4.173867130024933</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.232317550024852</v>
+        <v>1.231270615149989</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6123896300785989</v>
+        <v>0.6097722928914404</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.26860766952087</v>
+        <v>3.267037267208575</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.173719499299582</v>
+        <v>-4.176336836486739</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.138973866762571</v>
+        <v>1.137926931887709</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6099199236167927</v>
+        <v>0.6073025864296342</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.174770044966227</v>
+        <v>3.173199642653932</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.242089685623593</v>
+        <v>-4.24470702281075</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.030887653718269</v>
+        <v>1.029840718843406</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6191956226530076</v>
+        <v>0.6165782854658491</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.099597325873258</v>
+        <v>3.098026923560963</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.353961965249743</v>
+        <v>-4.3565793024369</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9765754504996997</v>
+        <v>0.9755285156248368</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6191956226530076</v>
+        <v>0.6165782854658491</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.090034034505149</v>
+        <v>3.088463632192854</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.409482041142333</v>
+        <v>-4.41209937832949</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.091398256834866</v>
+        <v>1.090351321960003</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6191956226530076</v>
+        <v>0.6165782854658491</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.227064871197352</v>
+        <v>3.225494468885056</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.234007781349863</v>
+        <v>-4.23662511853702</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.166155192743642</v>
+        <v>1.165108257868779</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6191956226530076</v>
+        <v>0.6165782854658491</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.231632103189139</v>
+        <v>3.230061700876844</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.226083406764949</v>
+        <v>-4.228700743952106</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.145066971338815</v>
+        <v>1.144020036463952</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6191956226530076</v>
+        <v>0.6165782854658491</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.207374131950346</v>
+        <v>3.205803729638051</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.2198052041951</v>
+        <v>-4.222422541382257</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.076116565768204</v>
+        <v>1.075069630893341</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6254738252228567</v>
+        <v>0.6228564880356982</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.139679366893705</v>
+        <v>3.13810896458141</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.159952584991377</v>
+        <v>-4.162569922178534</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.110229999881826</v>
+        <v>1.109183065006963</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6254738252228567</v>
+        <v>0.6228564880356982</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.149851753325838</v>
+        <v>3.148281351013543</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.073709121964999</v>
+        <v>-4.076326459152156</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.139673655666237</v>
+        <v>1.138626720791374</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6254738252228567</v>
+        <v>0.6228564880356982</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.144798023899698</v>
+        <v>3.143227621587403</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.119015941363979</v>
+        <v>-4.121633278551136</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.113326703351171</v>
+        <v>1.112279768476308</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5846636622136259</v>
+        <v>0.5820463250264674</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.112087701538685</v>
+        <v>3.11051729922639</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.14804904606628</v>
+        <v>-4.150666383253437</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.102265334503352</v>
+        <v>1.101218399628489</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5846636622136259</v>
+        <v>0.5820463250264674</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.112639574571787</v>
+        <v>3.111069172259492</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.05523856461542</v>
+        <v>-4.057855901802577</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.068662218975061</v>
+        <v>1.067615284100198</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6774741436644852</v>
+        <v>0.6748568064773267</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.097598555333668</v>
+        <v>3.096028153021373</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.099628033944848</v>
+        <v>-4.102245371132005</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.052779907167891</v>
+        <v>1.051732972293028</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6330846743350576</v>
+        <v>0.630467337147899</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.072838349660612</v>
+        <v>3.071267947348317</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.21616963905019</v>
+        <v>-4.218786976237348</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.001238973637477</v>
+        <v>1.000192038762614</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5165430692297148</v>
+        <v>0.5139257320425563</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.997989095109129</v>
+        <v>2.996418692796834</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.256093733632762</v>
+        <v>-4.25871107081992</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9907606316351154</v>
+        <v>0.9897136967602527</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5165430692297148</v>
+        <v>0.5139257320425563</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.003480390939797</v>
+        <v>3.001909988627502</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.283874131534115</v>
+        <v>-4.286491468721272</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9911456742431135</v>
+        <v>0.9900987393682505</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4887626713283617</v>
+        <v>0.4861453341412033</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.998309353967524</v>
+        <v>2.996738951655229</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.402254804264254</v>
+        <v>-4.404872141451411</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7821491251517114</v>
+        <v>0.7811021902768485</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4215448191773855</v>
+        <v>0.4189274819902271</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.796334362677592</v>
+        <v>2.794763960365297</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.510868882707585</v>
+        <v>-4.513486219894742</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8588531544935845</v>
+        <v>0.8578062196187217</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4215448191773855</v>
+        <v>0.4189274819902271</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.916484023396797</v>
+        <v>2.914913621084502</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.475459844459442</v>
+        <v>-4.478077181646599</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8875297958951647</v>
+        <v>0.8864828610203017</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4215448191773855</v>
+        <v>0.4189274819902271</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.93099704949912</v>
+        <v>2.929426647186825</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.437076181901291</v>
+        <v>-4.439693519088448</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9003027022607939</v>
+        <v>0.8992557673859309</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4599284817355367</v>
+        <v>0.4573111445483782</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.95144668837638</v>
+        <v>2.949876286064085</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.259959851866125</v>
+        <v>-4.262577189053282</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9678782631201621</v>
+        <v>0.9668313282452994</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4599284817355367</v>
+        <v>0.4573111445483782</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.948175717221682</v>
+        <v>2.946605314909386</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.30505209669967</v>
+        <v>-4.307669433886828</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.950524756948657</v>
+        <v>0.9494778220737941</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3980324385661469</v>
+        <v>0.3954151013789884</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.911721483081961</v>
+        <v>2.910151080769666</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.125676675460903</v>
+        <v>-4.12829401264806</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.016061900750578</v>
+        <v>1.015014965875715</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5548091967368656</v>
+        <v>0.5521918595497071</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.999574513290806</v>
+        <v>2.998004110978511</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.170690888981509</v>
+        <v>-4.173308226168666</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9788636706739255</v>
+        <v>0.9778167357990626</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.524460301422261</v>
+        <v>0.5218429642351025</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.962172631433633</v>
+        <v>2.960602229121338</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.437695399253944</v>
+        <v>-4.440312736441101</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8777534289038973</v>
+        <v>0.8767064940290343</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3300972633793124</v>
+        <v>0.3274799261921539</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.85124637094681</v>
+        <v>2.849675968634515</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.538893180691117</v>
+        <v>-4.541510517878274</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8364782382255296</v>
+        <v>0.8354313033506666</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2616884498339932</v>
+        <v>0.2590711126468347</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.80940500471612</v>
+        <v>2.807834602403825</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.532382214076804</v>
+        <v>-4.534999551263962</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8366825864255714</v>
+        <v>0.8356356515507084</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2616884498339932</v>
+        <v>0.2590711126468347</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.807004966270437</v>
+        <v>2.805434563958142</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.513344086369507</v>
+        <v>-4.515961423556664</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8408225567167351</v>
+        <v>0.8397756218418724</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2035048385027987</v>
+        <v>0.2008875013156401</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.768619518679965</v>
+        <v>2.76704911636767</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.565859888644328</v>
+        <v>-4.568477225831485</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9391106374409974</v>
+        <v>0.9380637025661345</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2035048385027987</v>
+        <v>0.2008875013156401</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.887913920314155</v>
+        <v>2.88634351800186</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.579726649978245</v>
+        <v>-4.582343987165403</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9343972618935639</v>
+        <v>0.9333503270187009</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1656469217689757</v>
+        <v>0.1630295845818172</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.866032499259995</v>
+        <v>2.8644620969477</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.534922478438316</v>
+        <v>-4.537539815625473</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9583274609064616</v>
+        <v>0.9572805260315989</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1656469217689757</v>
+        <v>0.1630295845818172</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.872041029656921</v>
+        <v>2.870470627344626</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.539051668895209</v>
+        <v>-4.38979684539047</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8546260060009037</v>
+        <v>0.9143279354027993</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2117052213680753</v>
+        <v>0.3308369418167004</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.79762623069358</v>
+        <v>2.869105262962755</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.622872890169908</v>
+        <v>-4.473618066665169</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8238911390225052</v>
+        <v>0.8835930684244009</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2117052213680753</v>
+        <v>0.3308369418167004</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.800419852225061</v>
+        <v>2.871898884494236</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.616720184117123</v>
+        <v>-4.467465360612384</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8270145698352773</v>
+        <v>0.886716499237173</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2178579274208596</v>
+        <v>0.3369896478694847</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.80477382424839</v>
+        <v>2.876252856517565</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.633529482267625</v>
+        <v>-4.484274658762886</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8193713273151868</v>
+        <v>0.8790732567170825</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2010486292703579</v>
+        <v>0.320180349718983</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.793768722098199</v>
+        <v>2.865247754367374</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.571231483491503</v>
+        <v>-4.421976659986764</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9106260806224566</v>
+        <v>0.9703280100243523</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2463428935448</v>
+        <v>0.3654746139934251</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.887280834459685</v>
+        <v>2.95875986672886</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.369441285826345</v>
+        <v>-4.220186462321606</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.793634161402647</v>
+        <v>0.8533360908045426</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4443610857139544</v>
+        <v>0.5634928061625795</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.808383751475305</v>
+        <v>2.87986278374448</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.42032799851254</v>
+        <v>-4.271073175007801</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8435697086503442</v>
+        <v>0.9032716380522399</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.3934743730277598</v>
+        <v>0.512606093476385</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.848141956185763</v>
+        <v>2.919620988454938</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.333717255862733</v>
+        <v>-4.184462432357994</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8928417418263106</v>
+        <v>0.9525436712282063</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.4721001042329181</v>
+        <v>0.5912318246815432</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.909945131024902</v>
+        <v>2.981424163294077</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.393926553868018</v>
+        <v>-4.244671730363279</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8672940034488683</v>
+        <v>0.926995932850764</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.4118908062276336</v>
+        <v>0.5310225266762587</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.872355533046403</v>
+        <v>2.943834565315578</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.317504507436091</v>
+        <v>-4.168249683931352</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8963544400615677</v>
+        <v>0.9560563694634632</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.4118908062276336</v>
+        <v>0.5310225266762587</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.870847151086332</v>
+        <v>2.942326183355507</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.273131375797522</v>
+        <v>-4.123876552292783</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9139665601524314</v>
+        <v>0.9736684895543268</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4562639378662022</v>
+        <v>0.5753956583148273</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.897333897504909</v>
+        <v>2.968812929774084</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.295611726656407</v>
+        <v>-4.146356903151668</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8993682139474679</v>
+        <v>0.9590701433493636</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4562639378662022</v>
+        <v>0.5753956583148273</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.891727691643499</v>
+        <v>2.963206723912675</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.247955996095351</v>
+        <v>-4.098701172590612</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9248122631996949</v>
+        <v>0.9845141926015906</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5039196684272578</v>
+        <v>0.623051388875883</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.926702887007937</v>
+        <v>2.998181919277113</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.147437837596597</v>
+        <v>-3.998183014091858</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9699118999739216</v>
+        <v>1.029613829375817</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6044378269260123</v>
+        <v>0.7235695473746375</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.991906155481915</v>
+        <v>3.06338518775109</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.131532508164244</v>
+        <v>-3.982277684659505</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9630287042227348</v>
+        <v>1.02273063362463</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5253251662167735</v>
+        <v>0.6444568866653986</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.931193231532244</v>
+        <v>3.002672263801419</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.086694106555846</v>
+        <v>-3.937439283051107</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9850617674767228</v>
+        <v>1.044763696878618</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.529868599161643</v>
+        <v>0.6490003196102681</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.938016993909794</v>
+        <v>3.009496026178969</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.106192562797854</v>
+        <v>-3.956937739293115</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9814233246109976</v>
+        <v>1.041125254012893</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4817839578817387</v>
+        <v>0.6009156783303637</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.91332714877293</v>
+        <v>2.984806181042105</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.061989725711953</v>
+        <v>-3.912734902207215</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.004984061973195</v>
+        <v>1.06468599137509</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.5259867949676391</v>
+        <v>0.6451185154162642</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.945728453552307</v>
+        <v>3.017207485821482</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.069549391549</v>
+        <v>-3.920294568044262</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.000370196107624</v>
+        <v>1.060072125509519</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5807901989774584</v>
+        <v>0.6999219194260835</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.977020496427446</v>
+        <v>3.048499528696621</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.911257974009728</v>
+        <v>-3.762003150504989</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.114934528306372</v>
+        <v>1.174636457708268</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5807901989774584</v>
+        <v>0.6999219194260835</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.028268261610486</v>
+        <v>3.099747293879661</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.703615970375251</v>
+        <v>-3.554361146870513</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.196432034354416</v>
+        <v>1.256133963756311</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7884322026119346</v>
+        <v>0.9075639230605597</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.151294168385425</v>
+        <v>3.2227732006546</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.652583877652723</v>
+        <v>-3.503329054147985</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.211793099681697</v>
+        <v>1.271495029083592</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8394642953344625</v>
+        <v>0.9585960157830876</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.176861652257212</v>
+        <v>3.248340684526386</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.587359696525517</v>
+        <v>-3.438104873020779</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.255070176225284</v>
+        <v>1.31477210562718</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9046884764616682</v>
+        <v>1.023820196910293</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.23318356502624</v>
+        <v>3.304662597295415</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.549932676454384</v>
+        <v>-3.400677852949646</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.266001956553018</v>
+        <v>1.325703885954914</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9099400144908498</v>
+        <v>1.029071734939475</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.232295460143029</v>
+        <v>3.303774492412204</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.570044332489092</v>
+        <v>-3.420789508984354</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.259214086470375</v>
+        <v>1.318916015872271</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.920967359488269</v>
+        <v>1.040099079936894</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.240168659472721</v>
+        <v>3.311647691741896</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.541631069389208</v>
+        <v>-3.39237624588447</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.431137162731539</v>
+        <v>1.490839092133435</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8619917967418402</v>
+        <v>0.9811235171904651</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.365341092846074</v>
+        <v>3.436820125115249</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.466848808364196</v>
+        <v>-3.317593984859458</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.581162976359362</v>
+        <v>1.640864905761257</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9367740577668529</v>
+        <v>1.055905778215478</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.530323358678899</v>
+        <v>3.601802390948074</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.440764724100388</v>
+        <v>-3.29150990059565</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.583304586078744</v>
+        <v>1.643006515480639</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9367740577668529</v>
+        <v>1.055905778215478</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.522031334692758</v>
+        <v>3.593510366961933</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.352886810991267</v>
+        <v>-3.203631987486529</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.616648946906172</v>
+        <v>1.676350876308067</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.052699700190204</v>
+        <v>1.171831420638829</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.589779915730548</v>
+        <v>3.661258947999723</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.343994349597984</v>
+        <v>-3.194739526093246</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.637760337190276</v>
+        <v>1.697462266592172</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.052699700190204</v>
+        <v>1.171831420638829</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.60733432145734</v>
+        <v>3.678813353726515</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.512470466567862</v>
+        <v>-3.363215643063123</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.562224937806909</v>
+        <v>1.621926867208805</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.024751864473623</v>
+        <v>1.143883584922248</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.582420667431975</v>
+        <v>3.65389969970115</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.066214273938422</v>
+        <v>-2.916959450433684</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.721997112046547</v>
+        <v>1.781699041448442</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9300331948039906</v>
+        <v>1.049164915252615</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.506859162818058</v>
+        <v>3.578338195087232</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.043493170255269</v>
+        <v>-2.894238346750531</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.721749576016713</v>
+        <v>1.781451505418608</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9300331948039906</v>
+        <v>1.049164915252615</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.497523185314962</v>
+        <v>3.569002217584137</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.172694983549312</v>
+        <v>-3.023440160044573</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.828974976550265</v>
+        <v>1.88867690595216</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8008313815099484</v>
+        <v>0.919963101958573</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.578908223189706</v>
+        <v>3.650387255458881</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.198569382023337</v>
+        <v>-3.049314558518599</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.855703039654301</v>
+        <v>1.915404969056196</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8457429902216895</v>
+        <v>0.9648747106703142</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.642933010910397</v>
+        <v>3.714412043179572</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.191514691808164</v>
+        <v>-3.042259868303426</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.855200271729915</v>
+        <v>1.91490220113181</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8527976804368633</v>
+        <v>0.971929400885488</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.643841181029047</v>
+        <v>3.715320213298221</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.164563467481676</v>
+        <v>-3.015308643976938</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.875986915105252</v>
+        <v>1.935688844507148</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8676780264645825</v>
+        <v>0.9868097469132071</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.66277554229042</v>
+        <v>3.734254574559595</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.209922650219769</v>
+        <v>-3.151261652033254</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.041946374154975</v>
+        <v>2.065410773429581</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8676780264645825</v>
+        <v>0.9868097469132071</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.846878674435379</v>
+        <v>3.918357706704554</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.232330768024641</v>
+        <v>-3.173669769838126</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.025099821936019</v>
+        <v>2.048564221210625</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8676780264645825</v>
+        <v>0.9868097469132071</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.838995369338372</v>
+        <v>3.910474401607547</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.260555003602242</v>
+        <v>-3.201894005415726</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.015864127254616</v>
+        <v>2.039328526529222</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.8856547789158911</v>
+        <v>1.004786499364516</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.851835420358795</v>
+        <v>3.92331445262797</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.269995929490772</v>
+        <v>-3.211334931304256</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.068341474621051</v>
+        <v>2.091805873895658</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.008081896459283</v>
+        <v>1.127213616907907</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.981545408606677</v>
+        <v>4.053024440875852</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.322269536826413</v>
+        <v>-3.263608538639898</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.050323126232096</v>
+        <v>2.073787525506702</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9558082891236414</v>
+        <v>1.074940009572266</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.953072338750593</v>
+        <v>4.024551371019768</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.398599514427319</v>
+        <v>-3.339938516240804</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.017902948085508</v>
+        <v>2.041367347360115</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9558082891236414</v>
+        <v>1.074940009572266</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.951184151644369</v>
+        <v>4.022663183913543</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.600853234751672</v>
+        <v>-3.542192236565157</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.93182168955863</v>
+        <v>1.955286088833236</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7535545687992879</v>
+        <v>0.8726862892479124</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.824652149052619</v>
+        <v>3.896131181321793</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.762421660278927</v>
+        <v>-3.703760662092412</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.86562832955788</v>
+        <v>1.889092728832486</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6267716450014086</v>
+        <v>0.745903365450033</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.747016404984043</v>
+        <v>3.818495437253218</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.870722322149047</v>
+        <v>-3.812061323962531</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.835381471675751</v>
+        <v>1.858845870950357</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6267716450014086</v>
+        <v>0.745903365450033</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.760089811849962</v>
+        <v>3.831568844119137</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.963869793452413</v>
+        <v>-3.905208795265898</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.790127679937344</v>
+        <v>1.81359207921195</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5039424337188758</v>
+        <v>0.6230741541675002</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.678397481863382</v>
+        <v>3.749876514132557</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.991770580561886</v>
+        <v>-3.933109582375371</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.777491406220557</v>
+        <v>1.800955805495163</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.469345509575941</v>
+        <v>0.5884772300245654</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.656163368504624</v>
+        <v>3.727642400773798</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.11429668326478</v>
+        <v>-4.055635685078265</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.725245409116598</v>
+        <v>1.748709808391204</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.3468194068730471</v>
+        <v>0.4659511273216715</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.579412150860086</v>
+        <v>3.65089118312926</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.344811179450369</v>
+        <v>-4.286150181263854</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.699745570232866</v>
+        <v>1.723209969507472</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.1163049106874584</v>
+        <v>0.2354366311360828</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.507809412739237</v>
+        <v>3.579288445008411</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.693556264674813</v>
+        <v>-4.634895266488297</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.700559255144936</v>
+        <v>1.724023654419542</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.007556956768560608</v>
+        <v>0.126688677217185</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.582872359389745</v>
+        <v>3.654351391658919</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.847542682450953</v>
+        <v>-4.788881684264438</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.707944957180119</v>
+        <v>1.731409356454725</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.007556956768560608</v>
+        <v>0.126688677217185</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.651852628535385</v>
+        <v>3.723331660804559</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.797020778623287</v>
+        <v>-4.738359780436772</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.714204920831306</v>
+        <v>1.737669320105913</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.007556956768560608</v>
+        <v>0.126688677217185</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.637903830655505</v>
+        <v>3.70938286292468</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.049495932631012</v>
+        <v>-4.990834934444496</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.625085348283631</v>
+        <v>1.648549747558237</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.007556956768560608</v>
+        <v>0.126688677217185</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.649774319710919</v>
+        <v>3.721253351980094</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.342391689110424</v>
+        <v>-5.283730690923909</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.50913758021081</v>
+        <v>1.532601979485416</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.007556956768560608</v>
+        <v>0.126688677217185</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.650984854229863</v>
+        <v>3.722463886499038</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.529055817245232</v>
+        <v>-5.470394819058717</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.438593671184208</v>
+        <v>1.462058070458814</v>
       </c>
       <c r="F2021" t="n">
-        <v>-0.01918201405599929</v>
+        <v>0.09994970639262513</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.639063213962448</v>
+        <v>3.710542246231623</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.675076504159194</v>
+        <v>-5.616415505972679</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.375263249154812</v>
+        <v>1.398727648429419</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.02826510584985625</v>
+        <v>0.09086661459876816</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.628691211622324</v>
+        <v>3.700170243891499</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.766790513268779</v>
+        <v>-5.708129515082264</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.500781702210022</v>
+        <v>1.524246101484628</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.02826510584985625</v>
+        <v>0.09086661459876816</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.790895268321368</v>
+        <v>3.862374300590543</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.798442172328748</v>
+        <v>-5.739781174142234</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.482967676549849</v>
+        <v>1.506432075824455</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.03343356309429646</v>
+        <v>0.08569815735432795</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.782640831938518</v>
+        <v>3.854119864207692</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.880376990597632</v>
+        <v>-5.821715992411117</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.460423166810787</v>
+        <v>1.483887566085393</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.04336830868137664</v>
+        <v>0.07576341176724777</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.786909402154761</v>
+        <v>3.858388434423936</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.982353112846039</v>
+        <v>-5.923692114659524</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.428558356367326</v>
+        <v>1.452022755641932</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1453444309297842</v>
+        <v>-0.02621271048115981</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.734649367261619</v>
+        <v>3.806128399530794</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.872346829368817</v>
+        <v>-5.813685831182303</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.46471375700239</v>
+        <v>1.488178156276996</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.122139859012509</v>
+        <v>-0.003008138563884599</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.740724997656159</v>
+        <v>3.812204029925334</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.729287253627891</v>
+        <v>-5.670626255441377</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.526187598020735</v>
+        <v>1.549651997295341</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1141264324225297</v>
+        <v>0.005005288026094679</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.749783064332121</v>
+        <v>3.821262096601296</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.427840528156054</v>
+        <v>-5.369179529969539</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.654027171092006</v>
+        <v>1.677491570366612</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1873202930493075</v>
+        <v>0.3064520134979319</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.937911982497759</v>
+        <v>4.009391014766934</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.452430772391238</v>
+        <v>-5.393769774204723</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.645162251150643</v>
+        <v>1.668626650425249</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1873202930493075</v>
+        <v>0.3064520134979319</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.93888316025047</v>
+        <v>4.010362192519644</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.401392396384717</v>
+        <v>-5.342731398198203</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.666420505933007</v>
+        <v>1.689884905207613</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1873202930493075</v>
+        <v>0.3064520134979319</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.939726064630226</v>
+        <v>4.0112050968994</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.360253101518087</v>
+        <v>-5.301592103331572</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.701914322753804</v>
+        <v>1.72537872202841</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2284595879159383</v>
+        <v>0.3475913083645628</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.983447740424349</v>
+        <v>4.054926772693524</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.263618189499446</v>
+        <v>-5.204957191312932</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.556752283685195</v>
+        <v>1.580216682959801</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3250944999345783</v>
+        <v>0.4442262203832027</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.857612683759468</v>
+        <v>3.929091716028643</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.394198924030289</v>
+        <v>-5.335537925843775</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.508022033946822</v>
+        <v>1.531486433221428</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.1945137654037358</v>
+        <v>0.3136454858523602</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.782766287114927</v>
+        <v>3.854245319384102</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.229702589839327</v>
+        <v>-5.171041591652813</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.55824738669929</v>
+        <v>1.581711785973895</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.3590100995946977</v>
+        <v>0.4781418200433221</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.865890906705586</v>
+        <v>3.937369938974761</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.257072522523759</v>
+        <v>-5.198411524337245</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.546487124061946</v>
+        <v>1.569951523336552</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.3590100995946977</v>
+        <v>0.4781418200433221</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.865078617142016</v>
+        <v>3.936557649411191</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.267457717413649</v>
+        <v>-5.208796719227134</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.552201825231063</v>
+        <v>1.575666224505669</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.3486249047048083</v>
+        <v>0.4677566251534327</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.868716279333155</v>
+        <v>3.94019531160233</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.286045876135874</v>
+        <v>-5.227384877949359</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.615603567518598</v>
+        <v>1.639067966793204</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.330036745982583</v>
+        <v>0.4491684664312074</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.928400389876245</v>
+        <v>3.99987942214542</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.28634442283191</v>
+        <v>-5.227683424645395</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.612353159658482</v>
+        <v>1.635817558933088</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.3297381992865471</v>
+        <v>0.4488699197351715</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.925090272676922</v>
+        <v>3.996569304946097</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.185521289141482</v>
+        <v>-5.126860290954967</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.657213308074045</v>
+        <v>1.680677707348651</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.3422024147709009</v>
+        <v>0.4613341352195253</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.937099696906926</v>
+        <v>4.0085787291761</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.994739928389075</v>
+        <v>-4.93607893020256</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.733655105853551</v>
+        <v>1.757119505128157</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.5329837755233082</v>
+        <v>0.6521154959719326</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.051697766836913</v>
+        <v>4.123176799106088</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.976223074347255</v>
+        <v>-4.91756207616074</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.720898693207876</v>
+        <v>1.744363092482481</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5459139049485164</v>
+        <v>0.6650456253971408</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.039292690229635</v>
+        <v>4.11077172249881</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.920892486445492</v>
+        <v>-4.862231488258978</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.777997864980639</v>
+        <v>1.801462264255245</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6012444928502786</v>
+        <v>0.720376213298903</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.10745797958275</v>
+        <v>4.178937011851925</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.908838359532529</v>
+        <v>-4.850177361346015</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.776506083647262</v>
+        <v>1.799970482921868</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6132986197632414</v>
+        <v>0.7324303402118658</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.108377023631966</v>
+        <v>4.179856055901141</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.94999347910075</v>
+        <v>-4.891332480914236</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.761924666004109</v>
+        <v>1.785389065278715</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5721435001950205</v>
+        <v>0.6912752206436449</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.085564582075169</v>
+        <v>4.157043614344344</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.847112889572157</v>
+        <v>-4.788451891385643</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.815927927693429</v>
+        <v>1.839392326968035</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6750240897236134</v>
+        <v>0.7941558101722378</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.160143961670207</v>
+        <v>4.231622993939382</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.078713282741658</v>
+        <v>-5.020052284555144</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.743490440599223</v>
+        <v>1.766954839873829</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6750240897236134</v>
+        <v>0.7941558101722378</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.180346631843801</v>
+        <v>4.251825664112976</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.09678579103327</v>
+        <v>-5.038124792846755</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.736261437282578</v>
+        <v>1.759725836557184</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6750240897236134</v>
+        <v>0.7941558101722378</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.180346631843801</v>
+        <v>4.251825664112976</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.271892623609714</v>
+        <v>-5.2132316254232</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.626470617845467</v>
+        <v>1.649935017120073</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6750240897236134</v>
+        <v>0.7941558101722378</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.140598545437268</v>
+        <v>4.212077577706443</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.240606603069259</v>
+        <v>-5.181945604882745</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.646007645058589</v>
+        <v>1.669472044333195</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7063101102640688</v>
+        <v>0.8254418307126932</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.166392776758482</v>
+        <v>4.237871809027656</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.087581210955975</v>
+        <v>-5.02892021276946</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.806388801476807</v>
+        <v>1.829853200751413</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.8593355023773529</v>
+        <v>0.9784672228259773</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.357379011599356</v>
+        <v>4.428858043868531</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.115888524829245</v>
+        <v>-5.05722752664273</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.982532100835791</v>
+        <v>2.005996500110397</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.8593355023773529</v>
+        <v>0.9784672228259773</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.544845236507649</v>
+        <v>4.616324268776824</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.282481749942767</v>
+        <v>-5.223820751756253</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.885297762144465</v>
+        <v>1.90876216141907</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.6927422772638305</v>
+        <v>0.8118739977124549</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.414292252793618</v>
+        <v>4.485771285062792</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.109417370560467</v>
+        <v>-5.050756372373953</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.958199916559102</v>
+        <v>1.981664315833708</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.6927422772638305</v>
+        <v>0.8118739977124549</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.417968655455335</v>
+        <v>4.48944768772451</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.080171390104771</v>
+        <v>-5.021510391918256</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.967516363864876</v>
+        <v>1.990980763139482</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.6927422772638305</v>
+        <v>0.8118739977124549</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.415586710578831</v>
+        <v>4.487065742848005</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.187096937982622</v>
+        <v>-5.128435939796107</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.922039383871371</v>
+        <v>1.945503783145976</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.5858167293859792</v>
+        <v>0.7049484498346036</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.348724621009755</v>
+        <v>4.42020365327893</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.33211549648987</v>
+        <v>-5.273454498303356</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.865460762611705</v>
+        <v>1.888925161886311</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.4407981708787306</v>
+        <v>0.559929891327355</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.263142288048639</v>
+        <v>4.334621320317814</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.450457262274588</v>
+        <v>-5.391796264088073</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.918055295555571</v>
+        <v>1.941519694830177</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.4514842094416207</v>
+        <v>0.5706159298902451</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.369485150444127</v>
+        <v>4.440964182713302</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.501867684595296</v>
+        <v>-5.443206686408781</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.895276823753227</v>
+        <v>1.918741223027833</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.4514842094416207</v>
+        <v>0.5706159298902451</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.367270847570065</v>
+        <v>4.43874987983924</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.581287135803048</v>
+        <v>-5.522626137616533</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.863412171344416</v>
+        <v>1.886876570619022</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.4514842094416207</v>
+        <v>0.5706159298902451</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.367173975644355</v>
+        <v>4.43865300791353</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.676750133720265</v>
+        <v>-5.618089135533751</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.825220865735572</v>
+        <v>1.848685265010178</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.4514842094416207</v>
+        <v>0.5706159298902451</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.367167869202398</v>
+        <v>4.438646901471573</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.716770131764049</v>
+        <v>-5.658109133577534</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.80730926308067</v>
+        <v>1.830773662355275</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.4114642113978369</v>
+        <v>0.5305959318464613</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.341252266938739</v>
+        <v>4.412731299207914</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.772139293896243</v>
+        <v>-5.713478295709728</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.790895415975519</v>
+        <v>1.814359815250124</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.4114642113978369</v>
+        <v>0.5305959318464613</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.346986084686465</v>
+        <v>4.41846511695564</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.81757707372707</v>
+        <v>-5.758916075540555</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.772258667386121</v>
+        <v>1.795723066660726</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.3686192207196772</v>
+        <v>0.4877509411683016</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.320817453622502</v>
+        <v>4.392296485891677</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.734351616879406</v>
+        <v>-5.675690618692891</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.825423242975506</v>
+        <v>1.848887642250111</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.3686192207196772</v>
+        <v>0.4877509411683016</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.340691846472821</v>
+        <v>4.412170878741996</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.558061392274098</v>
+        <v>-5.499400394087584</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.879640033342356</v>
+        <v>1.903104432616962</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.3686192207196772</v>
+        <v>0.4877509411683016</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.324392546997549</v>
+        <v>4.395871579266724</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.374849729141003</v>
+        <v>-5.316188730954488</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.95535564805964</v>
+        <v>1.978820047334246</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.3686192207196772</v>
+        <v>0.4877509411683016</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.326823496461595</v>
+        <v>4.39830252873077</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.303128282127152</v>
+        <v>-5.244467283940637</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.94983541271307</v>
+        <v>1.973299811987676</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.4403406677335279</v>
+        <v>0.5594723881821522</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.335647550517795</v>
+        <v>4.40712658278697</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,45 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.464538809209484</v>
+        <v>3.723809890676848</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.508374562017834</v>
+        <v>-5.373846066580415</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.814652646677969</v>
+        <v>1.868464044852936</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.3494359513054088</v>
+        <v>0.5173706154749489</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.228020466582095</v>
+        <v>4.328781265083819</v>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" s="2" t="n">
+        <v>45532</v>
+      </c>
+      <c r="B2070" t="n">
+        <v>3.846920940147567</v>
+      </c>
+      <c r="C2070" t="n">
+        <v>4.198191094327704</v>
+      </c>
+      <c r="D2070" t="n">
+        <v>-5.373846066580415</v>
+      </c>
+      <c r="E2070" t="n">
+        <v>1.868464044852936</v>
+      </c>
+      <c r="F2070" t="n">
+        <v>0.5173706154749489</v>
+      </c>
+      <c r="G2070" t="n">
+        <v>4.191254891314072</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240828.xlsx
+++ b/tame_output/ON/bt/strategyON_20240828.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>51.2%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>93.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>107.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.5%</t>
+          <t>-49.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.6%</t>
+          <t>423.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-699.0%</t>
+          <t>-693.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>-34.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-189.4%</t>
+          <t>-187.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-13.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>112.0%</t>
+          <t>120.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-290.1%</t>
+          <t>-286.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-172.3%</t>
+          <t>-166.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-27.3%</t>
         </is>
       </c>
     </row>
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.002246706699946</v>
+        <v>-8.999629369512789</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4227415563160113</v>
+        <v>-0.4216946214411483</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.517432170692126</v>
+        <v>-1.514814833504967</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.268054248262439</v>
+        <v>2.269624650574735</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.908787672714721</v>
+        <v>-8.906170335527564</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.395241424034829</v>
+        <v>-0.394194489159966</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.517432170692126</v>
+        <v>-1.514814833504967</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.258170766949532</v>
+        <v>2.259741169261827</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.89813449116129</v>
+        <v>-8.895517153974133</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.39281471191283</v>
+        <v>-0.3917677770379671</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.517432170692126</v>
+        <v>-1.514814833504967</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.256336206450158</v>
+        <v>2.257906608762453</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.800227452484799</v>
+        <v>-8.797610115297642</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3539522114156948</v>
+        <v>-0.3529052765408318</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.44944642083157</v>
+        <v>-1.446829083644411</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.296827341393031</v>
+        <v>2.298397743705326</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.776273911508842</v>
+        <v>-8.773656574321684</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3437022888798178</v>
+        <v>-0.3426553540049548</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.425492879855612</v>
+        <v>-1.422875542668453</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.311867972124099</v>
+        <v>2.313438374436394</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.512213973186045</v>
+        <v>-8.509596635998887</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2513386297124511</v>
+        <v>-0.2502916948375882</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.161432941532816</v>
+        <v>-1.158815604345657</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.457043618956025</v>
+        <v>2.45861402126832</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.805134349681206</v>
+        <v>-7.802517012494049</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.02870618602918329</v>
+        <v>0.02975312090404625</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.161432941532816</v>
+        <v>-1.158815604345657</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.454256585295724</v>
+        <v>2.455826987608019</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.764950051315016</v>
+        <v>-7.762332714127859</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.04512352926350083</v>
+        <v>0.04617046413836379</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.121248643166625</v>
+        <v>-1.118631305979466</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.47871078820328</v>
+        <v>2.480281190515575</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.601550180375654</v>
+        <v>-7.598932843188496</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1098502988600027</v>
+        <v>0.1108972337348657</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9578487722272624</v>
+        <v>-0.9552314350401039</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.576117531987654</v>
+        <v>2.577687934299949</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.368068958146055</v>
+        <v>-7.365451620958898</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2111672165896943</v>
+        <v>0.2122141514645572</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.7243675499976638</v>
+        <v>-0.7217502128105053</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.724130694163266</v>
+        <v>2.725701096475561</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.21840256713854</v>
+        <v>-7.215785229951383</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2681415626797414</v>
+        <v>0.2691884975546044</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.6314640587551279</v>
+        <v>-0.6288467215679694</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.776980578595828</v>
+        <v>2.778550980908123</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.086127093507653</v>
+        <v>-7.083509756320496</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2223125381392506</v>
+        <v>0.2233594730141135</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4991885851242412</v>
+        <v>-0.4965712479370827</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.757606648781515</v>
+        <v>2.75917705109381</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.930388760947912</v>
+        <v>-6.927771423760754</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2874229318507839</v>
+        <v>0.2884698667256469</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3434502525644997</v>
+        <v>-0.3408329153773412</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.853864709004997</v>
+        <v>2.855435111317292</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.845424094218592</v>
+        <v>-6.842806757031434</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3343151397661708</v>
+        <v>0.3353620746410337</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2584855858351801</v>
+        <v>-0.2558682486480216</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.917749850266247</v>
+        <v>2.919320252578542</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.951014083991696</v>
+        <v>-6.948396746804539</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.1641032142577101</v>
+        <v>0.1651501491325731</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3640755756082845</v>
+        <v>-0.361458238421126</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.726419926803166</v>
+        <v>2.727990329115461</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.882779499366269</v>
+        <v>-6.880162162179111</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2399413899849678</v>
+        <v>0.2409883248598303</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3456602527357485</v>
+        <v>-0.34304291554859</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.786013462403774</v>
+        <v>2.787583864716069</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.734839457958669</v>
+        <v>-6.732222120771512</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1824965979096005</v>
+        <v>0.183543532784463</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3253393368271909</v>
+        <v>-0.3227219996400324</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.681585203310501</v>
+        <v>2.683155605622796</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.681869935704681</v>
+        <v>-6.679252598517524</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1949704205577176</v>
+        <v>0.1960173554325806</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.272369814573202</v>
+        <v>-0.2697524773860435</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.704652930409416</v>
+        <v>2.706223332721711</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.51608173974439</v>
+        <v>-6.513464402557233</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2543250868467406</v>
+        <v>0.2553720217216036</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.272369814573202</v>
+        <v>-0.2697524773860435</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.697692318314323</v>
+        <v>2.699262720626618</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.482718533265621</v>
+        <v>-6.480101196078464</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2821327238193914</v>
+        <v>0.2831796586942543</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.272369814573202</v>
+        <v>-0.2697524773860435</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.712154672695466</v>
+        <v>2.713725075007761</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.3744593961431</v>
+        <v>-6.371842058955942</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3199684991275951</v>
+        <v>0.321015434002458</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.272369814573202</v>
+        <v>-0.2697524773860435</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.706686793154661</v>
+        <v>2.708257195466956</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.251168261325969</v>
+        <v>-6.248550924138812</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3667830470650242</v>
+        <v>0.3678299819398871</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1490786797560715</v>
+        <v>-0.146461342568913</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.778159568055516</v>
+        <v>2.779729970367812</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.198471394194677</v>
+        <v>-6.19585405700752</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3955627721548658</v>
+        <v>0.3966097070297288</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.09638181262478035</v>
+        <v>-0.09376447543762184</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.817478666571616</v>
+        <v>2.819049068883911</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.954705952211233</v>
+        <v>-5.952088615024076</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4888496572952943</v>
+        <v>0.4898965921701572</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.09638181262478035</v>
+        <v>-0.09376447543762184</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.813259374918667</v>
+        <v>2.814829777230962</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.864930279834761</v>
+        <v>-5.862312942647604</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5268842401658991</v>
+        <v>0.527931175040762</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.03478236771047033</v>
+        <v>-0.03216503052331182</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.852343355787269</v>
+        <v>2.853913758099564</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.615079885885686</v>
+        <v>-5.612462548698529</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6195664727292312</v>
+        <v>0.6206134076040941</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.03478236771047033</v>
+        <v>-0.03216503052331182</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.845085430770971</v>
+        <v>2.846655833083266</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.439187793418254</v>
+        <v>-5.436570456231097</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6935224332368528</v>
+        <v>0.6945693681117158</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.03478236771047033</v>
+        <v>-0.03216503052331182</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.84868455429162</v>
+        <v>2.850254956603915</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.267741330395791</v>
+        <v>-5.265123993208634</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7754285245003918</v>
+        <v>0.7764754593752548</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1366640953119928</v>
+        <v>0.1392814324991513</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.964879938159652</v>
+        <v>2.966450340471947</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.18771904328667</v>
+        <v>-5.185101706099513</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8064579169603374</v>
+        <v>0.8075048518351999</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2166863824211138</v>
+        <v>0.2193037196082723</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.011913788041421</v>
+        <v>3.013484190353716</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.124083301052735</v>
+        <v>-5.121465963865578</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8366070149082283</v>
+        <v>0.8376539497830913</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2803221246550483</v>
+        <v>0.2829394618422068</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.054790034436099</v>
+        <v>3.056360436748394</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.03038598283634</v>
+        <v>-5.027768645649183</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8552802009785818</v>
+        <v>0.8563271358534448</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2803221246550483</v>
+        <v>0.2829394618422068</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.035984293219895</v>
+        <v>3.03755469553219</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.040888605901629</v>
+        <v>-5.038271268714472</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8528222283773439</v>
+        <v>0.8538691632522069</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2698195015897594</v>
+        <v>0.2724368387769179</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.031425796005599</v>
+        <v>3.032996198317894</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.968646037730434</v>
+        <v>-4.966028700543277</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.885648569480642</v>
+        <v>0.8866955043555047</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2698195015897594</v>
+        <v>0.2724368387769179</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.035355109840419</v>
+        <v>3.036925512152714</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.950932350852569</v>
+        <v>-4.948315013665412</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8934126281491279</v>
+        <v>0.8944595630239909</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2730008304866762</v>
+        <v>0.2756181676738347</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.037942491095909</v>
+        <v>3.039512893408204</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.842127465372842</v>
+        <v>-4.839510128185685</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9339326535610124</v>
+        <v>0.9349795884358751</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2730008304866762</v>
+        <v>0.2756181676738347</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.034940562315902</v>
+        <v>3.036510964628198</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.622106667335832</v>
+        <v>-4.619489330148674</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.023520009786431</v>
+        <v>1.024566944661293</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4142206755546565</v>
+        <v>0.416838012741815</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.121251506367305</v>
+        <v>3.1228219086796</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.489238978272554</v>
+        <v>-4.486621641085397</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.092561268213565</v>
+        <v>1.093608203088428</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4142206755546565</v>
+        <v>0.416838012741815</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.137145689169128</v>
+        <v>3.138716091481423</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.369065894908055</v>
+        <v>-4.366448557720898</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.141776345999666</v>
+        <v>1.142823280874529</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5343937589191554</v>
+        <v>0.5370110961063139</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.210395383628129</v>
+        <v>3.211965785940424</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.233812533578078</v>
+        <v>-4.231195196390921</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.205965793093097</v>
+        <v>1.20701272796796</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6696471202491325</v>
+        <v>0.672264457436291</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.301635502987555</v>
+        <v>3.30320590529985</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.29368736093577</v>
+        <v>-4.291070023748613</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.168053353551446</v>
+        <v>1.169100288426309</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6097722928914404</v>
+        <v>0.6123896300785989</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.251748097974366</v>
+        <v>3.253318500286661</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.173867130024933</v>
+        <v>-4.171249792837776</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.231270615149989</v>
+        <v>1.232317550024852</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6097722928914404</v>
+        <v>0.6123896300785989</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.267037267208575</v>
+        <v>3.26860766952087</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.176336836486739</v>
+        <v>-4.173719499299582</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.137926931887709</v>
+        <v>1.138973866762571</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6073025864296342</v>
+        <v>0.6099199236167927</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.173199642653932</v>
+        <v>3.174770044966227</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.24470702281075</v>
+        <v>-4.242089685623593</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.029840718843406</v>
+        <v>1.030887653718269</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6165782854658491</v>
+        <v>0.6191956226530076</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.098026923560963</v>
+        <v>3.099597325873258</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.3565793024369</v>
+        <v>-4.353961965249743</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9755285156248368</v>
+        <v>0.9765754504996997</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6165782854658491</v>
+        <v>0.6191956226530076</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.088463632192854</v>
+        <v>3.090034034505149</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.41209937832949</v>
+        <v>-4.409482041142333</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.090351321960003</v>
+        <v>1.091398256834866</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6165782854658491</v>
+        <v>0.6191956226530076</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.225494468885056</v>
+        <v>3.227064871197352</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.23662511853702</v>
+        <v>-4.234007781349863</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.165108257868779</v>
+        <v>1.166155192743642</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6165782854658491</v>
+        <v>0.6191956226530076</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.230061700876844</v>
+        <v>3.231632103189139</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.228700743952106</v>
+        <v>-4.226083406764949</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.144020036463952</v>
+        <v>1.145066971338815</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6165782854658491</v>
+        <v>0.6191956226530076</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.205803729638051</v>
+        <v>3.207374131950346</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.222422541382257</v>
+        <v>-4.2198052041951</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.075069630893341</v>
+        <v>1.076116565768204</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6228564880356982</v>
+        <v>0.6254738252228567</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.13810896458141</v>
+        <v>3.139679366893705</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.162569922178534</v>
+        <v>-4.159952584991377</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.109183065006963</v>
+        <v>1.110229999881826</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6228564880356982</v>
+        <v>0.6254738252228567</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.148281351013543</v>
+        <v>3.149851753325838</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.076326459152156</v>
+        <v>-4.073709121964999</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.138626720791374</v>
+        <v>1.139673655666237</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6228564880356982</v>
+        <v>0.6254738252228567</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.143227621587403</v>
+        <v>3.144798023899698</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.121633278551136</v>
+        <v>-4.119015941363979</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.112279768476308</v>
+        <v>1.113326703351171</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5820463250264674</v>
+        <v>0.5846636622136259</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.11051729922639</v>
+        <v>3.112087701538685</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.150666383253437</v>
+        <v>-4.14804904606628</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.101218399628489</v>
+        <v>1.102265334503352</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5820463250264674</v>
+        <v>0.5846636622136259</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.111069172259492</v>
+        <v>3.112639574571787</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.057855901802577</v>
+        <v>-4.05523856461542</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.067615284100198</v>
+        <v>1.068662218975061</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6748568064773267</v>
+        <v>0.6774741436644852</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.096028153021373</v>
+        <v>3.097598555333668</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.102245371132005</v>
+        <v>-4.099628033944848</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.051732972293028</v>
+        <v>1.052779907167891</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.630467337147899</v>
+        <v>0.6330846743350576</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.071267947348317</v>
+        <v>3.072838349660612</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.218786976237348</v>
+        <v>-4.21616963905019</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.000192038762614</v>
+        <v>1.001238973637477</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5139257320425563</v>
+        <v>0.5165430692297148</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.996418692796834</v>
+        <v>2.997989095109129</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.25871107081992</v>
+        <v>-4.256093733632762</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9897136967602527</v>
+        <v>0.9907606316351154</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5139257320425563</v>
+        <v>0.5165430692297148</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.001909988627502</v>
+        <v>3.003480390939797</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.286491468721272</v>
+        <v>-4.283874131534115</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9900987393682505</v>
+        <v>0.9911456742431135</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4861453341412033</v>
+        <v>0.4887626713283617</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.996738951655229</v>
+        <v>2.998309353967524</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.404872141451411</v>
+        <v>-4.402254804264254</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7811021902768485</v>
+        <v>0.7821491251517114</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4189274819902271</v>
+        <v>0.4215448191773855</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.794763960365297</v>
+        <v>2.796334362677592</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.513486219894742</v>
+        <v>-4.510868882707585</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8578062196187217</v>
+        <v>0.8588531544935845</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4189274819902271</v>
+        <v>0.4215448191773855</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.914913621084502</v>
+        <v>2.916484023396797</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.478077181646599</v>
+        <v>-4.475459844459442</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8864828610203017</v>
+        <v>0.8875297958951647</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4189274819902271</v>
+        <v>0.4215448191773855</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.929426647186825</v>
+        <v>2.93099704949912</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.439693519088448</v>
+        <v>-4.437076181901291</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8992557673859309</v>
+        <v>0.9003027022607939</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4573111445483782</v>
+        <v>0.4599284817355367</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.949876286064085</v>
+        <v>2.95144668837638</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.262577189053282</v>
+        <v>-4.259959851866125</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9668313282452994</v>
+        <v>0.9678782631201621</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4573111445483782</v>
+        <v>0.4599284817355367</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.946605314909386</v>
+        <v>2.948175717221682</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.307669433886828</v>
+        <v>-4.30505209669967</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9494778220737941</v>
+        <v>0.950524756948657</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3954151013789884</v>
+        <v>0.3980324385661469</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.910151080769666</v>
+        <v>2.911721483081961</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.12829401264806</v>
+        <v>-4.125676675460903</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.015014965875715</v>
+        <v>1.016061900750578</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5521918595497071</v>
+        <v>0.5548091967368656</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.998004110978511</v>
+        <v>2.999574513290806</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.173308226168666</v>
+        <v>-4.170690888981509</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9778167357990626</v>
+        <v>0.9788636706739255</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5218429642351025</v>
+        <v>0.524460301422261</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.960602229121338</v>
+        <v>2.962172631433633</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.440312736441101</v>
+        <v>-4.437695399253944</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8767064940290343</v>
+        <v>0.8777534289038973</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3274799261921539</v>
+        <v>0.3300972633793124</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.849675968634515</v>
+        <v>2.85124637094681</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.541510517878274</v>
+        <v>-4.538893180691117</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8354313033506666</v>
+        <v>0.8364782382255296</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2590711126468347</v>
+        <v>0.2616884498339932</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.807834602403825</v>
+        <v>2.80940500471612</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.534999551263962</v>
+        <v>-4.532382214076804</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8356356515507084</v>
+        <v>0.8366825864255714</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2590711126468347</v>
+        <v>0.2616884498339932</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.805434563958142</v>
+        <v>2.807004966270437</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.515961423556664</v>
+        <v>-4.513344086369507</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8397756218418724</v>
+        <v>0.8408225567167351</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2008875013156401</v>
+        <v>0.2035048385027987</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.76704911636767</v>
+        <v>2.768619518679965</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.568477225831485</v>
+        <v>-4.565859888644328</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9380637025661345</v>
+        <v>0.9391106374409974</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2008875013156401</v>
+        <v>0.2035048385027987</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.88634351800186</v>
+        <v>2.887913920314155</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.582343987165403</v>
+        <v>-4.579726649978245</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9333503270187009</v>
+        <v>0.9343972618935639</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1630295845818172</v>
+        <v>0.1656469217689757</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.8644620969477</v>
+        <v>2.866032499259995</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.537539815625473</v>
+        <v>-4.534922478438316</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9572805260315989</v>
+        <v>0.9583274609064616</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1630295845818172</v>
+        <v>0.1656469217689757</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.870470627344626</v>
+        <v>2.872041029656921</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.38979684539047</v>
+        <v>-4.387179508203313</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9143279354027993</v>
+        <v>0.9153748702776623</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3308369418167004</v>
+        <v>0.3334542790038589</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.869105262962755</v>
+        <v>2.87067566527505</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.473618066665169</v>
+        <v>-4.471000729478011</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8835930684244009</v>
+        <v>0.8846400032992638</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3308369418167004</v>
+        <v>0.3334542790038589</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.871898884494236</v>
+        <v>2.873469286806531</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.467465360612384</v>
+        <v>-4.464848023425227</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.886716499237173</v>
+        <v>0.887763434112036</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3369896478694847</v>
+        <v>0.3396069850566432</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.876252856517565</v>
+        <v>2.87782325882986</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.484274658762886</v>
+        <v>-4.481657321575729</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8790732567170825</v>
+        <v>0.8801201915919454</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.320180349718983</v>
+        <v>0.3227976869061415</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.865247754367374</v>
+        <v>2.86681815667967</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.421976659986764</v>
+        <v>-4.419359322799607</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9703280100243523</v>
+        <v>0.9713749448992153</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3654746139934251</v>
+        <v>0.3680919511805836</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.95875986672886</v>
+        <v>2.960330269041155</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.220186462321606</v>
+        <v>-4.217569125134449</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8533360908045426</v>
+        <v>0.8543830256794054</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5634928061625795</v>
+        <v>0.566110143349738</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.87986278374448</v>
+        <v>2.881433186056775</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.271073175007801</v>
+        <v>-4.268455837820643</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9032716380522399</v>
+        <v>0.9043185729271028</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.512606093476385</v>
+        <v>0.5152234306635435</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.919620988454938</v>
+        <v>2.921191390767234</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.184462432357994</v>
+        <v>-4.181845095170837</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9525436712282063</v>
+        <v>0.9535906061030692</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5912318246815432</v>
+        <v>0.5938491618687017</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.981424163294077</v>
+        <v>2.982994565606372</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.244671730363279</v>
+        <v>-4.242054393176121</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.926995932850764</v>
+        <v>0.9280428677256269</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5310225266762587</v>
+        <v>0.5336398638634172</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.943834565315578</v>
+        <v>2.945404967627873</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.168249683931352</v>
+        <v>-4.165632346744195</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9560563694634632</v>
+        <v>0.9571033043383261</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5310225266762587</v>
+        <v>0.5336398638634172</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.942326183355507</v>
+        <v>2.943896585667802</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.123876552292783</v>
+        <v>-4.121259215105626</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9736684895543268</v>
+        <v>0.9747154244291898</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5753956583148273</v>
+        <v>0.5780129955019858</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.968812929774084</v>
+        <v>2.970383332086379</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.146356903151668</v>
+        <v>-4.143739565964511</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9590701433493636</v>
+        <v>0.9601170782242263</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5753956583148273</v>
+        <v>0.5780129955019858</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.963206723912675</v>
+        <v>2.96477712622497</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.098701172590612</v>
+        <v>-4.096083835403455</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9845141926015906</v>
+        <v>0.9855611274764533</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.623051388875883</v>
+        <v>0.6256687260630415</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.998181919277113</v>
+        <v>2.999752321589408</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.998183014091858</v>
+        <v>-3.9955656769047</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.029613829375817</v>
+        <v>1.03066076425068</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7235695473746375</v>
+        <v>0.726186884561796</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.06338518775109</v>
+        <v>3.064955590063385</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.982277684659505</v>
+        <v>-3.979660347472348</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.02273063362463</v>
+        <v>1.023777568499493</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6444568866653986</v>
+        <v>0.6470742238525571</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.002672263801419</v>
+        <v>3.004242666113714</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.937439283051107</v>
+        <v>-3.93482194586395</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.044763696878618</v>
+        <v>1.045810631753481</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6490003196102681</v>
+        <v>0.6516176567974266</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.009496026178969</v>
+        <v>3.011066428491264</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.956937739293115</v>
+        <v>-3.954320402105958</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.041125254012893</v>
+        <v>1.042172188887756</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6009156783303637</v>
+        <v>0.6035330155175223</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.984806181042105</v>
+        <v>2.9863765833544</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.912734902207215</v>
+        <v>-3.910117565020057</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.06468599137509</v>
+        <v>1.065732926249953</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6451185154162642</v>
+        <v>0.6477358526034227</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.017207485821482</v>
+        <v>3.018777888133777</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.920294568044262</v>
+        <v>-3.917677230857104</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.060072125509519</v>
+        <v>1.061119060384382</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6999219194260835</v>
+        <v>0.702539256613242</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.048499528696621</v>
+        <v>3.050069931008916</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.762003150504989</v>
+        <v>-3.759385813317832</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.174636457708268</v>
+        <v>1.17568339258313</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6999219194260835</v>
+        <v>0.702539256613242</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.099747293879661</v>
+        <v>3.101317696191956</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.554361146870513</v>
+        <v>-3.551743809683356</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.256133963756311</v>
+        <v>1.257180898631174</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9075639230605597</v>
+        <v>0.9101812602477182</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.2227732006546</v>
+        <v>3.224343602966895</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.503329054147985</v>
+        <v>-3.500711716960828</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.271495029083592</v>
+        <v>1.272541963958455</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9585960157830876</v>
+        <v>0.9612133529702461</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.248340684526386</v>
+        <v>3.249911086838682</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.438104873020779</v>
+        <v>-3.435487535833622</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.31477210562718</v>
+        <v>1.315819040502042</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.023820196910293</v>
+        <v>1.026437534097452</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.304662597295415</v>
+        <v>3.30623299960771</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.400677852949646</v>
+        <v>-3.398060515762488</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.325703885954914</v>
+        <v>1.326750820829776</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.029071734939475</v>
+        <v>1.031689072126633</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.303774492412204</v>
+        <v>3.305344894724499</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.420789508984354</v>
+        <v>-3.418172171797197</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.318916015872271</v>
+        <v>1.319962950747133</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.040099079936894</v>
+        <v>1.042716417124052</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.311647691741896</v>
+        <v>3.313218094054191</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.39237624588447</v>
+        <v>-3.389758908697313</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.490839092133435</v>
+        <v>1.491886027008298</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9811235171904651</v>
+        <v>0.9837408543776236</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.436820125115249</v>
+        <v>3.438390527427544</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.317593984859458</v>
+        <v>-3.3149766476723</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.640864905761257</v>
+        <v>1.64191184063612</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.055905778215478</v>
+        <v>1.058523115402636</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.601802390948074</v>
+        <v>3.603372793260369</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.29150990059565</v>
+        <v>-3.288892563408492</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.643006515480639</v>
+        <v>1.644053450355502</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.055905778215478</v>
+        <v>1.058523115402636</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.593510366961933</v>
+        <v>3.595080769274228</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.203631987486529</v>
+        <v>-3.201014650299372</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.676350876308067</v>
+        <v>1.67739781118293</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.171831420638829</v>
+        <v>1.174448757825987</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.661258947999723</v>
+        <v>3.662829350312018</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.194739526093246</v>
+        <v>-3.192122188906088</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.697462266592172</v>
+        <v>1.698509201467034</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.171831420638829</v>
+        <v>1.174448757825987</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.678813353726515</v>
+        <v>3.68038375603881</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.363215643063123</v>
+        <v>-3.360598305875966</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.621926867208805</v>
+        <v>1.622973802083667</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.143883584922248</v>
+        <v>1.146500922109406</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.65389969970115</v>
+        <v>3.655470102013445</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.916959450433684</v>
+        <v>-2.914342113246526</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.781699041448442</v>
+        <v>1.782745976323305</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.049164915252615</v>
+        <v>1.051782252439774</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.578338195087232</v>
+        <v>3.579908597399527</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.894238346750531</v>
+        <v>-2.891621009563374</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.781451505418608</v>
+        <v>1.782498440293471</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.049164915252615</v>
+        <v>1.051782252439774</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.569002217584137</v>
+        <v>3.570572619896432</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.023440160044573</v>
+        <v>-3.020822822857416</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.88867690595216</v>
+        <v>1.889723840827023</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.919963101958573</v>
+        <v>0.9225804391457315</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.650387255458881</v>
+        <v>3.651957657771176</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.049314558518599</v>
+        <v>-3.046697221331442</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.915404969056196</v>
+        <v>1.916451903931059</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9648747106703142</v>
+        <v>0.9674920478574727</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.714412043179572</v>
+        <v>3.715982445491867</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.042259868303426</v>
+        <v>-3.039642531116268</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.91490220113181</v>
+        <v>1.915949136006674</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.971929400885488</v>
+        <v>0.9745467380726465</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.715320213298221</v>
+        <v>3.716890615610517</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.015308643976938</v>
+        <v>-3.01269130678978</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.935688844507148</v>
+        <v>1.93673577938201</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9868097469132071</v>
+        <v>0.9894270841003656</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.734254574559595</v>
+        <v>3.735824976871889</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.151261652033254</v>
+        <v>-3.148644314846097</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.065410773429581</v>
+        <v>2.066457708304443</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9868097469132071</v>
+        <v>0.9894270841003656</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.918357706704554</v>
+        <v>3.919928109016849</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.173669769838126</v>
+        <v>-3.171052432650969</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.048564221210625</v>
+        <v>2.049611156085488</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9868097469132071</v>
+        <v>0.9894270841003656</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.910474401607547</v>
+        <v>3.912044803919843</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.201894005415726</v>
+        <v>-3.199276668228569</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.039328526529222</v>
+        <v>2.040375461404085</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.004786499364516</v>
+        <v>1.007403836551674</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.92331445262797</v>
+        <v>3.924884854940265</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.211334931304256</v>
+        <v>-3.208717594117099</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.091805873895658</v>
+        <v>2.09285280877052</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.127213616907907</v>
+        <v>1.129830954095066</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.053024440875852</v>
+        <v>4.054594843188147</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.263608538639898</v>
+        <v>-3.26099120145274</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.073787525506702</v>
+        <v>2.074834460381565</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.074940009572266</v>
+        <v>1.077557346759424</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.024551371019768</v>
+        <v>4.026121773332063</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.339938516240804</v>
+        <v>-3.337321179053646</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.041367347360115</v>
+        <v>2.042414282234978</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.074940009572266</v>
+        <v>1.077557346759424</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.022663183913543</v>
+        <v>4.024233586225838</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.542192236565157</v>
+        <v>-3.539574899378</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.955286088833236</v>
+        <v>1.956333023708098</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8726862892479124</v>
+        <v>0.8753036264350709</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.896131181321793</v>
+        <v>3.897701583634088</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.703760662092412</v>
+        <v>-3.701143324905255</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.889092728832486</v>
+        <v>1.890139663707349</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.745903365450033</v>
+        <v>0.7485207026371915</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.818495437253218</v>
+        <v>3.820065839565513</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.812061323962531</v>
+        <v>-3.809443986775374</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.858845870950357</v>
+        <v>1.85989280582522</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.745903365450033</v>
+        <v>0.7485207026371915</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.831568844119137</v>
+        <v>3.833139246431432</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.905208795265898</v>
+        <v>-3.902591458078741</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.81359207921195</v>
+        <v>1.814639014086813</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6230741541675002</v>
+        <v>0.6256914913546587</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.749876514132557</v>
+        <v>3.751446916444852</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.933109582375371</v>
+        <v>-3.930492245188214</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.800955805495163</v>
+        <v>1.802002740370026</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5884772300245654</v>
+        <v>0.5910945672117239</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.727642400773798</v>
+        <v>3.729212803086093</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.055635685078265</v>
+        <v>-4.053018347891108</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.748709808391204</v>
+        <v>1.749756743266067</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4659511273216715</v>
+        <v>0.4685684645088301</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.65089118312926</v>
+        <v>3.652461585441555</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.286150181263854</v>
+        <v>-4.283532844076697</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.723209969507472</v>
+        <v>1.724256904382335</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2354366311360828</v>
+        <v>0.2380539683232413</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.579288445008411</v>
+        <v>3.580858847320706</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.634895266488297</v>
+        <v>-4.63227792930114</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.724023654419542</v>
+        <v>1.725070589294405</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.126688677217185</v>
+        <v>0.1293060144043435</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.654351391658919</v>
+        <v>3.655921793971214</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.788881684264438</v>
+        <v>-4.786264347077281</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.731409356454725</v>
+        <v>1.732456291329588</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.126688677217185</v>
+        <v>0.1293060144043435</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.723331660804559</v>
+        <v>3.724902063116854</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.738359780436772</v>
+        <v>-4.735742443249615</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.737669320105913</v>
+        <v>1.738716254980776</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.126688677217185</v>
+        <v>0.1293060144043435</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.70938286292468</v>
+        <v>3.710953265236975</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.990834934444496</v>
+        <v>-4.988217597257339</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.648549747558237</v>
+        <v>1.6495966824331</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.126688677217185</v>
+        <v>0.1293060144043435</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.721253351980094</v>
+        <v>3.722823754292389</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.283730690923909</v>
+        <v>-5.281113353736751</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.532601979485416</v>
+        <v>1.533648914360279</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.126688677217185</v>
+        <v>0.1293060144043435</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.722463886499038</v>
+        <v>3.724034288811333</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.470394819058717</v>
+        <v>-5.467777481871559</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.462058070458814</v>
+        <v>1.463105005333677</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.09994970639262513</v>
+        <v>0.1025670435797836</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.710542246231623</v>
+        <v>3.712112648543918</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.616415505972679</v>
+        <v>-5.613798168785522</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.398727648429419</v>
+        <v>1.399774583304281</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.09086661459876816</v>
+        <v>0.09348395178592667</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.700170243891499</v>
+        <v>3.701740646203794</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.708129515082264</v>
+        <v>-5.705512177895107</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.524246101484628</v>
+        <v>1.525293036359491</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.09086661459876816</v>
+        <v>0.09348395178592667</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.862374300590543</v>
+        <v>3.863944702902838</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.739781174142234</v>
+        <v>-5.737163836955077</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.506432075824455</v>
+        <v>1.507479010699317</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.08569815735432795</v>
+        <v>0.08831549454148646</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.854119864207692</v>
+        <v>3.855690266519987</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.821715992411117</v>
+        <v>-5.81909865522396</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.483887566085393</v>
+        <v>1.484934500960255</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.07576341176724777</v>
+        <v>0.07838074895440628</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.858388434423936</v>
+        <v>3.859958836736231</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.923692114659524</v>
+        <v>-5.921074777472367</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.452022755641932</v>
+        <v>1.453069690516795</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.02621271048115981</v>
+        <v>-0.0235953732940013</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.806128399530794</v>
+        <v>3.807698801843089</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.813685831182303</v>
+        <v>-5.811068493995146</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.488178156276996</v>
+        <v>1.489225091151859</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.003008138563884599</v>
+        <v>-0.0003908013767260909</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.812204029925334</v>
+        <v>3.813774432237629</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.670626255441377</v>
+        <v>-5.66800891825422</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.549651997295341</v>
+        <v>1.550698932170204</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.005005288026094679</v>
+        <v>0.007622625213253187</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.821262096601296</v>
+        <v>3.822832498913591</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.369179529969539</v>
+        <v>-5.366562192782382</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.677491570366612</v>
+        <v>1.678538505241475</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3064520134979319</v>
+        <v>0.3090693506850904</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.009391014766934</v>
+        <v>4.010961417079229</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.393769774204723</v>
+        <v>-5.391152437017566</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.668626650425249</v>
+        <v>1.669673585300112</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3064520134979319</v>
+        <v>0.3090693506850904</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.010362192519644</v>
+        <v>4.01193259483194</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.342731398198203</v>
+        <v>-5.340114061011046</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.689884905207613</v>
+        <v>1.690931840082476</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3064520134979319</v>
+        <v>0.3090693506850904</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.0112050968994</v>
+        <v>4.012775499211696</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.301592103331572</v>
+        <v>-5.246429934262996</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.72537872202841</v>
+        <v>1.747443589655841</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3475913083645628</v>
+        <v>0.4027534774331403</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.054926772693524</v>
+        <v>4.088024074134671</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.204957191312932</v>
+        <v>-5.149795022244356</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.580216682959801</v>
+        <v>1.602281550587231</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4442262203832027</v>
+        <v>0.4993883894517802</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.929091716028643</v>
+        <v>3.96218901746979</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.335537925843775</v>
+        <v>-5.280375756775198</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.531486433221428</v>
+        <v>1.553551300848858</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3136454858523602</v>
+        <v>0.3688076549209377</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.854245319384102</v>
+        <v>3.887342620825248</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.171041591652813</v>
+        <v>-5.115879422584237</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.581711785973895</v>
+        <v>1.603776653601326</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4781418200433221</v>
+        <v>0.5333039891118996</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.937369938974761</v>
+        <v>3.970467240415908</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.198411524337245</v>
+        <v>-5.143249355268669</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.569951523336552</v>
+        <v>1.592016390963983</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4781418200433221</v>
+        <v>0.5333039891118996</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.936557649411191</v>
+        <v>3.969654950852338</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.208796719227134</v>
+        <v>-5.153634550158558</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.575666224505669</v>
+        <v>1.597731092133099</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4677566251534327</v>
+        <v>0.5229187942220103</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.94019531160233</v>
+        <v>3.973292613043476</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.227384877949359</v>
+        <v>-5.172222708880783</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.639067966793204</v>
+        <v>1.661132834420635</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4491684664312074</v>
+        <v>0.504330635499785</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.99987942214542</v>
+        <v>4.032976723586566</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.227683424645395</v>
+        <v>-5.172521255576819</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.635817558933088</v>
+        <v>1.657882426560519</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.4488699197351715</v>
+        <v>0.5040320888037491</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.996569304946097</v>
+        <v>4.029666606387243</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.126860290954967</v>
+        <v>-5.071698121886391</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.680677707348651</v>
+        <v>1.702742574976081</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4613341352195253</v>
+        <v>0.5164963042881029</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.0085787291761</v>
+        <v>4.041676030617247</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.93607893020256</v>
+        <v>-4.880916761133983</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.757119505128157</v>
+        <v>1.779184372755588</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6521154959719326</v>
+        <v>0.7072776650405103</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.123176799106088</v>
+        <v>4.156274100547234</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.91756207616074</v>
+        <v>-4.862399907092163</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.744363092482481</v>
+        <v>1.766427960109912</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6650456253971408</v>
+        <v>0.7202077944657185</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.11077172249881</v>
+        <v>4.143869023939956</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.862231488258978</v>
+        <v>-4.807069319190401</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.801462264255245</v>
+        <v>1.823527131882676</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.720376213298903</v>
+        <v>0.7755383823674806</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.178937011851925</v>
+        <v>4.212034313293072</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.850177361346015</v>
+        <v>-4.795015192277438</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.799970482921868</v>
+        <v>1.822035350549299</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7324303402118658</v>
+        <v>0.7875925092804434</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.179856055901141</v>
+        <v>4.212953357342287</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.891332480914236</v>
+        <v>-4.836170311845659</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.785389065278715</v>
+        <v>1.807453932906146</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6912752206436449</v>
+        <v>0.7464373897122225</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.157043614344344</v>
+        <v>4.190140915785491</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.788451891385643</v>
+        <v>-4.733289722317066</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.839392326968035</v>
+        <v>1.861457194595466</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7941558101722378</v>
+        <v>0.8493179792408154</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.231622993939382</v>
+        <v>4.264720295380529</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.020052284555144</v>
+        <v>-4.964890115486567</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.766954839873829</v>
+        <v>1.789019707501259</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7941558101722378</v>
+        <v>0.8493179792408154</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.251825664112976</v>
+        <v>4.284922965554123</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.038124792846755</v>
+        <v>-4.982962623778178</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.759725836557184</v>
+        <v>1.781790704184615</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7941558101722378</v>
+        <v>0.8493179792408154</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.251825664112976</v>
+        <v>4.284922965554123</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.2132316254232</v>
+        <v>-5.158069456354623</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.649935017120073</v>
+        <v>1.671999884747504</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7941558101722378</v>
+        <v>0.8493179792408154</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.212077577706443</v>
+        <v>4.24517487914759</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.181945604882745</v>
+        <v>-5.126783435814168</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.669472044333195</v>
+        <v>1.691536911960626</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8254418307126932</v>
+        <v>0.8806039997812708</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.237871809027656</v>
+        <v>4.270969110468803</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.02892021276946</v>
+        <v>-4.973758043700883</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.829853200751413</v>
+        <v>1.851918068378844</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9784672228259773</v>
+        <v>1.033629391894555</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.428858043868531</v>
+        <v>4.461955345309677</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.05722752664273</v>
+        <v>-5.002065357574153</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.005996500110397</v>
+        <v>2.028061367737828</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9784672228259773</v>
+        <v>1.033629391894555</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.616324268776824</v>
+        <v>4.64942157021797</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.223820751756253</v>
+        <v>-5.168658582687676</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.90876216141907</v>
+        <v>1.930827029046501</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8118739977124549</v>
+        <v>0.8670361667810325</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.485771285062792</v>
+        <v>4.518868586503938</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.050756372373953</v>
+        <v>-4.995594203305376</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.981664315833708</v>
+        <v>2.003729183461139</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8118739977124549</v>
+        <v>0.8670361667810325</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.48944768772451</v>
+        <v>4.522544989165656</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.021510391918256</v>
+        <v>-4.966348222849679</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.990980763139482</v>
+        <v>2.013045630766913</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8118739977124549</v>
+        <v>0.8670361667810325</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.487065742848005</v>
+        <v>4.520163044289151</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.128435939796107</v>
+        <v>-5.07327377072753</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.945503783145976</v>
+        <v>1.967568650773408</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7049484498346036</v>
+        <v>0.7601106189031811</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.42020365327893</v>
+        <v>4.453300954720076</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.273454498303356</v>
+        <v>-5.218292329234779</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.888925161886311</v>
+        <v>1.910990029513742</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.559929891327355</v>
+        <v>0.6150920603959326</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.334621320317814</v>
+        <v>4.367718621758961</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.391796264088073</v>
+        <v>-5.336634095019496</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.941519694830177</v>
+        <v>1.963584562457608</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5706159298902451</v>
+        <v>0.6257780989588226</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.440964182713302</v>
+        <v>4.474061484154448</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.443206686408781</v>
+        <v>-5.388044517340204</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.918741223027833</v>
+        <v>1.940806090655264</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5706159298902451</v>
+        <v>0.6257780989588226</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.43874987983924</v>
+        <v>4.471847181280387</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.522626137616533</v>
+        <v>-5.467463968547956</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.886876570619022</v>
+        <v>1.908941438246452</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5706159298902451</v>
+        <v>0.6257780989588226</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.43865300791353</v>
+        <v>4.471750309354676</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.618089135533751</v>
+        <v>-5.562926966465174</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.848685265010178</v>
+        <v>1.870750132637609</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5706159298902451</v>
+        <v>0.6257780989588226</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.438646901471573</v>
+        <v>4.47174420291272</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.658109133577534</v>
+        <v>-5.602946964508957</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.830773662355275</v>
+        <v>1.852838529982706</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.5305959318464613</v>
+        <v>0.5857581009150388</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.412731299207914</v>
+        <v>4.44582860064906</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.713478295709728</v>
+        <v>-5.658316126641151</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.814359815250124</v>
+        <v>1.836424682877555</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.5305959318464613</v>
+        <v>0.5857581009150388</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.41846511695564</v>
+        <v>4.451562418396787</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.758916075540555</v>
+        <v>-5.703753906471978</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.795723066660726</v>
+        <v>1.817787934288158</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.4877509411683016</v>
+        <v>0.5429131102368792</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.392296485891677</v>
+        <v>4.425393787332824</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.675690618692891</v>
+        <v>-5.620528449624314</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.848887642250111</v>
+        <v>1.870952509877542</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.4877509411683016</v>
+        <v>0.5429131102368792</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.412170878741996</v>
+        <v>4.445268180183143</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.499400394087584</v>
+        <v>-5.444238225019006</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.903104432616962</v>
+        <v>1.925169300244393</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.4877509411683016</v>
+        <v>0.5429131102368792</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.395871579266724</v>
+        <v>4.42896888070787</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.316188730954488</v>
+        <v>-5.261026561885911</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.978820047334246</v>
+        <v>2.000884914961677</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.4877509411683016</v>
+        <v>0.5429131102368792</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.39830252873077</v>
+        <v>4.431399830171916</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.244467283940637</v>
+        <v>-5.18930511487206</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.973299811987676</v>
+        <v>1.995364679615106</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.5594723881821522</v>
+        <v>0.6146345572507298</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.40712658278697</v>
+        <v>4.440223884228116</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.373846066580415</v>
+        <v>-5.318683897511838</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.868464044852936</v>
+        <v>1.890528912480367</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.5173706154749489</v>
+        <v>0.5725327845435264</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.328781265083819</v>
+        <v>4.361878566524966</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.846920940147567</v>
+        <v>3.792484517339273</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.198191094327704</v>
+        <v>4.194155739725979</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.373846066580415</v>
+        <v>-5.318683897511838</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.868464044852936</v>
+        <v>1.890528912480367</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5173706154749489</v>
+        <v>0.5725327845435264</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.191254891314072</v>
+        <v>4.187219536712346</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240828.xlsx
+++ b/tame_output/ON/bt/strategyON_20240828.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>58.2%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>93.3%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>107.2%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-49.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-76.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.5%</t>
+          <t>423.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-693.4%</t>
+          <t>-691.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.8%</t>
+          <t>-35.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-187.2%</t>
+          <t>-186.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.9%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>120.0%</t>
+          <t>119.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-286.9%</t>
+          <t>-291.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-166.7%</t>
+          <t>-172.0%</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-27.9%</t>
         </is>
       </c>
     </row>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199279</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969587</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923079</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770576</v>
+        <v>3.676841549770577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615279</v>
+        <v>3.68516138161528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812099</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646213</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611564</v>
+        <v>3.768951674611565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955324</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.895517153974133</v>
+        <v>-8.821538451800169</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3917677770379671</v>
+        <v>-0.3621762961683817</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.514814833504967</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311945</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.797610115297642</v>
+        <v>-8.723631413123679</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3529052765408318</v>
+        <v>-0.3233137956712464</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.446829083644411</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409724</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.773656574321684</v>
+        <v>-8.699677872147721</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3426553540049548</v>
+        <v>-0.3130638731353694</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.422875542668453</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.509596635998887</v>
+        <v>-8.435617933824924</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2502916948375882</v>
+        <v>-0.2207002139680028</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.158815604345657</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839721</v>
+        <v>3.83325274783972</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.802517012494049</v>
+        <v>-7.728538310320086</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.02975312090404625</v>
+        <v>0.05934460177363166</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.158815604345657</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.762332714127859</v>
+        <v>-7.688354011953895</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.04617046413836379</v>
+        <v>0.07576194500794919</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.118631305979466</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.598932843188496</v>
+        <v>-7.524954141014533</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1108972337348657</v>
+        <v>0.1404887146044511</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.9552314350401039</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.365451620958898</v>
+        <v>-7.291472918784934</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2122141514645572</v>
+        <v>0.2418056323341427</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.7217502128105053</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.215785229951383</v>
+        <v>-7.141806527777419</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2691884975546044</v>
+        <v>0.2987799784241898</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.6288467215679694</v>
@@ -45366,10 +45366,10 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.083509756320496</v>
+        <v>-7.009531054146533</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2233594730141135</v>
+        <v>0.2529509538836989</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.4965712479370827</v>
@@ -45389,10 +45389,10 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.927771423760754</v>
+        <v>-6.853792721586791</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2884698667256469</v>
+        <v>0.3180613475952323</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.3408329153773412</v>
@@ -45412,10 +45412,10 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.842806757031434</v>
+        <v>-6.768828054857471</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3353620746410337</v>
+        <v>0.3649535555106191</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.2558682486480216</v>
@@ -45435,10 +45435,10 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.948396746804539</v>
+        <v>-6.874418044630575</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.1651501491325731</v>
+        <v>0.1947416300021585</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.361458238421126</v>
@@ -45458,10 +45458,10 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.880162162179111</v>
+        <v>-6.806183460005148</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2409883248598303</v>
+        <v>0.2705798057294162</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.34304291554859</v>
@@ -45481,10 +45481,10 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.732222120771512</v>
+        <v>-6.658243418597548</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.183543532784463</v>
+        <v>0.2131350136540489</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.3227219996400324</v>
@@ -45504,10 +45504,10 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.679252598517524</v>
+        <v>-6.60527389634356</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.1960173554325806</v>
+        <v>0.225608836302166</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.2697524773860435</v>
@@ -45527,10 +45527,10 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.513464402557233</v>
+        <v>-6.439485700383269</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2553720217216036</v>
+        <v>0.284963502591189</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.2697524773860435</v>
@@ -45550,10 +45550,10 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.480101196078464</v>
+        <v>-6.4061224939045</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.2831796586942543</v>
+        <v>0.3127711395638397</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.2697524773860435</v>
@@ -45573,10 +45573,10 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.371842058955942</v>
+        <v>-6.297863356781979</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.321015434002458</v>
+        <v>0.3506069148720434</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.2697524773860435</v>
@@ -45596,10 +45596,10 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.248550924138812</v>
+        <v>-6.174572221964848</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3678299819398871</v>
+        <v>0.3974214628094725</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.146461342568913</v>
@@ -45619,10 +45619,10 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.19585405700752</v>
+        <v>-6.121875354833556</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.3966097070297288</v>
+        <v>0.4262011878993142</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.09376447543762184</v>
@@ -45642,10 +45642,10 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.952088615024076</v>
+        <v>-5.878109912850112</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.4898965921701572</v>
+        <v>0.5194880730397426</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.09376447543762184</v>
@@ -45665,10 +45665,10 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.862312942647604</v>
+        <v>-5.78833424047364</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.527931175040762</v>
+        <v>0.5575226559103474</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.03216503052331182</v>
@@ -45688,10 +45688,10 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.612462548698529</v>
+        <v>-5.538483846524565</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6206134076040941</v>
+        <v>0.6502048884736795</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.03216503052331182</v>
@@ -45711,10 +45711,10 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.436570456231097</v>
+        <v>-5.362591754057133</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.6945693681117158</v>
+        <v>0.7241608489813012</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.03216503052331182</v>
@@ -45734,10 +45734,10 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.265123993208634</v>
+        <v>-5.19114529103467</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.7764754593752548</v>
+        <v>0.8060669402448402</v>
       </c>
       <c r="F1921" t="n">
         <v>0.1392814324991513</v>
@@ -45757,10 +45757,10 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.185101706099513</v>
+        <v>-5.111123003925549</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8075048518351999</v>
+        <v>0.8370963327047858</v>
       </c>
       <c r="F1922" t="n">
         <v>0.2193037196082723</v>
@@ -45780,10 +45780,10 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.121465963865578</v>
+        <v>-5.047487261691614</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8376539497830913</v>
+        <v>0.8672454306526767</v>
       </c>
       <c r="F1923" t="n">
         <v>0.2829394618422068</v>
@@ -45803,10 +45803,10 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.027768645649183</v>
+        <v>-4.953789943475219</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8563271358534448</v>
+        <v>0.8859186167230304</v>
       </c>
       <c r="F1924" t="n">
         <v>0.2829394618422068</v>
@@ -45826,10 +45826,10 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.038271268714472</v>
+        <v>-4.964292566540508</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8538691632522069</v>
+        <v>0.8834606441217923</v>
       </c>
       <c r="F1925" t="n">
         <v>0.2724368387769179</v>
@@ -45849,10 +45849,10 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.966028700543277</v>
+        <v>-4.892049998369314</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8866955043555047</v>
+        <v>0.9162869852250903</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2724368387769179</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.82232699787996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.948315013665412</v>
+        <v>-4.874336311491448</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8944595630239909</v>
+        <v>0.9240510438935763</v>
       </c>
       <c r="F1927" t="n">
         <v>0.2756181676738347</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.839510128185685</v>
+        <v>-4.765531426011721</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9349795884358751</v>
+        <v>0.9645710693054608</v>
       </c>
       <c r="F1928" t="n">
         <v>0.2756181676738347</v>
@@ -45918,10 +45918,10 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.619489330148674</v>
+        <v>-4.545510627974711</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.024566944661293</v>
+        <v>1.054158425530879</v>
       </c>
       <c r="F1929" t="n">
         <v>0.416838012741815</v>
@@ -45941,10 +45941,10 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.486621641085397</v>
+        <v>-4.412642938911433</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.093608203088428</v>
+        <v>1.123199683958013</v>
       </c>
       <c r="F1930" t="n">
         <v>0.416838012741815</v>
@@ -45964,10 +45964,10 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.366448557720898</v>
+        <v>-4.292469855546934</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.142823280874529</v>
+        <v>1.172414761744115</v>
       </c>
       <c r="F1931" t="n">
         <v>0.5370110961063139</v>
@@ -45987,10 +45987,10 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.231195196390921</v>
+        <v>-4.157216494216957</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.20701272796796</v>
+        <v>1.236604208837546</v>
       </c>
       <c r="F1932" t="n">
         <v>0.672264457436291</v>
@@ -46010,10 +46010,10 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.291070023748613</v>
+        <v>-4.217091321574649</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.169100288426309</v>
+        <v>1.198691769295894</v>
       </c>
       <c r="F1933" t="n">
         <v>0.6123896300785989</v>
@@ -46033,10 +46033,10 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.171249792837776</v>
+        <v>-4.097271090663813</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.232317550024852</v>
+        <v>1.261909030894438</v>
       </c>
       <c r="F1934" t="n">
         <v>0.6123896300785989</v>
@@ -46056,10 +46056,10 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.173719499299582</v>
+        <v>-4.099740797125619</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.138973866762571</v>
+        <v>1.168565347632157</v>
       </c>
       <c r="F1935" t="n">
         <v>0.6099199236167927</v>
@@ -46079,10 +46079,10 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.242089685623593</v>
+        <v>-4.168110983449629</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.030887653718269</v>
+        <v>1.060479134587854</v>
       </c>
       <c r="F1936" t="n">
         <v>0.6191956226530076</v>
@@ -46102,10 +46102,10 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.353961965249743</v>
+        <v>-4.279983263075779</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9765754504996997</v>
+        <v>1.006166931369285</v>
       </c>
       <c r="F1937" t="n">
         <v>0.6191956226530076</v>
@@ -46125,10 +46125,10 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.409482041142333</v>
+        <v>-4.335503338968369</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.091398256834866</v>
+        <v>1.120989737704452</v>
       </c>
       <c r="F1938" t="n">
         <v>0.6191956226530076</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.234007781349863</v>
+        <v>-4.160029079175899</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.166155192743642</v>
+        <v>1.195746673613227</v>
       </c>
       <c r="F1939" t="n">
         <v>0.6191956226530076</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.226083406764949</v>
+        <v>-4.152104704590985</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.145066971338815</v>
+        <v>1.1746584522084</v>
       </c>
       <c r="F1940" t="n">
         <v>0.6191956226530076</v>
@@ -46194,10 +46194,10 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.2198052041951</v>
+        <v>-4.145826502021136</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.076116565768204</v>
+        <v>1.10570804663779</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6254738252228567</v>
@@ -46217,10 +46217,10 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.159952584991377</v>
+        <v>-4.085973882817413</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.110229999881826</v>
+        <v>1.139821480751411</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6254738252228567</v>
@@ -46240,10 +46240,10 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.073709121964999</v>
+        <v>-3.999730419791035</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.139673655666237</v>
+        <v>1.169265136535822</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6254738252228567</v>
@@ -46263,10 +46263,10 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.119015941363979</v>
+        <v>-4.045037239190015</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.113326703351171</v>
+        <v>1.142918184220756</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5846636622136259</v>
@@ -46286,10 +46286,10 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.14804904606628</v>
+        <v>-4.074070343892316</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.102265334503352</v>
+        <v>1.131856815372937</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5846636622136259</v>
@@ -46309,10 +46309,10 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.05523856461542</v>
+        <v>-3.981259862441457</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.068662218975061</v>
+        <v>1.098253699844647</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6774741436644852</v>
@@ -46332,10 +46332,10 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.099628033944848</v>
+        <v>-4.025649331770885</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.052779907167891</v>
+        <v>1.082371388037476</v>
       </c>
       <c r="F1947" t="n">
         <v>0.6330846743350576</v>
@@ -46355,10 +46355,10 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.21616963905019</v>
+        <v>-4.142190936876228</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.001238973637477</v>
+        <v>1.030830454507062</v>
       </c>
       <c r="F1948" t="n">
         <v>0.5165430692297148</v>
@@ -46378,10 +46378,10 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.256093733632762</v>
+        <v>-4.1821150314588</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9907606316351154</v>
+        <v>1.020352112504701</v>
       </c>
       <c r="F1949" t="n">
         <v>0.5165430692297148</v>
@@ -46401,10 +46401,10 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.283874131534115</v>
+        <v>-4.209895429360152</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9911456742431135</v>
+        <v>1.020737155112699</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4887626713283617</v>
@@ -46424,10 +46424,10 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.402254804264254</v>
+        <v>-4.328276102090291</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7821491251517114</v>
+        <v>0.8117406060212966</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4215448191773855</v>
@@ -46447,10 +46447,10 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.510868882707585</v>
+        <v>-4.436890180533622</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8588531544935845</v>
+        <v>0.8884446353631696</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4215448191773855</v>
@@ -46470,10 +46470,10 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.475459844459442</v>
+        <v>-4.401481142285479</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8875297958951647</v>
+        <v>0.9171212767647499</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4215448191773855</v>
@@ -46493,10 +46493,10 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.437076181901291</v>
+        <v>-4.363097479727328</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9003027022607939</v>
+        <v>0.9298941831303789</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4599284817355367</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.259959851866125</v>
+        <v>-4.185981149692162</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9678782631201621</v>
+        <v>0.9974697439897473</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4599284817355367</v>
@@ -46539,10 +46539,10 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.30505209669967</v>
+        <v>-4.231073394525708</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.950524756948657</v>
+        <v>0.9801162378182422</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3980324385661469</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011232</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.125676675460903</v>
+        <v>-4.05169797328694</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.016061900750578</v>
+        <v>1.045653381620164</v>
       </c>
       <c r="F1957" t="n">
         <v>0.5548091967368656</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982225</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.170690888981509</v>
+        <v>-4.096712186807546</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9788636706739255</v>
+        <v>1.008455151543511</v>
       </c>
       <c r="F1958" t="n">
         <v>0.524460301422261</v>
@@ -46608,10 +46608,10 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.437695399253944</v>
+        <v>-4.363716697079981</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8777534289038973</v>
+        <v>0.9073449097734827</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3300972633793124</v>
@@ -46631,10 +46631,10 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.538893180691117</v>
+        <v>-4.464914478517153</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8364782382255296</v>
+        <v>0.866069719095115</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2616884498339932</v>
@@ -46654,10 +46654,10 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.532382214076804</v>
+        <v>-4.458403511902841</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8366825864255714</v>
+        <v>0.8662740672951568</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2616884498339932</v>
@@ -46677,10 +46677,10 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.513344086369507</v>
+        <v>-4.439365384195543</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8408225567167351</v>
+        <v>0.8704140375863207</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2035048385027987</v>
@@ -46700,10 +46700,10 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.565859888644328</v>
+        <v>-4.491881186470364</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9391106374409974</v>
+        <v>0.9687021183105828</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2035048385027987</v>
@@ -46723,10 +46723,10 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.579726649978245</v>
+        <v>-4.505747947804282</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9343972618935639</v>
+        <v>0.9639887427631493</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1656469217689757</v>
@@ -46746,10 +46746,10 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.534922478438316</v>
+        <v>-4.460943776264352</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9583274609064616</v>
+        <v>0.9879189417760472</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1656469217689757</v>
@@ -46769,10 +46769,10 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.387179508203313</v>
+        <v>-4.313200806029349</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9153748702776623</v>
+        <v>0.9449663511472477</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3334542790038589</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.471000729478011</v>
+        <v>-4.397022027304048</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8846400032992638</v>
+        <v>0.9142314841688493</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3334542790038589</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.464848023425227</v>
+        <v>-4.390869321251263</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.887763434112036</v>
+        <v>0.9173549149816214</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3396069850566432</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.481657321575729</v>
+        <v>-4.407678619401765</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.8801201915919454</v>
+        <v>0.9097116724615308</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3227976869061415</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798423</v>
+        <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.419359322799607</v>
+        <v>-4.345380620625643</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9713749448992153</v>
+        <v>1.000966425768801</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3680919511805836</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.217569125134449</v>
+        <v>-4.143590422960485</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8543830256794054</v>
+        <v>0.883974506548991</v>
       </c>
       <c r="F1971" t="n">
         <v>0.566110143349738</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.268455837820643</v>
+        <v>-4.19447713564668</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9043185729271028</v>
+        <v>0.9339100537966882</v>
       </c>
       <c r="F1972" t="n">
         <v>0.5152234306635435</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.181845095170837</v>
+        <v>-4.107866392996873</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9535906061030692</v>
+        <v>0.9831820869726546</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5938491618687017</v>
@@ -46953,10 +46953,10 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.242054393176121</v>
+        <v>-4.168075691002158</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9280428677256269</v>
+        <v>0.9576343485952123</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5336398638634172</v>
@@ -46976,10 +46976,10 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.165632346744195</v>
+        <v>-4.091653644570231</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9571033043383261</v>
+        <v>0.9866947852079115</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5336398638634172</v>
@@ -46999,10 +46999,10 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.121259215105626</v>
+        <v>-4.047280512931662</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9747154244291898</v>
+        <v>1.004306905298775</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5780129955019858</v>
@@ -47022,10 +47022,10 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.143739565964511</v>
+        <v>-4.069760863790547</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9601170782242263</v>
+        <v>0.9897085590938119</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5780129955019858</v>
@@ -47045,10 +47045,10 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.096083835403455</v>
+        <v>-4.022105133229491</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9855611274764533</v>
+        <v>1.015152608346039</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6256687260630415</v>
@@ -47068,10 +47068,10 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.9955656769047</v>
+        <v>-3.921586974730737</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.03066076425068</v>
+        <v>1.060252245120266</v>
       </c>
       <c r="F1979" t="n">
         <v>0.726186884561796</v>
@@ -47091,10 +47091,10 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.979660347472348</v>
+        <v>-3.905681645298384</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.023777568499493</v>
+        <v>1.053369049369079</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6470742238525571</v>
@@ -47114,10 +47114,10 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.93482194586395</v>
+        <v>-3.860843243689986</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.045810631753481</v>
+        <v>1.075402112623067</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6516176567974266</v>
@@ -47137,10 +47137,10 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.954320402105958</v>
+        <v>-3.880341699931994</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.042172188887756</v>
+        <v>1.071763669757341</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6035330155175223</v>
@@ -47160,10 +47160,10 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.910117565020057</v>
+        <v>-3.836138862846094</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.065732926249953</v>
+        <v>1.095324407119539</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6477358526034227</v>
@@ -47183,10 +47183,10 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.917677230857104</v>
+        <v>-3.843698528683141</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.061119060384382</v>
+        <v>1.090710541253967</v>
       </c>
       <c r="F1984" t="n">
         <v>0.702539256613242</v>
@@ -47206,10 +47206,10 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.759385813317832</v>
+        <v>-3.685407111143868</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.17568339258313</v>
+        <v>1.205274873452716</v>
       </c>
       <c r="F1985" t="n">
         <v>0.702539256613242</v>
@@ -47229,10 +47229,10 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.551743809683356</v>
+        <v>-3.477765107509392</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.257180898631174</v>
+        <v>1.28677237950076</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9101812602477182</v>
@@ -47252,10 +47252,10 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.500711716960828</v>
+        <v>-3.426733014786864</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.272541963958455</v>
+        <v>1.302133444828041</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9612133529702461</v>
@@ -47275,10 +47275,10 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.435487535833622</v>
+        <v>-3.361508833659658</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.315819040502042</v>
+        <v>1.345410521371628</v>
       </c>
       <c r="F1988" t="n">
         <v>1.026437534097452</v>
@@ -47298,10 +47298,10 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.398060515762488</v>
+        <v>-3.324081813588525</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.326750820829776</v>
+        <v>1.356342301699362</v>
       </c>
       <c r="F1989" t="n">
         <v>1.031689072126633</v>
@@ -47321,10 +47321,10 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.418172171797197</v>
+        <v>-3.344193469623233</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.319962950747133</v>
+        <v>1.349554431616719</v>
       </c>
       <c r="F1990" t="n">
         <v>1.042716417124052</v>
@@ -47344,10 +47344,10 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.389758908697313</v>
+        <v>-3.315780206523349</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.491886027008298</v>
+        <v>1.521477507877883</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9837408543776236</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.3149766476723</v>
+        <v>-3.240997945498337</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.64191184063612</v>
+        <v>1.671503321505705</v>
       </c>
       <c r="F1992" t="n">
         <v>1.058523115402636</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.288892563408492</v>
+        <v>-3.214913861234529</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.644053450355502</v>
+        <v>1.673644931225088</v>
       </c>
       <c r="F1993" t="n">
         <v>1.058523115402636</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.201014650299372</v>
+        <v>-3.127035948125408</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.67739781118293</v>
+        <v>1.706989292052515</v>
       </c>
       <c r="F1994" t="n">
         <v>1.174448757825987</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.192122188906088</v>
+        <v>-3.118143486732125</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.698509201467034</v>
+        <v>1.72810068233662</v>
       </c>
       <c r="F1995" t="n">
         <v>1.174448757825987</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945361</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.360598305875966</v>
+        <v>-3.286619603702003</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.622973802083667</v>
+        <v>1.652565282953253</v>
       </c>
       <c r="F1996" t="n">
         <v>1.146500922109406</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.914342113246526</v>
+        <v>-2.840363411072563</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.782745976323305</v>
+        <v>1.812337457192891</v>
       </c>
       <c r="F1997" t="n">
         <v>1.051782252439774</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.891621009563374</v>
+        <v>-2.820922554694706</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.782498440293471</v>
+        <v>1.810777822240938</v>
       </c>
       <c r="F1998" t="n">
         <v>1.051782252439774</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.020822822857416</v>
+        <v>-2.950124367988748</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.889723840827023</v>
+        <v>1.91800322277449</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9225804391457315</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.046697221331442</v>
+        <v>-2.975998766462774</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.916451903931059</v>
+        <v>1.944731285878526</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9674920478574727</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.039642531116268</v>
+        <v>-2.9689440762476</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.915949136006674</v>
+        <v>1.944228517954141</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9745467380726465</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.01269130678978</v>
+        <v>-2.941992851921112</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.93673577938201</v>
+        <v>1.965015161329478</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9894270841003656</v>
@@ -47620,10 +47620,10 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.148644314846097</v>
+        <v>-3.077945859977429</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.066457708304443</v>
+        <v>2.094737090251911</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9894270841003656</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.171052432650969</v>
+        <v>-3.100353977782301</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.049611156085488</v>
+        <v>2.077890538032955</v>
       </c>
       <c r="F2004" t="n">
         <v>0.9894270841003656</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.199276668228569</v>
+        <v>-3.128578213359901</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.040375461404085</v>
+        <v>2.068654843351553</v>
       </c>
       <c r="F2005" t="n">
         <v>1.007403836551674</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.208717594117099</v>
+        <v>-3.138019139248431</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.09285280877052</v>
+        <v>2.121132190717987</v>
       </c>
       <c r="F2006" t="n">
         <v>1.129830954095066</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.26099120145274</v>
+        <v>-3.190292746584072</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.074834460381565</v>
+        <v>2.103113842329032</v>
       </c>
       <c r="F2007" t="n">
         <v>1.077557346759424</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.337321179053646</v>
+        <v>-3.266622724184978</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.042414282234978</v>
+        <v>2.070693664182444</v>
       </c>
       <c r="F2008" t="n">
         <v>1.077557346759424</v>
@@ -47758,10 +47758,10 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.539574899378</v>
+        <v>-3.468876444509331</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.956333023708098</v>
+        <v>1.984612405655566</v>
       </c>
       <c r="F2009" t="n">
         <v>0.8753036264350709</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.701143324905255</v>
+        <v>-3.630444870036587</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.890139663707349</v>
+        <v>1.918419045654816</v>
       </c>
       <c r="F2010" t="n">
         <v>0.7485207026371915</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389346</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.809443986775374</v>
+        <v>-3.738745531906706</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.85989280582522</v>
+        <v>1.888172187772687</v>
       </c>
       <c r="F2011" t="n">
         <v>0.7485207026371915</v>
@@ -47827,10 +47827,10 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.902591458078741</v>
+        <v>-3.831893003210073</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.814639014086813</v>
+        <v>1.84291839603428</v>
       </c>
       <c r="F2012" t="n">
         <v>0.6256914913546587</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.930492245188214</v>
+        <v>-3.859793790319546</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.802002740370026</v>
+        <v>1.830282122317493</v>
       </c>
       <c r="F2013" t="n">
         <v>0.5910945672117239</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.053018347891108</v>
+        <v>-3.982319893022439</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.749756743266067</v>
+        <v>1.778036125213534</v>
       </c>
       <c r="F2014" t="n">
         <v>0.4685684645088301</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.283532844076697</v>
+        <v>-4.212834389208028</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.724256904382335</v>
+        <v>1.752536286329802</v>
       </c>
       <c r="F2015" t="n">
         <v>0.2380539683232413</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.63227792930114</v>
+        <v>-4.561579474432472</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.725070589294405</v>
+        <v>1.753349971241872</v>
       </c>
       <c r="F2016" t="n">
         <v>0.1293060144043435</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237091</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.786264347077281</v>
+        <v>-4.715565892208613</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.732456291329588</v>
+        <v>1.760735673277056</v>
       </c>
       <c r="F2017" t="n">
         <v>0.1293060144043435</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423384</v>
+        <v>3.619923016423385</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.735742443249615</v>
+        <v>-4.665043988380947</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.738716254980776</v>
+        <v>1.766995636928243</v>
       </c>
       <c r="F2018" t="n">
         <v>0.1293060144043435</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609751</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.988217597257339</v>
+        <v>-4.917519142388671</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.6495966824331</v>
+        <v>1.677876064380567</v>
       </c>
       <c r="F2019" t="n">
         <v>0.1293060144043435</v>
@@ -48011,10 +48011,10 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.281113353736751</v>
+        <v>-5.210414898868083</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.533648914360279</v>
+        <v>1.561928296307746</v>
       </c>
       <c r="F2020" t="n">
         <v>0.1293060144043435</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.467777481871559</v>
+        <v>-5.397079027002891</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.463105005333677</v>
+        <v>1.491384387281144</v>
       </c>
       <c r="F2021" t="n">
         <v>0.1025670435797836</v>
@@ -48057,10 +48057,10 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.613798168785522</v>
+        <v>-5.543099713916853</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.399774583304281</v>
+        <v>1.428053965251749</v>
       </c>
       <c r="F2022" t="n">
         <v>0.09348395178592667</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.705512177895107</v>
+        <v>-5.634813723026438</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.525293036359491</v>
+        <v>1.553572418306959</v>
       </c>
       <c r="F2023" t="n">
         <v>0.09348395178592667</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.737163836955077</v>
+        <v>-5.666465382086407</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.507479010699317</v>
+        <v>1.535758392646785</v>
       </c>
       <c r="F2024" t="n">
         <v>0.08831549454148646</v>
@@ -48126,10 +48126,10 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.81909865522396</v>
+        <v>-5.748400200355291</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.484934500960255</v>
+        <v>1.513213882907723</v>
       </c>
       <c r="F2025" t="n">
         <v>0.07838074895440628</v>
@@ -48149,10 +48149,10 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.921074777472367</v>
+        <v>-5.850376322603698</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.453069690516795</v>
+        <v>1.481349072464262</v>
       </c>
       <c r="F2026" t="n">
         <v>-0.0235953732940013</v>
@@ -48172,10 +48172,10 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.811068493995146</v>
+        <v>-5.740370039126477</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.489225091151859</v>
+        <v>1.517504473099327</v>
       </c>
       <c r="F2027" t="n">
         <v>-0.0003908013767260909</v>
@@ -48195,10 +48195,10 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.66800891825422</v>
+        <v>-5.597310463385551</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.550698932170204</v>
+        <v>1.578978314117671</v>
       </c>
       <c r="F2028" t="n">
         <v>0.007622625213253187</v>
@@ -48218,10 +48218,10 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.366562192782382</v>
+        <v>-5.295863737913713</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.678538505241475</v>
+        <v>1.706817887188942</v>
       </c>
       <c r="F2029" t="n">
         <v>0.3090693506850904</v>
@@ -48241,10 +48241,10 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.391152437017566</v>
+        <v>-5.320453982148897</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.669673585300112</v>
+        <v>1.697952967247579</v>
       </c>
       <c r="F2030" t="n">
         <v>0.3090693506850904</v>
@@ -48264,10 +48264,10 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.340114061011046</v>
+        <v>-5.269415606142377</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.690931840082476</v>
+        <v>1.719211222029943</v>
       </c>
       <c r="F2031" t="n">
         <v>0.3090693506850904</v>
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.246429934262996</v>
+        <v>-5.228276311275746</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.747443589655841</v>
+        <v>1.754705038850741</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4027534774331403</v>
+        <v>0.3502086455517213</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.088024074134671</v>
+        <v>4.05649717500582</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.149795022244356</v>
+        <v>-5.131641399257106</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.602281550587231</v>
+        <v>1.609542999782132</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4993883894517802</v>
+        <v>0.4468435575703612</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.96218901746979</v>
+        <v>3.930662118340938</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.280375756775198</v>
+        <v>-5.262222133787948</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.553551300848858</v>
+        <v>1.560812750043759</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3688076549209377</v>
+        <v>0.3162628230395187</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.887342620825248</v>
+        <v>3.855815721696397</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.115879422584237</v>
+        <v>-5.097725799596986</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.603776653601326</v>
+        <v>1.611038102796226</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5333039891118996</v>
+        <v>0.4807591572304806</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.970467240415908</v>
+        <v>3.938940341287056</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.143249355268669</v>
+        <v>-5.125095732281419</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.592016390963983</v>
+        <v>1.599277840158883</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5333039891118996</v>
+        <v>0.4807591572304806</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.969654950852338</v>
+        <v>3.938128051723486</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.153634550158558</v>
+        <v>-5.135480927171308</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.597731092133099</v>
+        <v>1.604992541328</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.5229187942220103</v>
+        <v>0.4703739623405913</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.973292613043476</v>
+        <v>3.941765713914624</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.172222708880783</v>
+        <v>-5.154069085893533</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.661132834420635</v>
+        <v>1.668394283615534</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.504330635499785</v>
+        <v>0.4517858036183659</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.032976723586566</v>
+        <v>4.001449824457715</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.172521255576819</v>
+        <v>-5.154367632589569</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.657882426560519</v>
+        <v>1.665143875755418</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5040320888037491</v>
+        <v>0.45148725692233</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.029666606387243</v>
+        <v>3.998139707258392</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.071698121886391</v>
+        <v>-5.053544498899141</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.702742574976081</v>
+        <v>1.710004024170981</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5164963042881029</v>
+        <v>0.4639514724066838</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.041676030617247</v>
+        <v>4.010149131488395</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.880916761133983</v>
+        <v>-4.862763138146734</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.779184372755588</v>
+        <v>1.786445821950487</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7072776650405103</v>
+        <v>0.6547328331590911</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.156274100547234</v>
+        <v>4.124747201418383</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.862399907092163</v>
+        <v>-4.844246284104914</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.766427960109912</v>
+        <v>1.773689409304812</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.7202077944657185</v>
+        <v>0.6676629625842994</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.143869023939956</v>
+        <v>4.112342124811105</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.807069319190401</v>
+        <v>-4.788915696203151</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.823527131882676</v>
+        <v>1.830788581077575</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7755383823674806</v>
+        <v>0.7229935504860615</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.212034313293072</v>
+        <v>4.180507414164221</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.795015192277438</v>
+        <v>-4.776861569290189</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.822035350549299</v>
+        <v>1.829296799744198</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7875925092804434</v>
+        <v>0.7350476773990243</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.212953357342287</v>
+        <v>4.181426458213435</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.836170311845659</v>
+        <v>-4.81801668885841</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.807453932906146</v>
+        <v>1.814715382101046</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.7464373897122225</v>
+        <v>0.6938925578308034</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.190140915785491</v>
+        <v>4.158614016656639</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.733289722317066</v>
+        <v>-4.715136099329817</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.861457194595466</v>
+        <v>1.868718643790365</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.8493179792408154</v>
+        <v>0.7967731473593963</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.264720295380529</v>
+        <v>4.233193396251677</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.964890115486567</v>
+        <v>-4.946736492499317</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.789019707501259</v>
+        <v>1.796281156696159</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.8493179792408154</v>
+        <v>0.7967731473593963</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.284922965554123</v>
+        <v>4.253396066425271</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.982962623778178</v>
+        <v>-4.964809000790929</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.781790704184615</v>
+        <v>1.789052153379515</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.8493179792408154</v>
+        <v>0.7967731473593963</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.284922965554123</v>
+        <v>4.253396066425271</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.158069456354623</v>
+        <v>-5.139915833367374</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.671999884747504</v>
+        <v>1.679261333942403</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.8493179792408154</v>
+        <v>0.7967731473593963</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.24517487914759</v>
+        <v>4.213647980018738</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.126783435814168</v>
+        <v>-5.108629812826918</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.691536911960626</v>
+        <v>1.698798361155526</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8806039997812708</v>
+        <v>0.8280591678998517</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.270969110468803</v>
+        <v>4.239442211339951</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.973758043700883</v>
+        <v>-4.955604420713634</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.851918068378844</v>
+        <v>1.859179517573744</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.033629391894555</v>
+        <v>0.9810845600131358</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.461955345309677</v>
+        <v>4.430428446180827</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.002065357574153</v>
+        <v>-4.983911734586904</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.028061367737828</v>
+        <v>2.035322816932728</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.033629391894555</v>
+        <v>0.9810845600131358</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.64942157021797</v>
+        <v>4.617894671089118</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.168658582687676</v>
+        <v>-5.150504959700426</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.930827029046501</v>
+        <v>1.938088478241401</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8670361667810325</v>
+        <v>0.8144913348996135</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.518868586503938</v>
+        <v>4.487341687375087</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.995594203305376</v>
+        <v>-4.977440580318127</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.003729183461139</v>
+        <v>2.010990632656039</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8670361667810325</v>
+        <v>0.8144913348996135</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.522544989165656</v>
+        <v>4.491018090036805</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.966348222849679</v>
+        <v>-4.94819459986243</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.013045630766913</v>
+        <v>2.020307079961813</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8670361667810325</v>
+        <v>0.8144913348996135</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.520163044289151</v>
+        <v>4.4886361451603</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539104</v>
+        <v>3.699424827539102</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.07327377072753</v>
+        <v>-5.055120147740281</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.967568650773408</v>
+        <v>1.974830099968307</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7601106189031811</v>
+        <v>0.7075657870217621</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.453300954720076</v>
+        <v>4.421774055591224</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983734</v>
+        <v>3.689962785983732</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.218292329234779</v>
+        <v>-5.20013870624753</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.910990029513742</v>
+        <v>1.918251478708642</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6150920603959326</v>
+        <v>0.5625472285145136</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.367718621758961</v>
+        <v>4.33619172263011</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969745</v>
+        <v>3.711872614969744</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.336634095019496</v>
+        <v>-5.318480472032247</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.963584562457608</v>
+        <v>1.970846011652508</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6257780989588226</v>
+        <v>0.5732332670774036</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.474061484154448</v>
+        <v>4.442534585025596</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073535</v>
+        <v>3.714899237073533</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.388044517340204</v>
+        <v>-5.369890894352955</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.940806090655264</v>
+        <v>1.948067539850163</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6257780989588226</v>
+        <v>0.5732332670774036</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.471847181280387</v>
+        <v>4.440320282151535</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720062</v>
+        <v>3.70477813472006</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.467463968547956</v>
+        <v>-5.449310345560707</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.908941438246452</v>
+        <v>1.916202887441352</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6257780989588226</v>
+        <v>0.5732332670774036</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.471750309354676</v>
+        <v>4.440223410225824</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581129</v>
+        <v>3.736825137581127</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.562926966465174</v>
+        <v>-5.544773343477924</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.870750132637609</v>
+        <v>1.878011581832509</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6257780989588226</v>
+        <v>0.5732332670774036</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.47174420291272</v>
+        <v>4.440217303783868</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500731</v>
+        <v>3.715393145500729</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.602946964508957</v>
+        <v>-5.584793341521708</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.852838529982706</v>
+        <v>1.860099979177606</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.5857581009150388</v>
+        <v>0.5332132690336198</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.44582860064906</v>
+        <v>4.414301701520208</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636267</v>
+        <v>3.736109598636265</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.658316126641151</v>
+        <v>-5.640162503653902</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.836424682877555</v>
+        <v>1.843686132072455</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.5857581009150388</v>
+        <v>0.5332132690336198</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.451562418396787</v>
+        <v>4.420035519267935</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.73684305539601</v>
+        <v>3.736843055396008</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.703753906471978</v>
+        <v>-5.685600283484729</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.817787934288158</v>
+        <v>1.825049383483057</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5429131102368792</v>
+        <v>0.4903682783554602</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.425393787332824</v>
+        <v>4.393866888203973</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396419</v>
+        <v>3.790292685396417</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.620528449624314</v>
+        <v>-5.602374826637065</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.870952509877542</v>
+        <v>1.878213959072442</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5429131102368792</v>
+        <v>0.4903682783554602</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.445268180183143</v>
+        <v>4.413741281054292</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299173</v>
+        <v>3.794507029299171</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.444238225019006</v>
+        <v>-5.426084602031757</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.925169300244393</v>
+        <v>1.932430749439292</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5429131102368792</v>
+        <v>0.4903682783554602</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.42896888070787</v>
+        <v>4.39744198157902</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590404</v>
+        <v>3.794725278590402</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.261026561885911</v>
+        <v>-5.242872938898662</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.000884914961677</v>
+        <v>2.008146364156576</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5429131102368792</v>
+        <v>0.4903682783554602</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.431399830171916</v>
+        <v>4.399872931043065</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146282</v>
+        <v>3.776866743146281</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.18930511487206</v>
+        <v>-5.171151491884811</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.995364679615106</v>
+        <v>2.002626128810006</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6146345572507298</v>
+        <v>0.5620897253693108</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.440223884228116</v>
+        <v>4.408696985099264</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676848</v>
+        <v>3.723809890676846</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.318683897511838</v>
+        <v>-5.300530274524589</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.890528912480367</v>
+        <v>1.897790361675267</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.5725327845435264</v>
+        <v>0.5199879526621074</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.361878566524966</v>
+        <v>4.330351667396114</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.792484517339273</v>
+        <v>3.862651538391607</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.194155739725979</v>
+        <v>4.187901821097963</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.318683897511838</v>
+        <v>-5.300530274524589</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.890528912480367</v>
+        <v>1.897790361675267</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5725327845435264</v>
+        <v>0.5199879526621074</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.187219536712346</v>
+        <v>4.180965618084331</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240828.xlsx
+++ b/tame_output/ON/bt/strategyON_20240828.xlsx
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>58.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,17 +844,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>79.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>107.2%</t>
+          <t>128.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-79.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.9%</t>
+          <t>125.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.1%</t>
+          <t>-39.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.5%</t>
+          <t>-49.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.6%</t>
+          <t>423.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-691.6%</t>
+          <t>-676.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-186.4%</t>
+          <t>-180.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>119.7%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-291.1%</t>
+          <t>-295.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-172.0%</t>
+          <t>-155.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-22.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>77.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>-6.8%</t>
         </is>
       </c>
     </row>
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.329184830008393</v>
+        <v>-5.195317405826184</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.9846486196118076</v>
+        <v>1.038195589284692</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.3313998427407806</v>
+        <v>-0.2235950597255912</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.917839070284444</v>
+        <v>2.982521940093558</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.737773607189072</v>
+        <v>-5.603906183006862</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8199746527542953</v>
+        <v>0.8735216224271789</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.6321838369062697</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.671447347990797</v>
+        <v>2.73613021779991</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.851534019211937</v>
+        <v>-5.717666595029727</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.7696559204166098</v>
+        <v>0.8232028900894939</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.6321838369062697</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.666632780462257</v>
+        <v>2.731315650271371</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.267925893498934</v>
+        <v>-6.134058469316725</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6010932213106881</v>
+        <v>0.6546401909835722</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.6321838369062697</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.664626831071135</v>
+        <v>2.729309700880248</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.629099523315922</v>
+        <v>-6.495232099133712</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4668824600525721</v>
+        <v>0.5204294297254561</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.6321838369062697</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.674885521739814</v>
+        <v>2.739568391548927</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.972358042958941</v>
+        <v>-6.838490618776731</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3256786173410595</v>
+        <v>0.3792255870139436</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.6321838369062697</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.670985086885509</v>
+        <v>2.735667956694622</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199279</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.020560860201285</v>
+        <v>-6.886693436019075</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3048024104991232</v>
+        <v>0.3583493801720068</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.6321838369062697</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.669390006940509</v>
+        <v>2.734072876749623</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969587</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.317222202011482</v>
+        <v>-7.183354777829273</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1899168497042525</v>
+        <v>0.2434638193771361</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.7009269726401482</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.631923101429391</v>
+        <v>2.696605971238504</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923079</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.503941910320785</v>
+        <v>-7.370074486138575</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1112026618461281</v>
+        <v>0.1647496315190118</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.7009269726401482</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.627896796894988</v>
+        <v>2.692579666704101</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.886943299063416</v>
+        <v>-7.753075874881207</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.04209999497250827</v>
+        <v>0.01144697470037537</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.8087317556553376</v>
+        <v>-0.7009269726401482</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.627794695573404</v>
+        <v>2.692477565382517</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.891429744264805</v>
+        <v>-7.757562320082595</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.04132305708163386</v>
+        <v>0.01222391259125022</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.8132182008567264</v>
+        <v>-0.705413417841537</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.627674344424</v>
+        <v>2.692357214233114</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.250960066768808</v>
+        <v>-8.117092642586599</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1797848827851847</v>
+        <v>-0.1262379131123006</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.8132182008567264</v>
+        <v>-0.705413417841537</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.63302464772205</v>
+        <v>2.697707517531164</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.30130913022303</v>
+        <v>-8.167441706040821</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1920084882096957</v>
+        <v>-0.1384615185368121</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.8635672643109484</v>
+        <v>-0.7557624812957591</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.610731229606695</v>
+        <v>2.675414099415808</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.398928407644426</v>
+        <v>-8.265060983462217</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2280144485564857</v>
+        <v>-0.1744674788836016</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9611865417323451</v>
+        <v>-0.8533817587171557</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.555201413775626</v>
+        <v>2.619884283584739</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.452999907152785</v>
+        <v>-8.319132482970575</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.2467494920382567</v>
+        <v>-0.1932025223653731</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.015258041240704</v>
+        <v>-0.9074532582255151</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.525652070392182</v>
+        <v>2.590334940201296</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.657258082482649</v>
+        <v>-8.523390658300439</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3229395650515601</v>
+        <v>-0.269392595378676</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.142896985854693</v>
+        <v>-1.035092202839504</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.454581900742431</v>
+        <v>2.519264770551545</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.690910920991122</v>
+        <v>-8.557043496808912</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3319181459705134</v>
+        <v>-0.2783711762976293</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.243310353771731</v>
+        <v>-1.135505570756541</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.398816434476645</v>
+        <v>2.463499304285758</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.82999703560998</v>
+        <v>-8.69612961142777</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3721808903246351</v>
+        <v>-0.318633920651751</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.382396468390588</v>
+        <v>-1.274591685375398</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.330736467198752</v>
+        <v>2.395419337007866</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.005121452996523</v>
+        <v>-8.871254028814313</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4276754365317355</v>
+        <v>-0.3741284668588518</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.557520885777131</v>
+        <v>-1.449716102761942</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.240217037514342</v>
+        <v>2.304899907323456</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.239573547011013</v>
+        <v>-9.105706122828803</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.5286754390391275</v>
+        <v>-0.4751284693662434</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.557520885777131</v>
+        <v>-1.449716102761942</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.232997872612747</v>
+        <v>2.29768074242186</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.343948278037459</v>
+        <v>-9.210080853855249</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5770975222236823</v>
+        <v>-0.5235505525507982</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.661895616803577</v>
+        <v>-1.554090833788388</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.163700843222903</v>
+        <v>2.228383713032017</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.506461743736043</v>
+        <v>-9.372594319553833</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6409871186645595</v>
+        <v>-0.5874401489916758</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.759529047222264</v>
+        <v>-1.651724264207075</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.106236574810247</v>
+        <v>2.17091944461936</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.632498537104333</v>
+        <v>-9.498631112922123</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6887081073827606</v>
+        <v>-0.6351611377098769</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.734277424412522</v>
+        <v>-1.626472641397332</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.124081277125207</v>
+        <v>2.188764146934321</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.575426765208402</v>
+        <v>-9.441559341026192</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6618890629379877</v>
+        <v>-0.6083420932651036</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.734277424412522</v>
+        <v>-1.626472641397332</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.128071612811608</v>
+        <v>2.192754482620721</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.717098606932522</v>
+        <v>-9.583231182750312</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.7200330265263775</v>
+        <v>-0.6664860568534934</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.734277424412522</v>
+        <v>-1.626472641397332</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.126596385912866</v>
+        <v>2.19127925572198</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.667507762507688</v>
+        <v>-9.533640338325478</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6851432785915712</v>
+        <v>-0.6315963089186876</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.684686579987688</v>
+        <v>-1.576881796972498</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.171404302732639</v>
+        <v>2.236087172541752</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770577</v>
+        <v>3.676841549770576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.518589428035831</v>
+        <v>-9.384722003853621</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6386270784495118</v>
+        <v>-0.5850801087766277</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.653436989252515</v>
+        <v>-1.545632206237325</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.17710292352706</v>
+        <v>2.241785793336173</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68516138161528</v>
+        <v>3.685161381615279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.292744275316419</v>
+        <v>-9.15887685113421</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5387099443255381</v>
+        <v>-0.4851629746526545</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.611510313665351</v>
+        <v>-1.503705530650162</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.211838001915567</v>
+        <v>2.27652087172468</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.168165618978827</v>
+        <v>-9.034298194796618</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4877393372344425</v>
+        <v>-0.4341923675615589</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.611510313665351</v>
+        <v>-1.503705530650162</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.212977146471625</v>
+        <v>2.277660016280739</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.143128937410317</v>
+        <v>-9.009261513228108</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4750908904449309</v>
+        <v>-0.4215439207720468</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.586181226114615</v>
+        <v>-1.478376443099426</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.230808373164174</v>
+        <v>2.295491242973288</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.070995762122436</v>
+        <v>-8.937128337940226</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4405039160911421</v>
+        <v>-0.3869569464182581</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.586181226114615</v>
+        <v>-1.478376443099426</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.236542077402811</v>
+        <v>2.301224947211924</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.999629369512789</v>
+        <v>-8.865761945330579</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4216946214411483</v>
+        <v>-0.3681476517682643</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.514814833504967</v>
+        <v>-1.407010050489778</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.269624650574735</v>
+        <v>2.334307520383848</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.906170335527564</v>
+        <v>-8.772302911345355</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.394194489159966</v>
+        <v>-0.3406475194870819</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.514814833504967</v>
+        <v>-1.407010050489778</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.259741169261827</v>
+        <v>2.324424039070941</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.821538451800169</v>
+        <v>-8.669699449392535</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3621762961683817</v>
+        <v>-0.3014406952053279</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.514814833504967</v>
+        <v>-1.407010050489778</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.257906608762453</v>
+        <v>2.322589478571567</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.723631413123679</v>
+        <v>-8.571792410716045</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3233137956712464</v>
+        <v>-0.2625781947081927</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.446829083644411</v>
+        <v>-1.339024300629222</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.298397743705326</v>
+        <v>2.36308061351444</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.699677872147721</v>
+        <v>-8.547838869740087</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3130638731353694</v>
+        <v>-0.2523282721723157</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.422875542668453</v>
+        <v>-1.315070759653264</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.313438374436394</v>
+        <v>2.378121244245508</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.435617933824924</v>
+        <v>-8.28377893141729</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2207002139680028</v>
+        <v>-0.1599646130049495</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.158815604345657</v>
+        <v>-1.051010821330468</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.45861402126832</v>
+        <v>2.523296891077433</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.83325274783972</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.728538310320086</v>
+        <v>-7.576699307912452</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.05934460177363166</v>
+        <v>0.120080202736685</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.158815604345657</v>
+        <v>-1.051010821330468</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.455826987608019</v>
+        <v>2.520509857417133</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.688354011953895</v>
+        <v>-7.536515009546261</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.07576194500794919</v>
+        <v>0.1364975459710025</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.118631305979466</v>
+        <v>-1.010826522964277</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.480281190515575</v>
+        <v>2.544964060324689</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.524954141014533</v>
+        <v>-7.373115138606899</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1404887146044511</v>
+        <v>0.2012243155675044</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9552314350401039</v>
+        <v>-0.8474266520249145</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.577687934299949</v>
+        <v>2.642370804109063</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.291472918784934</v>
+        <v>-7.1396339163773</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2418056323341427</v>
+        <v>0.3025412332971964</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.7217502128105053</v>
+        <v>-0.613945429795316</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.725701096475561</v>
+        <v>2.790383966284674</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.141806527777419</v>
+        <v>-6.989967525369785</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2987799784241898</v>
+        <v>0.3595155793872431</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.6288467215679694</v>
+        <v>-0.52104193855278</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.778550980908123</v>
+        <v>2.843233850717237</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.009531054146533</v>
+        <v>-6.857692051738899</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2529509538836989</v>
+        <v>0.3136865548467527</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4965712479370827</v>
+        <v>-0.3887664649218934</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.75917705109381</v>
+        <v>2.823859920902923</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.853792721586791</v>
+        <v>-6.701953719179157</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3180613475952323</v>
+        <v>0.3787969485582861</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3408329153773412</v>
+        <v>-0.2330281323621518</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.855435111317292</v>
+        <v>2.920117981126405</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.768828054857471</v>
+        <v>-6.616989052449837</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3649535555106191</v>
+        <v>0.4256891564736729</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2558682486480216</v>
+        <v>-0.1480634656328322</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.919320252578542</v>
+        <v>2.984003122387656</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.874418044630575</v>
+        <v>-6.722579042222941</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.1947416300021585</v>
+        <v>0.2554772309652122</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.361458238421126</v>
+        <v>-0.2536534554059366</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.727990329115461</v>
+        <v>2.792673198924574</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.806183460005148</v>
+        <v>-6.654344457597514</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2705798057294162</v>
+        <v>0.3313154066924695</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.34304291554859</v>
+        <v>-0.2352381325334006</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.787583864716069</v>
+        <v>2.852266734525182</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.658243418597548</v>
+        <v>-6.506404416189914</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2131350136540489</v>
+        <v>0.2738706146171022</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3227219996400324</v>
+        <v>-0.214917216624843</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.683155605622796</v>
+        <v>2.74783847543191</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.60527389634356</v>
+        <v>-6.453434893935926</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.225608836302166</v>
+        <v>0.2863444372652193</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2697524773860435</v>
+        <v>-0.1619476943708542</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.706223332721711</v>
+        <v>2.770906202530825</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.439485700383269</v>
+        <v>-6.287646697975635</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.284963502591189</v>
+        <v>0.3456991035542427</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2697524773860435</v>
+        <v>-0.1619476943708542</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.699262720626618</v>
+        <v>2.763945590435732</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.4061224939045</v>
+        <v>-6.254283491496866</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3127711395638397</v>
+        <v>0.373506740526893</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2697524773860435</v>
+        <v>-0.1619476943708542</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.713725075007761</v>
+        <v>2.778407944816875</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.297863356781979</v>
+        <v>-6.146024354374345</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3506069148720434</v>
+        <v>0.4113425158350967</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2697524773860435</v>
+        <v>-0.1619476943708542</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.708257195466956</v>
+        <v>2.77294006527607</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.174572221964848</v>
+        <v>-6.022733219557214</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.3974214628094725</v>
+        <v>0.4581570637725263</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.146461342568913</v>
+        <v>-0.03865655955372366</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.779729970367812</v>
+        <v>2.844412840176925</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.121875354833556</v>
+        <v>-5.970036352425923</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4262011878993142</v>
+        <v>0.4869367888623679</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.09376447543762184</v>
+        <v>0.01404030757756752</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.819049068883911</v>
+        <v>2.883731938693025</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.878109912850112</v>
+        <v>-5.726270910442478</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5194880730397426</v>
+        <v>0.5802236740027964</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.09376447543762184</v>
+        <v>0.01404030757756752</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.814829777230962</v>
+        <v>2.879512647040076</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.78833424047364</v>
+        <v>-5.636495238066006</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5575226559103474</v>
+        <v>0.6182582568734012</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.03216503052331182</v>
+        <v>0.07563975249187754</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.853913758099564</v>
+        <v>2.918596627908677</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.538483846524565</v>
+        <v>-5.386644844116931</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6502048884736795</v>
+        <v>0.7109404894367333</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.03216503052331182</v>
+        <v>0.07563975249187754</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.846655833083266</v>
+        <v>2.91133870289238</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.362591754057133</v>
+        <v>-5.210752751649499</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7241608489813012</v>
+        <v>0.7848964499443549</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.03216503052331182</v>
+        <v>0.07563975249187754</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.850254956603915</v>
+        <v>2.914937826413028</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.19114529103467</v>
+        <v>-5.039306288627036</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8060669402448402</v>
+        <v>0.8668025412078939</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1392814324991513</v>
+        <v>0.2470862155143407</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.966450340471947</v>
+        <v>3.03113321028106</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.111123003925549</v>
+        <v>-4.959284001517915</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8370963327047858</v>
+        <v>0.8978319336678391</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2193037196082723</v>
+        <v>0.3271085026234616</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.013484190353716</v>
+        <v>3.078167060162829</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.047487261691614</v>
+        <v>-4.895648259283981</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8672454306526767</v>
+        <v>0.9279810316157302</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2829394618422068</v>
+        <v>0.3907442448573962</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.056360436748394</v>
+        <v>3.121043306557508</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.953789943475219</v>
+        <v>-4.801950941067585</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8859186167230304</v>
+        <v>0.9466542176860839</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2829394618422068</v>
+        <v>0.3907442448573962</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.03755469553219</v>
+        <v>3.102237565341303</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.964292566540508</v>
+        <v>-4.724171135975595</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8834606441217923</v>
+        <v>0.9795092163477572</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2724368387769179</v>
+        <v>0.4685240499493864</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.032996198317894</v>
+        <v>3.150648525021375</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.892049998369314</v>
+        <v>-4.651928567804401</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9162869852250903</v>
+        <v>1.012335557451055</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2724368387769179</v>
+        <v>0.4685240499493864</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.036925512152714</v>
+        <v>3.154577838856195</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232699787996</v>
+        <v>3.822326997879961</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.874336311491448</v>
+        <v>-4.634214880926535</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9240510438935763</v>
+        <v>1.020099616119541</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2756181676738347</v>
+        <v>0.4717053788463032</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.039512893408204</v>
+        <v>3.157165220111685</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.765531426011721</v>
+        <v>-4.525409995446808</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9645710693054608</v>
+        <v>1.060619641531426</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2756181676738347</v>
+        <v>0.4717053788463032</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.036510964628198</v>
+        <v>3.154163291331678</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.545510627974711</v>
+        <v>-4.305389197409798</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.054158425530879</v>
+        <v>1.150206997756844</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.416838012741815</v>
+        <v>0.6129252239142834</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.1228219086796</v>
+        <v>3.240474235383081</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.412642938911433</v>
+        <v>-4.17252150834652</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.123199683958013</v>
+        <v>1.219248256183979</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.416838012741815</v>
+        <v>0.6129252239142834</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.138716091481423</v>
+        <v>3.256368418184904</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.292469855546934</v>
+        <v>-4.052348424982021</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.172414761744115</v>
+        <v>1.26846333397008</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5370110961063139</v>
+        <v>0.7330983072787823</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.211965785940424</v>
+        <v>3.329618112643905</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.157216494216957</v>
+        <v>-3.917095063652044</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.236604208837546</v>
+        <v>1.332652781063511</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.672264457436291</v>
+        <v>0.8683516686087595</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.30320590529985</v>
+        <v>3.420858232003332</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.217091321574649</v>
+        <v>-3.976969891009737</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.198691769295894</v>
+        <v>1.294740341521859</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6123896300785989</v>
+        <v>0.8084768412510673</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.253318500286661</v>
+        <v>3.370970826990142</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.097271090663813</v>
+        <v>-3.857149660098899</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.261909030894438</v>
+        <v>1.357957603120403</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6123896300785989</v>
+        <v>0.8084768412510673</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.26860766952087</v>
+        <v>3.38625999622435</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.099740797125619</v>
+        <v>-3.859619366560705</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.168565347632157</v>
+        <v>1.264613919858122</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6099199236167927</v>
+        <v>0.8060071347892611</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.174770044966227</v>
+        <v>3.292422371669709</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.168110983449629</v>
+        <v>-3.927989552884715</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.060479134587854</v>
+        <v>1.15652770681382</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6191956226530076</v>
+        <v>0.8152828338254761</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.099597325873258</v>
+        <v>3.217249652576739</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.279983263075779</v>
+        <v>-4.039861832510866</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.006166931369285</v>
+        <v>1.102215503595251</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6191956226530076</v>
+        <v>0.8152828338254761</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.090034034505149</v>
+        <v>3.20768636120863</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.335503338968369</v>
+        <v>-4.095381908403455</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.120989737704452</v>
+        <v>1.217038309930417</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6191956226530076</v>
+        <v>0.8152828338254761</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.227064871197352</v>
+        <v>3.344717197900832</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205894</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.160029079175899</v>
+        <v>-3.919907648610986</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.195746673613227</v>
+        <v>1.291795245839193</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6191956226530076</v>
+        <v>0.8152828338254761</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.231632103189139</v>
+        <v>3.34928442989262</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.765024323225439</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.152104704590985</v>
+        <v>-3.911983274026072</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.1746584522084</v>
+        <v>1.270707024434365</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6191956226530076</v>
+        <v>0.8152828338254761</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.207374131950346</v>
+        <v>3.325026458653827</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.145826502021136</v>
+        <v>-3.905705071456223</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.10570804663779</v>
+        <v>1.201756618863755</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6254738252228567</v>
+        <v>0.8215610363953251</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.139679366893705</v>
+        <v>3.257331693597187</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.085973882817413</v>
+        <v>-3.8458524522525</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.139821480751411</v>
+        <v>1.235870052977377</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6254738252228567</v>
+        <v>0.8215610363953251</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.149851753325838</v>
+        <v>3.267504080029319</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.999730419791035</v>
+        <v>-3.759608989226122</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.169265136535822</v>
+        <v>1.265313708761788</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6254738252228567</v>
+        <v>0.8215610363953251</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.144798023899698</v>
+        <v>3.262450350603179</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.045037239190015</v>
+        <v>-3.804915808625102</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.142918184220756</v>
+        <v>1.238966756446721</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5846636622136259</v>
+        <v>0.7807508733860943</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.112087701538685</v>
+        <v>3.229740028242166</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.074070343892316</v>
+        <v>-3.833948913327404</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.131856815372937</v>
+        <v>1.227905387598902</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5846636622136259</v>
+        <v>0.7807508733860943</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.112639574571787</v>
+        <v>3.230291901275268</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.981259862441457</v>
+        <v>-3.741138431876545</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.098253699844647</v>
+        <v>1.194302272070612</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6774741436644852</v>
+        <v>0.8735613548369536</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.097598555333668</v>
+        <v>3.215250882037149</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.025649331770885</v>
+        <v>-3.785527901205972</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.082371388037476</v>
+        <v>1.178419960263441</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6330846743350576</v>
+        <v>0.829171885507526</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.072838349660612</v>
+        <v>3.190490676364093</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.142190936876228</v>
+        <v>-3.902069506311315</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.030830454507062</v>
+        <v>1.126879026733027</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5165430692297148</v>
+        <v>0.7126302804021832</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.997989095109129</v>
+        <v>3.115641421812611</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.1821150314588</v>
+        <v>-3.941993600893887</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.020352112504701</v>
+        <v>1.116400684730666</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5165430692297148</v>
+        <v>0.7126302804021832</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.003480390939797</v>
+        <v>3.121132717643278</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.209895429360152</v>
+        <v>-3.96977399879524</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.020737155112699</v>
+        <v>1.116785727338664</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4887626713283617</v>
+        <v>0.6848498825008301</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.998309353967524</v>
+        <v>3.115961680671005</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.328276102090291</v>
+        <v>-4.088154671525378</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8117406060212966</v>
+        <v>0.9077891782472616</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4215448191773855</v>
+        <v>0.6176320303498539</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.796334362677592</v>
+        <v>2.913986689381073</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.436890180533622</v>
+        <v>-4.196768749968709</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8884446353631696</v>
+        <v>0.9844932075891348</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4215448191773855</v>
+        <v>0.6176320303498539</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.916484023396797</v>
+        <v>3.034136350100278</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.401481142285479</v>
+        <v>-4.161359711720566</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9171212767647499</v>
+        <v>1.013169848990715</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4215448191773855</v>
+        <v>0.6176320303498539</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.93099704949912</v>
+        <v>3.048649376202601</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.363097479727328</v>
+        <v>-4.122976049162415</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9298941831303789</v>
+        <v>1.025942755356344</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4599284817355367</v>
+        <v>0.6560156929080051</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.95144668837638</v>
+        <v>3.06909901507986</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.185981149692162</v>
+        <v>-3.945859719127249</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9974697439897473</v>
+        <v>1.093518316215712</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4599284817355367</v>
+        <v>0.6560156929080051</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.948175717221682</v>
+        <v>3.065828043925162</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.231073394525708</v>
+        <v>-3.990951963960795</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9801162378182422</v>
+        <v>1.076164810044207</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3980324385661469</v>
+        <v>0.5941196497386153</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.911721483081961</v>
+        <v>3.029373809785442</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011232</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.05169797328694</v>
+        <v>-3.811576542722027</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.045653381620164</v>
+        <v>1.141701953846129</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5548091967368656</v>
+        <v>0.750896407909334</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.999574513290806</v>
+        <v>3.117226839994287</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982225</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.096712186807546</v>
+        <v>-3.856590756242633</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.008455151543511</v>
+        <v>1.104503723769476</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.524460301422261</v>
+        <v>0.7205475125947294</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.962172631433633</v>
+        <v>3.079824958137114</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.363716697079981</v>
+        <v>-4.123595266515069</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9073449097734827</v>
+        <v>1.003393481999447</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3300972633793124</v>
+        <v>0.5261844745517809</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.85124637094681</v>
+        <v>2.968898697650291</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.464914478517153</v>
+        <v>-4.224793047952241</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.866069719095115</v>
+        <v>0.96211829132108</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2616884498339932</v>
+        <v>0.4577756610064617</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.80940500471612</v>
+        <v>2.927057331419601</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.458403511902841</v>
+        <v>-4.218282081337929</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8662740672951568</v>
+        <v>0.9623226395211217</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2616884498339932</v>
+        <v>0.4577756610064617</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.807004966270437</v>
+        <v>2.924657292973917</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.439365384195543</v>
+        <v>-4.199243953630631</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8704140375863207</v>
+        <v>0.9664626098122855</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2035048385027987</v>
+        <v>0.3995920496752671</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.768619518679965</v>
+        <v>2.886271845383446</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.491881186470364</v>
+        <v>-4.251759755905452</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9687021183105828</v>
+        <v>1.064750690536548</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2035048385027987</v>
+        <v>0.3995920496752671</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.887913920314155</v>
+        <v>3.005566247017636</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.505747947804282</v>
+        <v>-4.26562651723937</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9639887427631493</v>
+        <v>1.060037314989114</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1656469217689757</v>
+        <v>0.3617341329414442</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.866032499259995</v>
+        <v>2.983684825963476</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.460943776264352</v>
+        <v>-4.22082234569944</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9879189417760472</v>
+        <v>1.083967514002012</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1656469217689757</v>
+        <v>0.3617341329414442</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.872041029656921</v>
+        <v>2.989693356360402</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.313200806029349</v>
+        <v>-4.073079375464437</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9449663511472477</v>
+        <v>1.041014923373212</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3334542790038589</v>
+        <v>0.5295414901763273</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.87067566527505</v>
+        <v>2.988327991978531</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.397022027304048</v>
+        <v>-4.156900596739136</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9142314841688493</v>
+        <v>1.010280056394814</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3334542790038589</v>
+        <v>0.5295414901763273</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.873469286806531</v>
+        <v>2.991121613510012</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.390869321251263</v>
+        <v>-4.150747890686351</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9173549149816214</v>
+        <v>1.013403487207586</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3396069850566432</v>
+        <v>0.5356941962291116</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.87782325882986</v>
+        <v>2.995475585533341</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.407678619401765</v>
+        <v>-4.167557188836853</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9097116724615308</v>
+        <v>1.005760244687496</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3227976869061415</v>
+        <v>0.5188848980786099</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.86681815667967</v>
+        <v>2.98447048338315</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798423</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.345380620625643</v>
+        <v>-4.105259190060731</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.000966425768801</v>
+        <v>1.097014997994765</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3680919511805836</v>
+        <v>0.564179162353052</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.960330269041155</v>
+        <v>3.077982595744636</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.143590422960485</v>
+        <v>-3.903468992395573</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.883974506548991</v>
+        <v>0.9800230787749558</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.566110143349738</v>
+        <v>0.7621973545222064</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.881433186056775</v>
+        <v>2.999085512760256</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.19447713564668</v>
+        <v>-3.954355705081768</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9339100537966882</v>
+        <v>1.029958626022653</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5152234306635435</v>
+        <v>0.7113106418360119</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.921191390767234</v>
+        <v>3.038843717470715</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031954</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.107866392996873</v>
+        <v>-3.86774496243196</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9831820869726546</v>
+        <v>1.07923065919862</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5938491618687017</v>
+        <v>0.7899363730411701</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.982994565606372</v>
+        <v>3.100646892309853</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.168075691002158</v>
+        <v>-3.927954260437245</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9576343485952123</v>
+        <v>1.053682920821178</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5336398638634172</v>
+        <v>0.7297270750358856</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.945404967627873</v>
+        <v>3.063057294331354</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.091653644570231</v>
+        <v>-3.851532214005318</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9866947852079115</v>
+        <v>1.082743357433877</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5336398638634172</v>
+        <v>0.7297270750358856</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.943896585667802</v>
+        <v>3.061548912371283</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.047280512931662</v>
+        <v>-3.807159082366749</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.004306905298775</v>
+        <v>1.10035547752474</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5780129955019858</v>
+        <v>0.7741002066744542</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.970383332086379</v>
+        <v>3.08803565878986</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.069760863790547</v>
+        <v>-3.829639433225634</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9897085590938119</v>
+        <v>1.085757131319777</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5780129955019858</v>
+        <v>0.7741002066744542</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.96477712622497</v>
+        <v>3.082429452928451</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.022105133229491</v>
+        <v>-3.781983702664578</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.015152608346039</v>
+        <v>1.111201180572004</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6256687260630415</v>
+        <v>0.8217559372355099</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.999752321589408</v>
+        <v>3.117404648292889</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.921586974730737</v>
+        <v>-3.681465544165824</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.060252245120266</v>
+        <v>1.156300817346231</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.726186884561796</v>
+        <v>0.9222740957342644</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.064955590063385</v>
+        <v>3.182607916766866</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.905681645298384</v>
+        <v>-3.665560214733471</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.053369049369079</v>
+        <v>1.149417621595044</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6470742238525571</v>
+        <v>0.8431614350250255</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.004242666113714</v>
+        <v>3.121894992817195</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.860843243689986</v>
+        <v>-3.620721813125073</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.075402112623067</v>
+        <v>1.171450684849032</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6516176567974266</v>
+        <v>0.847704867969895</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.011066428491264</v>
+        <v>3.128718755194746</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.880341699931994</v>
+        <v>-3.640220269367081</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.071763669757341</v>
+        <v>1.167812241983306</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6035330155175223</v>
+        <v>0.7996202266899907</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.9863765833544</v>
+        <v>3.104028910057881</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.836138862846094</v>
+        <v>-3.596017432281181</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.095324407119539</v>
+        <v>1.191372979345504</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6477358526034227</v>
+        <v>0.8438230637758911</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.018777888133777</v>
+        <v>3.136430214837258</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.843698528683141</v>
+        <v>-3.603577098118228</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.090710541253967</v>
+        <v>1.186759113479932</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.702539256613242</v>
+        <v>0.8986264677857104</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.050069931008916</v>
+        <v>3.167722257712398</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.685407111143868</v>
+        <v>-3.445285680578956</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.205274873452716</v>
+        <v>1.301323445678681</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.702539256613242</v>
+        <v>0.8986264677857104</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.101317696191956</v>
+        <v>3.218970022895437</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.477765107509392</v>
+        <v>-3.237643676944479</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.28677237950076</v>
+        <v>1.382820951726725</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9101812602477182</v>
+        <v>1.106268471420186</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.224343602966895</v>
+        <v>3.341995929670376</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.426733014786864</v>
+        <v>-3.186611584221951</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.302133444828041</v>
+        <v>1.398182017054006</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9612133529702461</v>
+        <v>1.157300564142715</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.249911086838682</v>
+        <v>3.367563413542163</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.361508833659658</v>
+        <v>-3.121387403094745</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.345410521371628</v>
+        <v>1.441459093597593</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.026437534097452</v>
+        <v>1.22252474526992</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.30623299960771</v>
+        <v>3.423885326311191</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.324081813588525</v>
+        <v>-3.083960383023612</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.356342301699362</v>
+        <v>1.452390873925327</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.031689072126633</v>
+        <v>1.227776283299102</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.305344894724499</v>
+        <v>3.42299722142798</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.344193469623233</v>
+        <v>-3.10407203905832</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.349554431616719</v>
+        <v>1.445603003842684</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.042716417124052</v>
+        <v>1.238803628296521</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.313218094054191</v>
+        <v>3.430870420757672</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.315780206523349</v>
+        <v>-3.075658775958436</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.521477507877883</v>
+        <v>1.617526080103848</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9837408543776236</v>
+        <v>1.179828065550092</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.438390527427544</v>
+        <v>3.556042854131026</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.240997945498337</v>
+        <v>-3.000876514933424</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.671503321505705</v>
+        <v>1.767551893731671</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.058523115402636</v>
+        <v>1.254610326575105</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.603372793260369</v>
+        <v>3.72102511996385</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.214913861234529</v>
+        <v>-2.974792430669616</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.673644931225088</v>
+        <v>1.769693503451053</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.058523115402636</v>
+        <v>1.254610326575105</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.595080769274228</v>
+        <v>3.712733095977709</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.127035948125408</v>
+        <v>-2.886914517560495</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.706989292052515</v>
+        <v>1.80303786427848</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.174448757825987</v>
+        <v>1.370535968998456</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.662829350312018</v>
+        <v>3.7804816770155</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.118143486732125</v>
+        <v>-2.878022056167212</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.72810068233662</v>
+        <v>1.824149254562585</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.174448757825987</v>
+        <v>1.370535968998456</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.68038375603881</v>
+        <v>3.798036082742291</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945361</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.286619603702003</v>
+        <v>-3.04649817313709</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.652565282953253</v>
+        <v>1.748613855179218</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.146500922109406</v>
+        <v>1.342588133281875</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.655470102013445</v>
+        <v>3.773122428716927</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.840363411072563</v>
+        <v>-2.60024198050765</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.812337457192891</v>
+        <v>1.908386029418856</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.051782252439774</v>
+        <v>1.247869463612242</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.579908597399527</v>
+        <v>3.697560924103009</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.820922554694706</v>
+        <v>-2.577520876824497</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.810777822240938</v>
+        <v>1.908138493389021</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.051782252439774</v>
+        <v>1.247869463612242</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.570572619896432</v>
+        <v>3.688224946599913</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.950124367988748</v>
+        <v>-2.70672269011854</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.91800322277449</v>
+        <v>2.015363893922573</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9225804391457315</v>
+        <v>1.1186676503182</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.651957657771176</v>
+        <v>3.769609984474657</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.975998766462774</v>
+        <v>-2.732597088592565</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.944731285878526</v>
+        <v>2.04209195702661</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9674920478574727</v>
+        <v>1.163579259029941</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.715982445491867</v>
+        <v>3.833634772195348</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.9689440762476</v>
+        <v>-2.725542398377392</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.944228517954141</v>
+        <v>2.041589189102224</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9745467380726465</v>
+        <v>1.170633949245115</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.716890615610517</v>
+        <v>3.834542942313997</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.941992851921112</v>
+        <v>-2.698591174050904</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.965015161329478</v>
+        <v>2.062375832477561</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9894270841003656</v>
+        <v>1.185514295272834</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.735824976871889</v>
+        <v>3.853477303575371</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.077945859977429</v>
+        <v>-2.83454418210722</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.094737090251911</v>
+        <v>2.192097761399994</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9894270841003656</v>
+        <v>1.185514295272834</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.919928109016849</v>
+        <v>4.03758043572033</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.100353977782301</v>
+        <v>-2.856952299912092</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.077890538032955</v>
+        <v>2.175251209181039</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9894270841003656</v>
+        <v>1.185514295272834</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.912044803919843</v>
+        <v>4.029697130623323</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.128578213359901</v>
+        <v>-2.885176535489693</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.068654843351553</v>
+        <v>2.166015514499636</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.007403836551674</v>
+        <v>1.203491047724143</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.924884854940265</v>
+        <v>4.042537181643747</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.138019139248431</v>
+        <v>-2.894617461378223</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.121132190717987</v>
+        <v>2.218492861866071</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.129830954095066</v>
+        <v>1.325918165267534</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.054594843188147</v>
+        <v>4.172247169891628</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.190292746584072</v>
+        <v>-2.946891068713864</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.103113842329032</v>
+        <v>2.200474513477115</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.077557346759424</v>
+        <v>1.273644557931893</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.026121773332063</v>
+        <v>4.143774100035544</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.266622724184978</v>
+        <v>-3.02322104631477</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.070693664182444</v>
+        <v>2.168054335330528</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.077557346759424</v>
+        <v>1.273644557931893</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.024233586225838</v>
+        <v>4.141885912929319</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.468876444509331</v>
+        <v>-3.225474766639123</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.984612405655566</v>
+        <v>2.081973076803649</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8753036264350709</v>
+        <v>1.07139083760754</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.897701583634088</v>
+        <v>4.01535391033757</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.630444870036587</v>
+        <v>-3.387043192166378</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.918419045654816</v>
+        <v>2.015779716802899</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7485207026371915</v>
+        <v>0.9446079138096602</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.820065839565513</v>
+        <v>3.937718166268994</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389346</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.738745531906706</v>
+        <v>-3.495343854036498</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.888172187772687</v>
+        <v>1.98553285892077</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7485207026371915</v>
+        <v>0.9446079138096602</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.833139246431432</v>
+        <v>3.950791573134913</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.831893003210073</v>
+        <v>-3.588491325339864</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.84291839603428</v>
+        <v>1.940279067182364</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6256914913546587</v>
+        <v>0.8217787025271275</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.751446916444852</v>
+        <v>3.869099243148333</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.859793790319546</v>
+        <v>-3.616392112449337</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.830282122317493</v>
+        <v>1.927642793465576</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5910945672117239</v>
+        <v>0.7871817783841927</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.729212803086093</v>
+        <v>3.846865129789574</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.982319893022439</v>
+        <v>-3.738918215152231</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.778036125213534</v>
+        <v>1.875396796361618</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4685684645088301</v>
+        <v>0.6646556756812988</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.652461585441555</v>
+        <v>3.770113912145037</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.212834389208028</v>
+        <v>-3.96943271133782</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.752536286329802</v>
+        <v>1.849896957477886</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2380539683232413</v>
+        <v>0.4341411794957101</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.580858847320706</v>
+        <v>3.698511174024187</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.561579474432472</v>
+        <v>-4.318177796562264</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.753349971241872</v>
+        <v>1.850710642389955</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1293060144043435</v>
+        <v>0.3253932255768123</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.655921793971214</v>
+        <v>3.773574120674696</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237091</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.715565892208613</v>
+        <v>-4.472164214338404</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.760735673277056</v>
+        <v>1.858096344425139</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1293060144043435</v>
+        <v>0.3253932255768123</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.724902063116854</v>
+        <v>3.842554389820335</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.665043988380947</v>
+        <v>-4.421642310510738</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.766995636928243</v>
+        <v>1.864356308076326</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1293060144043435</v>
+        <v>0.3253932255768123</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.710953265236975</v>
+        <v>3.828605591940456</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.917519142388671</v>
+        <v>-4.674117464518463</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.677876064380567</v>
+        <v>1.77523673552865</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1293060144043435</v>
+        <v>0.3253932255768123</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.722823754292389</v>
+        <v>3.84047608099587</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.210414898868083</v>
+        <v>-4.967013220997875</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.561928296307746</v>
+        <v>1.659288967455829</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1293060144043435</v>
+        <v>0.3253932255768123</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.724034288811333</v>
+        <v>3.841686615514814</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.397079027002891</v>
+        <v>-5.153677349132683</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.491384387281144</v>
+        <v>1.588745058429228</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1025670435797836</v>
+        <v>0.2986542547522524</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.712112648543918</v>
+        <v>3.8297649752474</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.543099713916853</v>
+        <v>-5.299698036046645</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.428053965251749</v>
+        <v>1.525414636399832</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.09348395178592667</v>
+        <v>0.2895711629583954</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.701740646203794</v>
+        <v>3.819392972907275</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.634813723026438</v>
+        <v>-5.39141204515623</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.553572418306959</v>
+        <v>1.650933089455042</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.09348395178592667</v>
+        <v>0.2895711629583954</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.863944702902838</v>
+        <v>3.981597029606319</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.666465382086407</v>
+        <v>-5.423063704216199</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.535758392646785</v>
+        <v>1.633119063794869</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.08831549454148646</v>
+        <v>0.2844027057139552</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.855690266519987</v>
+        <v>3.973342593223469</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.748400200355291</v>
+        <v>-5.504998522485082</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.513213882907723</v>
+        <v>1.610574554055806</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.07838074895440628</v>
+        <v>0.274467960126875</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.859958836736231</v>
+        <v>3.977611163439712</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.850376322603698</v>
+        <v>-5.60697464473349</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.481349072464262</v>
+        <v>1.578709743612346</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.0235953732940013</v>
+        <v>0.1724918378784674</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.807698801843089</v>
+        <v>3.92535112854657</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.740370039126477</v>
+        <v>-5.496968361256268</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.517504473099327</v>
+        <v>1.61486514424741</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.0003908013767260909</v>
+        <v>0.1956964097957427</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.813774432237629</v>
+        <v>3.93142675894111</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.597310463385551</v>
+        <v>-5.353908785515342</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.578978314117671</v>
+        <v>1.676338985265755</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.007622625213253187</v>
+        <v>0.2037098363857219</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.822832498913591</v>
+        <v>3.940484825617072</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.295863737913713</v>
+        <v>-5.052462060043505</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.706817887188942</v>
+        <v>1.804178558337026</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3090693506850904</v>
+        <v>0.5051565618575592</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.010961417079229</v>
+        <v>4.128613743782711</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.320453982148897</v>
+        <v>-5.077052304278689</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.697952967247579</v>
+        <v>1.795313638395663</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3090693506850904</v>
+        <v>0.5051565618575592</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.01193259483194</v>
+        <v>4.129584921535421</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.269415606142377</v>
+        <v>-5.026013928272168</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.719211222029943</v>
+        <v>1.816571893178026</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3090693506850904</v>
+        <v>0.5051565618575592</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.012775499211696</v>
+        <v>4.130427825915176</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.228276311275746</v>
+        <v>-4.984874633405537</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.754705038850741</v>
+        <v>1.852065709998824</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3502086455517213</v>
+        <v>0.54629585672419</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.05649717500582</v>
+        <v>4.174149501709301</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.131641399257106</v>
+        <v>-4.888239721386897</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.609542999782132</v>
+        <v>1.706903670930215</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4468435575703612</v>
+        <v>0.64293076874283</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.930662118340938</v>
+        <v>4.04831444504442</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.262222133787948</v>
+        <v>-5.01882045591774</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.560812750043759</v>
+        <v>1.658173421191842</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3162628230395187</v>
+        <v>0.5123500342119874</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.855815721696397</v>
+        <v>3.973468048399877</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.097725799596986</v>
+        <v>-4.854324121726778</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.611038102796226</v>
+        <v>1.708398773944309</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4807591572304806</v>
+        <v>0.6768463684029493</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.938940341287056</v>
+        <v>4.056592667990538</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.125095732281419</v>
+        <v>-4.88169405441121</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.599277840158883</v>
+        <v>1.696638511306966</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4807591572304806</v>
+        <v>0.6768463684029493</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.938128051723486</v>
+        <v>4.055780378426967</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.135480927171308</v>
+        <v>-4.8920792493011</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.604992541328</v>
+        <v>1.702353212476083</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4703739623405913</v>
+        <v>0.66646117351306</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.941765713914624</v>
+        <v>4.059418040618106</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.154069085893533</v>
+        <v>-4.910667408023325</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.668394283615534</v>
+        <v>1.765754954763618</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4517858036183659</v>
+        <v>0.6478730147908347</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.001449824457715</v>
+        <v>4.119102151161196</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.154367632589569</v>
+        <v>-4.91096595471936</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.665143875755418</v>
+        <v>1.762504546903502</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.45148725692233</v>
+        <v>0.6475744680947988</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.998139707258392</v>
+        <v>4.115792033961873</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.053544498899141</v>
+        <v>-4.810142821028933</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.710004024170981</v>
+        <v>1.807364695319065</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4639514724066838</v>
+        <v>0.6600386835791526</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.010149131488395</v>
+        <v>4.127801458191876</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.862763138146734</v>
+        <v>-4.619361460276526</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.786445821950487</v>
+        <v>1.883806493098571</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6547328331590911</v>
+        <v>0.85082004433156</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.124747201418383</v>
+        <v>4.242399528121864</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.844246284104914</v>
+        <v>-4.600844606234705</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.773689409304812</v>
+        <v>1.871050080452895</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6676629625842994</v>
+        <v>0.8637501737567682</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.112342124811105</v>
+        <v>4.229994451514586</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.788915696203151</v>
+        <v>-4.545514018332943</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.830788581077575</v>
+        <v>1.928149252225658</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7229935504860615</v>
+        <v>0.9190807616585304</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.180507414164221</v>
+        <v>4.298159740867701</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.776861569290189</v>
+        <v>-4.53345989141998</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.829296799744198</v>
+        <v>1.926657470892281</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7350476773990243</v>
+        <v>0.9311348885714932</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.181426458213435</v>
+        <v>4.299078784916917</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.81801668885841</v>
+        <v>-4.574615010988201</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.814715382101046</v>
+        <v>1.912076053249129</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6938925578308034</v>
+        <v>0.8899797690032722</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.158614016656639</v>
+        <v>4.27626634336012</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.715136099329817</v>
+        <v>-4.471734421459608</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.868718643790365</v>
+        <v>1.966079314938448</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7967731473593963</v>
+        <v>0.9928603585318652</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.233193396251677</v>
+        <v>4.350845722955158</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.946736492499317</v>
+        <v>-4.703334814629109</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.796281156696159</v>
+        <v>1.893641827844243</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7967731473593963</v>
+        <v>0.9928603585318652</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.253396066425271</v>
+        <v>4.371048393128753</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.964809000790929</v>
+        <v>-4.721407322920721</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.789052153379515</v>
+        <v>1.886412824527598</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7967731473593963</v>
+        <v>0.9928603585318652</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.253396066425271</v>
+        <v>4.371048393128753</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.139915833367374</v>
+        <v>-4.896514155497165</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.679261333942403</v>
+        <v>1.776622005090487</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7967731473593963</v>
+        <v>0.9928603585318652</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.213647980018738</v>
+        <v>4.33130030672222</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.108629812826918</v>
+        <v>-4.86522813495671</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.698798361155526</v>
+        <v>1.796159032303609</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8280591678998517</v>
+        <v>1.024146379072321</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.239442211339951</v>
+        <v>4.357094538043433</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.955604420713634</v>
+        <v>-4.712202742843425</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.859179517573744</v>
+        <v>1.956540188721827</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9810845600131358</v>
+        <v>1.177171771185605</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.430428446180827</v>
+        <v>4.548080772884307</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.983911734586904</v>
+        <v>-4.740510056716696</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.035322816932728</v>
+        <v>2.132683488080811</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9810845600131358</v>
+        <v>1.177171771185605</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.617894671089118</v>
+        <v>4.7355469977926</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.150504959700426</v>
+        <v>-4.907103281830218</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.938088478241401</v>
+        <v>2.035449149389485</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8144913348996135</v>
+        <v>1.010578546072082</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.487341687375087</v>
+        <v>4.604994014078568</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.977440580318127</v>
+        <v>-4.734038902447918</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.010990632656039</v>
+        <v>2.108351303804122</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8144913348996135</v>
+        <v>1.010578546072082</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.491018090036805</v>
+        <v>4.608670416740286</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.94819459986243</v>
+        <v>-4.704792921992222</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.020307079961813</v>
+        <v>2.117667751109896</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8144913348996135</v>
+        <v>1.010578546072082</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.4886361451603</v>
+        <v>4.606288471863781</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539102</v>
+        <v>3.699424827539104</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.055120147740281</v>
+        <v>-4.811718469870073</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.974830099968307</v>
+        <v>2.07219077111639</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7075657870217621</v>
+        <v>0.9036529981942308</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.421774055591224</v>
+        <v>4.539426382294706</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983732</v>
+        <v>3.689962785983734</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.20013870624753</v>
+        <v>-4.956737028377321</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.918251478708642</v>
+        <v>2.015612149856725</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5625472285145136</v>
+        <v>0.7586344396869823</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.33619172263011</v>
+        <v>4.453844049333591</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969744</v>
+        <v>3.711872614969745</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.318480472032247</v>
+        <v>-5.075078794162039</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.970846011652508</v>
+        <v>2.068206682800591</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5732332670774036</v>
+        <v>0.7693204782498724</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.442534585025596</v>
+        <v>4.560186911729078</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073533</v>
+        <v>3.714899237073535</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.369890894352955</v>
+        <v>-5.126489216482747</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.948067539850163</v>
+        <v>2.045428210998247</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5732332670774036</v>
+        <v>0.7693204782498724</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.440320282151535</v>
+        <v>4.557972608855017</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70477813472006</v>
+        <v>3.704778134720062</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.449310345560707</v>
+        <v>-5.205908667690498</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.916202887441352</v>
+        <v>2.013563558589436</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5732332670774036</v>
+        <v>0.7693204782498724</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.440223410225824</v>
+        <v>4.557875736929306</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581127</v>
+        <v>3.736825137581129</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.544773343477924</v>
+        <v>-5.301371665607716</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.878011581832509</v>
+        <v>1.975372252980592</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5732332670774036</v>
+        <v>0.7693204782498724</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.440217303783868</v>
+        <v>4.55786963048735</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500729</v>
+        <v>3.715393145500731</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.584793341521708</v>
+        <v>-5.3413916636515</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.860099979177606</v>
+        <v>1.957460650325689</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.5332132690336198</v>
+        <v>0.7293004802060885</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.414301701520208</v>
+        <v>4.53195402822369</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636265</v>
+        <v>3.736109598636267</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.640162503653902</v>
+        <v>-5.396760825783693</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.843686132072455</v>
+        <v>1.941046803220539</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.5332132690336198</v>
+        <v>0.7293004802060885</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.420035519267935</v>
+        <v>4.537687845971417</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396008</v>
+        <v>3.73684305539601</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.685600283484729</v>
+        <v>-5.442198605614521</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.825049383483057</v>
+        <v>1.92241005463114</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.4903682783554602</v>
+        <v>0.6864554895279289</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.393866888203973</v>
+        <v>4.511519214907453</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396417</v>
+        <v>3.790292685396419</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.602374826637065</v>
+        <v>-5.358973148766856</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.878213959072442</v>
+        <v>1.975574630220525</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.4903682783554602</v>
+        <v>0.6864554895279289</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.413741281054292</v>
+        <v>4.531393607757773</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299171</v>
+        <v>3.794507029299173</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.426084602031757</v>
+        <v>-5.182682924161549</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.932430749439292</v>
+        <v>2.029791420587376</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.4903682783554602</v>
+        <v>0.6864554895279289</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.39744198157902</v>
+        <v>4.5150943082825</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590402</v>
+        <v>3.794725278590404</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.242872938898662</v>
+        <v>-4.999471261028454</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.008146364156576</v>
+        <v>2.10550703530466</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.4903682783554602</v>
+        <v>0.6864554895279289</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.399872931043065</v>
+        <v>4.517525257746546</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146281</v>
+        <v>3.776866743146282</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.171151491884811</v>
+        <v>-4.927749814014603</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.002626128810006</v>
+        <v>2.099986799958089</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.5620897253693108</v>
+        <v>0.7581769365417795</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.408696985099264</v>
+        <v>4.526349311802746</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676846</v>
+        <v>3.723809890676847</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.300530274524589</v>
+        <v>-5.147144682126132</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.897790361675267</v>
+        <v>1.959144598634649</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.5199879526621074</v>
+        <v>0.6863446349011448</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.330351667396114</v>
+        <v>4.430165676739537</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.862651538391607</v>
+        <v>3.861947350949959</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.187901821097963</v>
+        <v>4.398698097898717</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.300530274524589</v>
+        <v>-5.147144682126132</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.897790361675267</v>
+        <v>1.959144598634649</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5199879526621074</v>
+        <v>0.6863446349011448</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.180965618084331</v>
+        <v>4.391761894885085</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240828.xlsx
+++ b/tame_output/ON/bt/strategyON_20240828.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>50.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,27 +834,27 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>128.2%</t>
+          <t>100.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.2%</t>
+          <t>125.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-39.9%</t>
+          <t>-13.1%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-48.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.9%</t>
+          <t>424.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-676.3%</t>
+          <t>-686.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-180.3%</t>
+          <t>-174.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>117.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-295.5%</t>
+          <t>-292.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-155.4%</t>
+          <t>-165.3%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.1%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>1.5%</t>
         </is>
       </c>
     </row>
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.195317405826184</v>
+        <v>-5.329184830008393</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.038195589284692</v>
+        <v>0.9846486196118076</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.2235950597255912</v>
+        <v>-0.3313998427407806</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.982521940093558</v>
+        <v>2.917839070284444</v>
       </c>
     </row>
     <row r="1864">
@@ -44420,19 +44420,19 @@
         <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.115440519943672</v>
+        <v>3.297551015812623</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.603906183006862</v>
+        <v>-5.737773607189072</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8735216224271789</v>
+        <v>1.002085148623247</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.6321838369062697</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.73613021779991</v>
+        <v>2.853557843859748</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.110625952415132</v>
+        <v>3.292736448284083</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.717666595029727</v>
+        <v>-5.851534019211937</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.8232028900894939</v>
+        <v>0.9517664162855608</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.6321838369062697</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.731315650271371</v>
+        <v>2.848743276331208</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.10862000302401</v>
+        <v>3.290730498892961</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.134058469316725</v>
+        <v>-6.267925893498934</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6546401909835722</v>
+        <v>0.7832037171796391</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.6321838369062697</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.729309700880248</v>
+        <v>2.846737326940086</v>
       </c>
     </row>
     <row r="1867">
@@ -44489,19 +44489,19 @@
         <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.118878693692689</v>
+        <v>3.30098918956164</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.495232099133712</v>
+        <v>-6.629099523315922</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5204294297254561</v>
+        <v>0.6489929559215231</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.6321838369062697</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.739568391548927</v>
+        <v>2.856996017608765</v>
       </c>
     </row>
     <row r="1868">
@@ -44512,19 +44512,19 @@
         <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.114978258838384</v>
+        <v>3.297088754707335</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.838490618776731</v>
+        <v>-6.972358042958941</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3792255870139436</v>
+        <v>0.5077891132100105</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.6321838369062697</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.735667956694622</v>
+        <v>2.85309558275446</v>
       </c>
     </row>
     <row r="1869">
@@ -44535,19 +44535,19 @@
         <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.113383178893385</v>
+        <v>3.295493674762336</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.886693436019075</v>
+        <v>-7.020560860201285</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3583493801720068</v>
+        <v>0.4869129063680742</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.6321838369062697</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.734072876749623</v>
+        <v>2.85150050280946</v>
       </c>
     </row>
     <row r="1870">
@@ -44558,19 +44558,19 @@
         <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.117162154822593</v>
+        <v>3.299272650691544</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.183354777829273</v>
+        <v>-7.317222202011482</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2434638193771361</v>
+        <v>0.3720273455732035</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.7009269726401482</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.696605971238504</v>
+        <v>2.814033597298342</v>
       </c>
     </row>
     <row r="1871">
@@ -44581,19 +44581,19 @@
         <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.11313585028819</v>
+        <v>3.295246346157141</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.370074486138575</v>
+        <v>-7.503941910320785</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1647496315190118</v>
+        <v>0.2933131577150792</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.7009269726401482</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.692579666704101</v>
+        <v>2.810007292763939</v>
       </c>
     </row>
     <row r="1872">
@@ -44604,19 +44604,19 @@
         <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.113033748966606</v>
+        <v>3.295144244835557</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.753075874881207</v>
+        <v>-7.886943299063416</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.01144697470037537</v>
+        <v>0.1400105008964427</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.7009269726401482</v>
+        <v>-0.8087317556553376</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.692477565382517</v>
+        <v>2.809905191442355</v>
       </c>
     </row>
     <row r="1873">
@@ -44627,19 +44627,19 @@
         <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.115605264938036</v>
+        <v>3.297715760806987</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.757562320082595</v>
+        <v>-7.891429744264805</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.01222391259125022</v>
+        <v>0.1407874387873171</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.705413417841537</v>
+        <v>-0.8132182008567264</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.692357214233114</v>
+        <v>2.809784840292951</v>
       </c>
     </row>
     <row r="1874">
@@ -44650,19 +44650,19 @@
         <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.120955568236086</v>
+        <v>3.303066064105037</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.117092642586599</v>
+        <v>-8.250960066768808</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1262379131123006</v>
+        <v>0.002325613083766331</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.705413417841537</v>
+        <v>-0.8132182008567264</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.697707517531164</v>
+        <v>2.815135143591001</v>
       </c>
     </row>
     <row r="1875">
@@ -44673,19 +44673,19 @@
         <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.128871588193264</v>
+        <v>3.310982084062215</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.167441706040821</v>
+        <v>-8.30130913022303</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1384615185368121</v>
+        <v>-0.009897992340744732</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.7557624812957591</v>
+        <v>-0.8635672643109484</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.675414099415808</v>
+        <v>2.792841725475646</v>
       </c>
     </row>
     <row r="1876">
@@ -44696,19 +44696,19 @@
         <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.131913338815032</v>
+        <v>3.314023834683983</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.265060983462217</v>
+        <v>-8.398928407644426</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1744674788836016</v>
+        <v>-0.04590395268753467</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.8533817587171557</v>
+        <v>-0.9611865417323451</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.619884283584739</v>
+        <v>2.737311909644577</v>
       </c>
     </row>
     <row r="1877">
@@ -44719,19 +44719,19 @@
         <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.134806895136605</v>
+        <v>3.316917391005556</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.319132482970575</v>
+        <v>-8.452999907152785</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1932025223653731</v>
+        <v>-0.06463899616930568</v>
       </c>
       <c r="F1877" t="n">
-        <v>-0.9074532582255151</v>
+        <v>-1.015258041240704</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.590334940201296</v>
+        <v>2.707762566261133</v>
       </c>
     </row>
     <row r="1878">
@@ -44742,19 +44742,19 @@
         <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.140320092255247</v>
+        <v>3.322430588124198</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.523390658300439</v>
+        <v>-8.657258082482649</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.269392595378676</v>
+        <v>-0.1408290691826091</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.035092202839504</v>
+        <v>-1.142896985854693</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.519264770551545</v>
+        <v>2.636692396611382</v>
       </c>
     </row>
     <row r="1879">
@@ -44765,19 +44765,19 @@
         <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.144802646739683</v>
+        <v>3.326913142608634</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.557043496808912</v>
+        <v>-8.690910920991122</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2783711762976293</v>
+        <v>-0.1498076501015624</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.135505570756541</v>
+        <v>-1.243310353771731</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.463499304285758</v>
+        <v>2.580926930345596</v>
       </c>
     </row>
     <row r="1880">
@@ -44788,19 +44788,19 @@
         <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.160174348233104</v>
+        <v>3.342284844102055</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.69612961142777</v>
+        <v>-8.82999703560998</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.318633920651751</v>
+        <v>-0.1900703944556841</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.274591685375398</v>
+        <v>-1.382396468390588</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.395419337007866</v>
+        <v>2.512846963067703</v>
       </c>
     </row>
     <row r="1881">
@@ -44811,19 +44811,19 @@
         <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.174729568980621</v>
+        <v>3.356840064849572</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.871254028814313</v>
+        <v>-9.005121452996523</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3741284668588518</v>
+        <v>-0.2455649406627844</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.449716102761942</v>
+        <v>-1.557520885777131</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.304899907323456</v>
+        <v>2.422327533383293</v>
       </c>
     </row>
     <row r="1882">
@@ -44834,19 +44834,19 @@
         <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.167510404079025</v>
+        <v>3.349620899947976</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.105706122828803</v>
+        <v>-9.239573547011013</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4751284693662434</v>
+        <v>-0.3465649431701765</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.449716102761942</v>
+        <v>-1.557520885777131</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.29768074242186</v>
+        <v>2.415108368481698</v>
       </c>
     </row>
     <row r="1883">
@@ -44857,19 +44857,19 @@
         <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.160838213305049</v>
+        <v>3.342948709174</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.210080853855249</v>
+        <v>-9.343948278037459</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5235505525507982</v>
+        <v>-0.3949870263547313</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.554090833788388</v>
+        <v>-1.661895616803577</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.228383713032017</v>
+        <v>2.345811339091854</v>
       </c>
     </row>
     <row r="1884">
@@ -44880,19 +44880,19 @@
         <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.161954003143605</v>
+        <v>3.344064499012556</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.372594319553833</v>
+        <v>-9.506461743736043</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5874401489916758</v>
+        <v>-0.4588766227956085</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.651724264207075</v>
+        <v>-1.759529047222264</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.17091944461936</v>
+        <v>2.288347070679198</v>
       </c>
     </row>
     <row r="1885">
@@ -44903,19 +44903,19 @@
         <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.16464773177272</v>
+        <v>3.346758227641671</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.498631112922123</v>
+        <v>-9.632498537104333</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6351611377098769</v>
+        <v>-0.5065976115138096</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.626472641397332</v>
+        <v>-1.734277424412522</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.188764146934321</v>
+        <v>2.306191772994158</v>
       </c>
     </row>
     <row r="1886">
@@ -44926,19 +44926,19 @@
         <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.168638067459121</v>
+        <v>3.350748563328072</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.441559341026192</v>
+        <v>-9.575426765208402</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6083420932651036</v>
+        <v>-0.4797785670690367</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.626472641397332</v>
+        <v>-1.734277424412522</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.192754482620721</v>
+        <v>2.310182108680559</v>
       </c>
     </row>
     <row r="1887">
@@ -44949,19 +44949,19 @@
         <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.167162840560379</v>
+        <v>3.34927333642933</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.583231182750312</v>
+        <v>-9.717098606932522</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6664860568534934</v>
+        <v>-0.5379225306574265</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.626472641397332</v>
+        <v>-1.734277424412522</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.19127925572198</v>
+        <v>2.308706881781817</v>
       </c>
     </row>
     <row r="1888">
@@ -44972,19 +44972,19 @@
         <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.182216250725251</v>
+        <v>3.364326746594202</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.533640338325478</v>
+        <v>-9.667507762507688</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6315963089186876</v>
+        <v>-0.5030327827226202</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.576881796972498</v>
+        <v>-1.684686579987688</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.236087172541752</v>
+        <v>2.35351479860159</v>
       </c>
     </row>
     <row r="1889">
@@ -44995,19 +44995,19 @@
         <v>3.676841549770576</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.169165117078568</v>
+        <v>3.351275612947519</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.384722003853621</v>
+        <v>-9.518589428035831</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5850801087766277</v>
+        <v>-0.4565165825805608</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.545632206237325</v>
+        <v>-1.653436989252515</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.241785793336173</v>
+        <v>2.359213419396011</v>
       </c>
     </row>
     <row r="1890">
@@ -45018,19 +45018,19 @@
         <v>3.685161381615279</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.178744190114777</v>
+        <v>3.360854685983728</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.15887685113421</v>
+        <v>-9.292744275316419</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4851629746526545</v>
+        <v>-0.3565994484565871</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.503705530650162</v>
+        <v>-1.611510313665351</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.27652087172468</v>
+        <v>2.393948497784518</v>
       </c>
     </row>
     <row r="1891">
@@ -45041,19 +45041,19 @@
         <v>3.684843823812099</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.179883334670836</v>
+        <v>3.361993830539787</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.034298194796618</v>
+        <v>-9.168165618978827</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4341923675615589</v>
+        <v>-0.3056288413654915</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.503705530650162</v>
+        <v>-1.611510313665351</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.277660016280739</v>
+        <v>2.395087642340576</v>
       </c>
     </row>
     <row r="1892">
@@ -45064,19 +45064,19 @@
         <v>3.710935533646213</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.182517108832943</v>
+        <v>3.364627604701894</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.009261513228108</v>
+        <v>-9.143128937410317</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4215439207720468</v>
+        <v>-0.2929803945759799</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.478376443099426</v>
+        <v>-1.586181226114615</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.295491242973288</v>
+        <v>2.412918869033125</v>
       </c>
     </row>
     <row r="1893">
@@ -45087,19 +45087,19 @@
         <v>3.768951674611564</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.18825081307158</v>
+        <v>3.370361308940531</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.937128337940226</v>
+        <v>-9.070995762122436</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3869569464182581</v>
+        <v>-0.2583934202221911</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.478376443099426</v>
+        <v>-1.586181226114615</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.301224947211924</v>
+        <v>2.418652573271762</v>
       </c>
     </row>
     <row r="1894">
@@ -45110,19 +45110,19 @@
         <v>3.728577929955324</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.178513550677715</v>
+        <v>3.360624046546666</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.865761945330579</v>
+        <v>-8.999629369512789</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3681476517682643</v>
+        <v>-0.2395841255721973</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.407010050489778</v>
+        <v>-1.514814833504967</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.334307520383848</v>
+        <v>2.451735146443686</v>
       </c>
     </row>
     <row r="1895">
@@ -45133,19 +45133,19 @@
         <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.168630069364807</v>
+        <v>3.350740565233758</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.772302911345355</v>
+        <v>-8.906170335527564</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3406475194870819</v>
+        <v>-0.212083993291015</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.407010050489778</v>
+        <v>-1.514814833504967</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.324424039070941</v>
+        <v>2.441851665130778</v>
       </c>
     </row>
     <row r="1896">
@@ -45156,19 +45156,19 @@
         <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.166795508865433</v>
+        <v>3.348906004734384</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.669699449392535</v>
+        <v>-8.895517153974133</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3014406952053279</v>
+        <v>-0.2096572811690161</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.407010050489778</v>
+        <v>-1.514814833504967</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.322589478571567</v>
+        <v>2.440017104631404</v>
       </c>
     </row>
     <row r="1897">
@@ -45179,19 +45179,19 @@
         <v>3.784684521311945</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.166495193891973</v>
+        <v>3.348605689760924</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.571792410716045</v>
+        <v>-8.797610115297642</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2625781947081927</v>
+        <v>-0.1707947806718808</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.339024300629222</v>
+        <v>-1.446829083644411</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.36308061351444</v>
+        <v>2.480508239574277</v>
       </c>
     </row>
     <row r="1898">
@@ -45202,19 +45202,19 @@
         <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.167163700037466</v>
+        <v>3.349274195906417</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.547838869740087</v>
+        <v>-8.773656574321684</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2523282721723157</v>
+        <v>-0.1605448581360038</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.315070759653264</v>
+        <v>-1.422875542668453</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.378121244245508</v>
+        <v>2.495548870305345</v>
       </c>
     </row>
     <row r="1899">
@@ -45225,19 +45225,19 @@
         <v>3.789311112017767</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.153903383875714</v>
+        <v>3.336013879744665</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.28377893141729</v>
+        <v>-8.509596635998887</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1599646130049495</v>
+        <v>-0.06818119896863717</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.051010821330468</v>
+        <v>-1.158815604345657</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.523296891077433</v>
+        <v>2.640724517137271</v>
       </c>
     </row>
     <row r="1900">
@@ -45248,19 +45248,19 @@
         <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.151116350215413</v>
+        <v>3.333226846084364</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.576699307912452</v>
+        <v>-7.802517012494049</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.120080202736685</v>
+        <v>0.2118636167729973</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.051010821330468</v>
+        <v>-1.158815604345657</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.520509857417133</v>
+        <v>2.63793748347697</v>
       </c>
     </row>
     <row r="1901">
@@ -45271,19 +45271,19 @@
         <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.151459974103255</v>
+        <v>3.333570469972206</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.536515009546261</v>
+        <v>-7.762332714127859</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1364975459710025</v>
+        <v>0.2282809600073148</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.010826522964277</v>
+        <v>-1.118631305979466</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.544964060324689</v>
+        <v>2.662391686384526</v>
       </c>
     </row>
     <row r="1902">
@@ -45294,19 +45294,19 @@
         <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.150826795324011</v>
+        <v>3.332937291192962</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.373115138606899</v>
+        <v>-7.598932843188496</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2012243155675044</v>
+        <v>0.2930077296038167</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8474266520249145</v>
+        <v>-0.9552314350401039</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.642370804109063</v>
+        <v>2.7597984301689</v>
       </c>
     </row>
     <row r="1903">
@@ -45317,19 +45317,19 @@
         <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.158751224161864</v>
+        <v>3.340861720030815</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.1396339163773</v>
+        <v>-7.365451620958898</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3025412332971964</v>
+        <v>0.3943246473335082</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.613945429795316</v>
+        <v>-0.7217502128105053</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.790383966284674</v>
+        <v>2.907811592344512</v>
       </c>
     </row>
     <row r="1904">
@@ -45340,19 +45340,19 @@
         <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.155859013848905</v>
+        <v>3.337969509717856</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.989967525369785</v>
+        <v>-7.215785229951383</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3595155793872431</v>
+        <v>0.4512989934235554</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.52104193855278</v>
+        <v>-0.6288467215679694</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.843233850717237</v>
+        <v>2.960661476777074</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.057119799856059</v>
+        <v>3.23923029572501</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.857692051738899</v>
+        <v>-7.083509756320496</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3136865548467527</v>
+        <v>0.4054699688830645</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3887664649218934</v>
+        <v>-0.4965712479370827</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.823859920902923</v>
+        <v>2.941287546962761</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.059934860543696</v>
+        <v>3.242045356412647</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.701953719179157</v>
+        <v>-6.927771423760754</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3787969485582861</v>
+        <v>0.4705803625945979</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.2330281323621518</v>
+        <v>-0.3408329153773412</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.920117981126405</v>
+        <v>3.037545607186243</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.072841201767355</v>
+        <v>3.254951697636306</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.616989052449837</v>
+        <v>-6.842806757031434</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4256891564736729</v>
+        <v>0.5174725705099847</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1480634656328322</v>
+        <v>-0.2558682486480216</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.984003122387656</v>
+        <v>3.101430748447493</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.944865272168136</v>
+        <v>3.126975768037087</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.722579042222941</v>
+        <v>-6.948396746804539</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2554772309652122</v>
+        <v>0.3472606450015241</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2536534554059366</v>
+        <v>-0.361458238421126</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.792673198924574</v>
+        <v>2.910100824984412</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987899</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.993409614045222</v>
+        <v>3.175520109914173</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.654344457597514</v>
+        <v>-6.880162162179111</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3313154066924695</v>
+        <v>0.4230988207287814</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.2352381325334006</v>
+        <v>-0.34304291554859</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.852266734525182</v>
+        <v>2.96969436058502</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.876788805406815</v>
+        <v>3.058899301275766</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.506404416189914</v>
+        <v>-6.732222120771512</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2738706146171022</v>
+        <v>0.365654028653414</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.214917216624843</v>
+        <v>-0.3227219996400324</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.74783847543191</v>
+        <v>2.865266101491747</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.868074819153337</v>
+        <v>3.050185315022288</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.453434893935926</v>
+        <v>-6.679252598517524</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2863444372652193</v>
+        <v>0.3781278513015316</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1619476943708542</v>
+        <v>-0.2697524773860435</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.770906202530825</v>
+        <v>2.888333828590662</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.861114207058244</v>
+        <v>3.043224702927195</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.287646697975635</v>
+        <v>-6.513464402557233</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3456991035542427</v>
+        <v>0.4374825175905546</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1619476943708542</v>
+        <v>-0.2697524773860435</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.763945590435732</v>
+        <v>2.881373216495569</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.875576561439387</v>
+        <v>3.057687057308338</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.254283491496866</v>
+        <v>-6.480101196078464</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.373506740526893</v>
+        <v>0.4652901545632053</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1619476943708542</v>
+        <v>-0.2697524773860435</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.778407944816875</v>
+        <v>2.895835570876712</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.870108681898582</v>
+        <v>3.052219177767533</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.146024354374345</v>
+        <v>-6.371842058955942</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4113425158350967</v>
+        <v>0.503125929871409</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1619476943708542</v>
+        <v>-0.2697524773860435</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.77294006527607</v>
+        <v>2.890367691335907</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.867606775909159</v>
+        <v>3.04971727177811</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.022733219557214</v>
+        <v>-6.248550924138812</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4581570637725263</v>
+        <v>0.5499404778088381</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.03865655955372366</v>
+        <v>-0.146461342568913</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.844412840176925</v>
+        <v>2.961840466236763</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.875307754146484</v>
+        <v>3.057418250015435</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.970036352425923</v>
+        <v>-6.19585405700752</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4869367888623679</v>
+        <v>0.5787202028986798</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.01404030757756752</v>
+        <v>-0.09376447543762184</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.883731938693025</v>
+        <v>3.001159564752862</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.871088462493535</v>
+        <v>3.053198958362486</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.726270910442478</v>
+        <v>-5.952088615024076</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5802236740027964</v>
+        <v>0.6720070880391082</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.01404030757756752</v>
+        <v>-0.09376447543762184</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.879512647040076</v>
+        <v>2.996940273099913</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.873212776413551</v>
+        <v>3.055323272282502</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.636495238066006</v>
+        <v>-5.862312942647604</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6182582568734012</v>
+        <v>0.710041670909713</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.07563975249187754</v>
+        <v>-0.03216503052331182</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.918596627908677</v>
+        <v>3.036024253968515</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.865954851397253</v>
+        <v>3.048065347266204</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.386644844116931</v>
+        <v>-5.612462548698529</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7109404894367333</v>
+        <v>0.8027239034730451</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.07563975249187754</v>
+        <v>-0.03216503052331182</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.91133870289238</v>
+        <v>3.028766328952217</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.869553974917902</v>
+        <v>3.051664470786853</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.210752751649499</v>
+        <v>-5.436570456231097</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7848964499443549</v>
+        <v>0.8766798639806668</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.07563975249187754</v>
+        <v>-0.03216503052331182</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.914937826413028</v>
+        <v>3.032365452472866</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.882881480972455</v>
+        <v>3.064991976841406</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.039306288627036</v>
+        <v>-5.265123993208634</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8668025412078939</v>
+        <v>0.9585859552442058</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2470862155143407</v>
+        <v>0.1392814324991513</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.03113321028106</v>
+        <v>3.148560836340898</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632777</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.881901958588752</v>
+        <v>3.064012454457703</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.959284001517915</v>
+        <v>-5.185101706099513</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8978319336678391</v>
+        <v>0.9896153477041509</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3271085026234616</v>
+        <v>0.2193037196082723</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.078167060162829</v>
+        <v>3.195594686222667</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.88659675964307</v>
+        <v>3.068707255512021</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.895648259283981</v>
+        <v>-5.121465963865578</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9279810316157302</v>
+        <v>1.019764445652042</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3907442448573962</v>
+        <v>0.2829394618422068</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.121043306557508</v>
+        <v>3.238470932617345</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.867791018426865</v>
+        <v>3.049901514295816</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.801950941067585</v>
+        <v>-5.027768645649183</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9466542176860839</v>
+        <v>1.038437631722396</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3907442448573962</v>
+        <v>0.2829394618422068</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.102237565341303</v>
+        <v>3.219665191401141</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.869534095051743</v>
+        <v>3.051644590920694</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.724171135975595</v>
+        <v>-5.038271268714472</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9795092163477572</v>
+        <v>1.035979659121158</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4685240499493864</v>
+        <v>0.2724368387769179</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.150648525021375</v>
+        <v>3.215106694186845</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.873463408886563</v>
+        <v>3.055573904755514</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.651928567804401</v>
+        <v>-4.97693122125607</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.012335557451055</v>
+        <v>1.064444991939339</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4685240499493864</v>
+        <v>0.2724368387769179</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.154577838856195</v>
+        <v>3.219036008021665</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.82232699787996</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.874141992803903</v>
+        <v>3.056252488672854</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.634214880926535</v>
+        <v>-4.959217534378205</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.020099616119541</v>
+        <v>1.072209050607825</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4717053788463032</v>
+        <v>0.2756181676738347</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.157165220111685</v>
+        <v>3.221623389277155</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.871140064023896</v>
+        <v>3.053250559892847</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.525409995446808</v>
+        <v>-4.850412648898478</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.060619641531426</v>
+        <v>1.112729076019709</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4717053788463032</v>
+        <v>0.2756181676738347</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.154163291331678</v>
+        <v>3.218621460497149</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675934</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.872719101034511</v>
+        <v>3.054829596903462</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.305389197409798</v>
+        <v>-4.630391850861467</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.150206997756844</v>
+        <v>1.202316432245127</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.6129252239142834</v>
+        <v>0.416838012741815</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.240474235383081</v>
+        <v>3.304932404548551</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539946</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.888613283836334</v>
+        <v>3.070723779705285</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.17252150834652</v>
+        <v>-4.497524161798189</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.219248256183979</v>
+        <v>1.271357690672262</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.6129252239142834</v>
+        <v>0.416838012741815</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.256368418184904</v>
+        <v>3.320826587350374</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.889759128276636</v>
+        <v>3.071869624145587</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.052348424982021</v>
+        <v>-4.377351078433691</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.26846333397008</v>
+        <v>1.320572768458363</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7330983072787823</v>
+        <v>0.5370110961063139</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.329618112643905</v>
+        <v>3.394076281809375</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.899847230838076</v>
+        <v>3.081957726707027</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.917095063652044</v>
+        <v>-4.242097717103714</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.332652781063511</v>
+        <v>1.384762215551794</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8683516686087595</v>
+        <v>0.672264457436291</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.420858232003332</v>
+        <v>3.485316401168801</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.885884722239501</v>
+        <v>3.067995218108452</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.976969891009737</v>
+        <v>-4.301972544461406</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.294740341521859</v>
+        <v>1.346849776010143</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.8084768412510673</v>
+        <v>0.6123896300785989</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.370970826990142</v>
+        <v>3.435428996155612</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.90117389147371</v>
+        <v>3.083284387342661</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.857149660098899</v>
+        <v>-4.182152313550569</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.357957603120403</v>
+        <v>1.410067037608686</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.8084768412510673</v>
+        <v>0.6123896300785989</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.38625999622435</v>
+        <v>3.450718165389821</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.808818090796152</v>
+        <v>2.990928586665103</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.859619366560705</v>
+        <v>-4.184622020012375</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.264613919858122</v>
+        <v>1.316723354346405</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.8060071347892611</v>
+        <v>0.6099199236167927</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.292422371669709</v>
+        <v>3.356880540835178</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003597</v>
+        <v>3.743220196003596</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.728079952281453</v>
+        <v>2.910190448150404</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.927989552884715</v>
+        <v>-4.252992206336385</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.15652770681382</v>
+        <v>1.208637141302103</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.8152828338254761</v>
+        <v>0.6191956226530076</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.217249652576739</v>
+        <v>3.281707821742209</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.718516660913344</v>
+        <v>2.900627156782295</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.039861832510866</v>
+        <v>-4.364864485962536</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.102215503595251</v>
+        <v>1.154324938083534</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.8152828338254761</v>
+        <v>0.6191956226530076</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.20768636120863</v>
+        <v>3.2721445303741</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.855547497605547</v>
+        <v>3.037657993474498</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.095381908403455</v>
+        <v>-4.420384561855125</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.217038309930417</v>
+        <v>1.2691477444187</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.8152828338254761</v>
+        <v>0.6191956226530076</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.344717197900832</v>
+        <v>3.409175367066303</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205894</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.860114729597334</v>
+        <v>3.042225225466285</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.919907648610986</v>
+        <v>-4.438226695660378</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.291795245839193</v>
+        <v>1.266578122888387</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.8152828338254761</v>
+        <v>0.6191956226530076</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.34928442989262</v>
+        <v>3.41374259905809</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.835856758358541</v>
+        <v>3.017967254227492</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.911983274026072</v>
+        <v>-4.430302321075464</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.270707024434365</v>
+        <v>1.245489901483559</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.8152828338254761</v>
+        <v>0.6191956226530076</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.325026458653827</v>
+        <v>3.389484627819297</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.764395071759991</v>
+        <v>2.946505567628942</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.905705071456223</v>
+        <v>-4.424024118505615</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.201756618863755</v>
+        <v>1.176539495912949</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.8215610363953251</v>
+        <v>0.6254738252228567</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.257331693597187</v>
+        <v>3.321789862762656</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.774567458192124</v>
+        <v>2.956677954061075</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.8458524522525</v>
+        <v>-4.364171499301892</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.235870052977377</v>
+        <v>1.21065293002657</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.8215610363953251</v>
+        <v>0.6254738252228567</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.267504080029319</v>
+        <v>3.331962249194789</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.769513728765984</v>
+        <v>2.951624224634935</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.759608989226122</v>
+        <v>-4.277928036275514</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.265313708761788</v>
+        <v>1.240096585810982</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.8215610363953251</v>
+        <v>0.6254738252228567</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.262450350603179</v>
+        <v>3.326908519768649</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316044</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.761289504210509</v>
+        <v>2.94340000007946</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.804915808625102</v>
+        <v>-4.323234855674494</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.238966756446721</v>
+        <v>1.213749633495915</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7807508733860943</v>
+        <v>0.5846636622136259</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.229740028242166</v>
+        <v>3.294198197407636</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.761841377243611</v>
+        <v>2.943951873112562</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.833948913327404</v>
+        <v>-4.352267960376795</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.227905387598902</v>
+        <v>1.202688264648097</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7807508733860943</v>
+        <v>0.5846636622136259</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.230291901275268</v>
+        <v>3.294750070440738</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.691114069134977</v>
+        <v>2.873224565003928</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.741138431876545</v>
+        <v>-4.259457478925936</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.194302272070612</v>
+        <v>1.169085149119806</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8735613548369536</v>
+        <v>0.6774741436644852</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.215250882037149</v>
+        <v>3.279709051202619</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560423</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.692987545059577</v>
+        <v>2.875098040928528</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.785527901205972</v>
+        <v>-4.303846948255363</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.178419960263441</v>
+        <v>1.153202837312636</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.829171885507526</v>
+        <v>0.6330846743350576</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.190490676364093</v>
+        <v>3.254948845529563</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.6880632535713</v>
+        <v>2.870173749440251</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.902069506311315</v>
+        <v>-4.420388553360706</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.126879026733027</v>
+        <v>1.101661903782222</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7126302804021832</v>
+        <v>0.5165430692297148</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.115641421812611</v>
+        <v>3.18009959097808</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.693554549401968</v>
+        <v>2.875665045270919</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.941993600893887</v>
+        <v>-4.460312647943278</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.116400684730666</v>
+        <v>1.09118356177986</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7126302804021832</v>
+        <v>0.5165430692297148</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.121132717643278</v>
+        <v>3.185590886808748</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.68959784049886</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.705051751170507</v>
+        <v>2.887162247039458</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.96977399879524</v>
+        <v>-4.48809304584463</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.116785727338664</v>
+        <v>1.091568604387858</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6848498825008301</v>
+        <v>0.4887626713283617</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.115961680671005</v>
+        <v>3.180419849836475</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.64306962170532</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.54340747117116</v>
+        <v>2.725517967040111</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.088154671525378</v>
+        <v>-4.606473718574769</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9077891782472616</v>
+        <v>0.8825720552964562</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6176320303498539</v>
+        <v>0.4215448191773855</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.913986689381073</v>
+        <v>2.978444858546543</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729264</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.663557131890366</v>
+        <v>2.845667627759317</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.196768749968709</v>
+        <v>-4.7150877970181</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9844932075891348</v>
+        <v>0.9592760846383295</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6176320303498539</v>
+        <v>0.4215448191773855</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.034136350100278</v>
+        <v>3.098594519265748</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190764</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.678070157992689</v>
+        <v>2.86018065386164</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.161359711720566</v>
+        <v>-4.679678758769957</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.013169848990715</v>
+        <v>0.9879527260399095</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6176320303498539</v>
+        <v>0.4215448191773855</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.048649376202601</v>
+        <v>3.113107545368071</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.675489599335057</v>
+        <v>2.857600095204008</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.122976049162415</v>
+        <v>-4.641295096211806</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.025942755356344</v>
+        <v>1.000725632405539</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6560156929080051</v>
+        <v>0.4599284817355367</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.06909901507986</v>
+        <v>3.133557184245331</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.672218628180359</v>
+        <v>2.85432912404931</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.945859719127249</v>
+        <v>-4.46417876617664</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.093518316215712</v>
+        <v>1.068301193264907</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6560156929080051</v>
+        <v>0.4599284817355367</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.065828043925162</v>
+        <v>3.130286213090633</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.672902019942272</v>
+        <v>2.855012515811223</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.990951963960795</v>
+        <v>-4.509271011010186</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.076164810044207</v>
+        <v>1.050947687093402</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5941196497386153</v>
+        <v>0.3980324385661469</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.029373809785442</v>
+        <v>3.093831978950912</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.666688995248687</v>
+        <v>2.848799491117638</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.811576542722027</v>
+        <v>-4.329895589771418</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.141701953846129</v>
+        <v>1.116484830895323</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.750896407909334</v>
+        <v>0.5548091967368656</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.117226839994287</v>
+        <v>3.181685009159757</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982225</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.647496450580276</v>
+        <v>2.829606946449228</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.856590756242633</v>
+        <v>-4.374909803292024</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.104503723769476</v>
+        <v>1.079286600818671</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7205475125947294</v>
+        <v>0.524460301422261</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.079824958137114</v>
+        <v>3.144283127302584</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.653188012919222</v>
+        <v>2.835298508788173</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.123595266515069</v>
+        <v>-4.641914313564459</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.003393481999447</v>
+        <v>0.9781763590486425</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5261844745517809</v>
+        <v>0.3300972633793124</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.968898697650291</v>
+        <v>3.033356866815761</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.652391934815724</v>
+        <v>2.834502430684675</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.224793047952241</v>
+        <v>-4.743112095001631</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.96211829132108</v>
+        <v>0.9369011683702748</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4577756610064617</v>
+        <v>0.2616884498339932</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.927057331419601</v>
+        <v>2.991515500585071</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.64999189637004</v>
+        <v>2.832102392238991</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.218282081337929</v>
+        <v>-4.736601128387319</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9623226395211217</v>
+        <v>0.9371055165703166</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4577756610064617</v>
+        <v>0.2616884498339932</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.924657292973917</v>
+        <v>2.989115462139388</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.646516615578285</v>
+        <v>2.828627111447236</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.199243953630631</v>
+        <v>-4.717563000680022</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9664626098122855</v>
+        <v>0.9412454868614804</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3995920496752671</v>
+        <v>0.2035048385027987</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.886271845383446</v>
+        <v>2.950730014548916</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.765811017212476</v>
+        <v>2.947921513081427</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.251759755905452</v>
+        <v>-4.770078802954842</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.064750690536548</v>
+        <v>1.039533567585743</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3995920496752671</v>
+        <v>0.2035048385027987</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.005566247017636</v>
+        <v>3.070024416183106</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067861</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.766644346198609</v>
+        <v>2.94875484206756</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.26562651723937</v>
+        <v>-4.78394556428876</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.060037314989114</v>
+        <v>1.034820192038309</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3617341329414442</v>
+        <v>0.1656469217689757</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.983684825963476</v>
+        <v>3.048142995128946</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789118</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.772652876595535</v>
+        <v>2.954763372464486</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.22082234569944</v>
+        <v>-4.73914139274883</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.083967514002012</v>
+        <v>1.058750391051207</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3617341329414442</v>
+        <v>0.1656469217689757</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.989693356360402</v>
+        <v>3.054151525525872</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.670603097872735</v>
+        <v>2.852713593741686</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.073079375464437</v>
+        <v>-4.591398422513827</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.041014923373212</v>
+        <v>1.015797800422408</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5295414901763273</v>
+        <v>0.3334542790038589</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.988327991978531</v>
+        <v>3.052786161144001</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.673396719404216</v>
+        <v>2.780270426446463</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.156900596739136</v>
+        <v>-4.675219643788526</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.010280056394814</v>
+        <v>0.9098261446173053</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5295414901763273</v>
+        <v>0.3334542790038589</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.991121613510012</v>
+        <v>2.980342993848778</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.674059067795874</v>
+        <v>2.780932774838121</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.150747890686351</v>
+        <v>-4.669066937735741</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.013403487207586</v>
+        <v>0.9129495754300774</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5356941962291116</v>
+        <v>0.3396069850566432</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.995475585533341</v>
+        <v>2.984696965872107</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.673139544535984</v>
+        <v>2.780013251578231</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.167557188836853</v>
+        <v>-4.685876235886243</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.005760244687496</v>
+        <v>0.9053063329099869</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5188848980786099</v>
+        <v>0.3227976869061415</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.98447048338315</v>
+        <v>2.973691863721917</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798423</v>
+        <v>3.867362636798421</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.739475098332805</v>
+        <v>2.846348805375052</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.105259190060731</v>
+        <v>-4.623578237110121</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.097014997994765</v>
+        <v>0.9965610862172567</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.564179162353052</v>
+        <v>0.3680919511805836</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.077982595744636</v>
+        <v>3.067203976083403</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.541767100046932</v>
+        <v>2.648640807089179</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.903468992395573</v>
+        <v>-4.421788039444963</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9800230787749558</v>
+        <v>0.8795691669974468</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7621973545222064</v>
+        <v>0.566110143349738</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.999085512760256</v>
+        <v>2.988306893099022</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.612057332369107</v>
+        <v>2.718931039411355</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.954355705081768</v>
+        <v>-4.472674752131158</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.029958626022653</v>
+        <v>0.9295047142451442</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7113106418360119</v>
+        <v>0.5152234306635435</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.038843717470715</v>
+        <v>3.028065097809481</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.626685068485151</v>
+        <v>2.733558775527398</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.86774496243196</v>
+        <v>-4.386064009481351</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.07923065919862</v>
+        <v>0.9787767474211106</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7899363730411701</v>
+        <v>0.5938491618687017</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.100646892309853</v>
+        <v>3.089868272648619</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.625221049309823</v>
+        <v>2.73209475635207</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.927954260437245</v>
+        <v>-4.446273307486636</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.053682920821178</v>
+        <v>0.9532290090436684</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7297270750358856</v>
+        <v>0.5336398638634172</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.063057294331354</v>
+        <v>3.05227867467012</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397789</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.623712667349751</v>
+        <v>2.730586374391998</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.851532214005318</v>
+        <v>-4.369851261054709</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.082743357433877</v>
+        <v>0.9822894456563676</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7297270750358856</v>
+        <v>0.5336398638634172</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.061548912371283</v>
+        <v>3.050770292710049</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316244</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.623575534785187</v>
+        <v>2.730449241827435</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.807159082366749</v>
+        <v>-4.32547812941614</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.10035547752474</v>
+        <v>0.9999015657472312</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7741002066744542</v>
+        <v>0.5780129955019858</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.08803565878986</v>
+        <v>3.077257039128626</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.617969328923778</v>
+        <v>2.724843035966025</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.829639433225634</v>
+        <v>-4.347958480275025</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.085757131319777</v>
+        <v>0.9853032195422677</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7741002066744542</v>
+        <v>0.5780129955019858</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.082429452928451</v>
+        <v>3.071650833267217</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.624351085951583</v>
+        <v>2.73122479299383</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.781983702664578</v>
+        <v>-4.300302749713969</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.111201180572004</v>
+        <v>1.010747268794495</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8217559372355099</v>
+        <v>0.6256687260630415</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.117404648292889</v>
+        <v>3.106626028631655</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569613</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.629243459326307</v>
+        <v>2.736117166368555</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.681465544165824</v>
+        <v>-4.199784591215215</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.156300817346231</v>
+        <v>1.055846905568721</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9222740957342644</v>
+        <v>0.726186884561796</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.182607916766866</v>
+        <v>3.171829297105632</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.61599813180218</v>
+        <v>2.722871838844427</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.665560214733471</v>
+        <v>-4.183879261782862</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.149417621595044</v>
+        <v>1.048963709817535</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8431614350250255</v>
+        <v>0.6470742238525571</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.121894992817195</v>
+        <v>3.111116373155961</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932765</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.620095834412808</v>
+        <v>2.726969541455055</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.620721813125073</v>
+        <v>-4.139040860174464</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.171450684849032</v>
+        <v>1.070996773071523</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.847704867969895</v>
+        <v>0.6516176567974266</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.128718755194746</v>
+        <v>3.117940135533511</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917047</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.624256774043886</v>
+        <v>2.731130481086133</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.640220269367081</v>
+        <v>-4.158539316416472</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.167812241983306</v>
+        <v>1.067358330205797</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7996202266899907</v>
+        <v>0.6035330155175223</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.104028910057881</v>
+        <v>3.093250290396647</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405955</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.630136376571723</v>
+        <v>2.737010083613971</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.596017432281181</v>
+        <v>-4.114336479330571</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.191372979345504</v>
+        <v>1.090919067567995</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8438230637758911</v>
+        <v>0.6477358526034227</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.136430214837258</v>
+        <v>3.125651595176024</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.83819962926564</v>
+        <v>3.838199629265638</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.628546377040971</v>
+        <v>2.735420084083218</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.603577098118228</v>
+        <v>-4.121896145167618</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.186759113479932</v>
+        <v>1.086305201702424</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8986264677857104</v>
+        <v>0.702539256613242</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.167722257712398</v>
+        <v>3.156943638051164</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284873</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.679794142224011</v>
+        <v>2.786667849266258</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.445285680578956</v>
+        <v>-3.963604727628346</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.301323445678681</v>
+        <v>1.200869533901172</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8986264677857104</v>
+        <v>0.702539256613242</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.218970022895437</v>
+        <v>3.208191403234203</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.865338681321017</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.678234846818264</v>
+        <v>2.785108553860511</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.237643676944479</v>
+        <v>-3.75596272399387</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.382820951726725</v>
+        <v>1.282367039949216</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.106268471420186</v>
+        <v>0.9101812602477182</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.341995929670376</v>
+        <v>3.331217310009142</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475134</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.673183075056534</v>
+        <v>2.780056782098781</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.186611584221951</v>
+        <v>-3.704930631271341</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.398182017054006</v>
+        <v>1.297728105276497</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.157300564142715</v>
+        <v>0.9612133529702461</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.367563413542163</v>
+        <v>3.356784793880929</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.690370479149239</v>
+        <v>2.797244186191486</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.121387403094745</v>
+        <v>-3.639706450144136</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.441459093597593</v>
+        <v>1.341005181820084</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.22252474526992</v>
+        <v>1.026437534097452</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.423885326311191</v>
+        <v>3.413106706649957</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.686331451448519</v>
+        <v>2.793205158490766</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.083960383023612</v>
+        <v>-3.602279430073002</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.452390873925327</v>
+        <v>1.351936962147818</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.227776283299102</v>
+        <v>1.031689072126633</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.42299722142798</v>
+        <v>3.412218601766746</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.687588243779759</v>
+        <v>2.794461950822007</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.10407203905832</v>
+        <v>-3.62239108610771</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.445603003842684</v>
+        <v>1.345149092065175</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.238803628296521</v>
+        <v>1.042716417124052</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.430870420757672</v>
+        <v>3.420091801096438</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.84814601480097</v>
+        <v>2.955019721843217</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.075658775958436</v>
+        <v>-3.593977823007827</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.617526080103848</v>
+        <v>1.517072168326339</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.179828065550092</v>
+        <v>0.9837408543776236</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.556042854131026</v>
+        <v>3.545264234469792</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.968258924018787</v>
+        <v>3.075132631061035</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.000876514933424</v>
+        <v>-3.519195561982814</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.767551893731671</v>
+        <v>1.667097981954162</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.254610326575105</v>
+        <v>1.058523115402636</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.72102511996385</v>
+        <v>3.710246500302616</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.959966900032646</v>
+        <v>3.066840607074893</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.974792430669616</v>
+        <v>-3.493111477719006</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.769693503451053</v>
+        <v>1.669239591673544</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.254610326575105</v>
+        <v>1.058523115402636</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.712733095977709</v>
+        <v>3.701954476316475</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.958160095616426</v>
+        <v>3.065033802658673</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.886914517560495</v>
+        <v>-3.405233564609885</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.80303786427848</v>
+        <v>1.702583952500972</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.370535968998456</v>
+        <v>1.174448757825987</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.7804816770155</v>
+        <v>3.769703057354266</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.975714501343217</v>
+        <v>3.082588208385464</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.878022056167212</v>
+        <v>-3.396341103216602</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.824149254562585</v>
+        <v>1.723695342785076</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.370535968998456</v>
+        <v>1.174448757825987</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.798036082742291</v>
+        <v>3.787257463081057</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945361</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.967569548747801</v>
+        <v>3.074443255790048</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.04649817313709</v>
+        <v>-3.56481722018648</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.748613855179218</v>
+        <v>1.648159943401709</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.342588133281875</v>
+        <v>1.146500922109406</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.773122428716927</v>
+        <v>3.762343809055692</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.948839245935663</v>
+        <v>3.05571295297791</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.60024198050765</v>
+        <v>-3.11856102755704</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.908386029418856</v>
+        <v>1.807932117641347</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.247869463612242</v>
+        <v>1.051782252439774</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.697560924103009</v>
+        <v>3.686782304441774</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.939503268432567</v>
+        <v>3.046376975474815</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.577520876824497</v>
+        <v>-3.095839923873887</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.908138493389021</v>
+        <v>1.807684581611512</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.247869463612242</v>
+        <v>1.051782252439774</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.688224946599913</v>
+        <v>3.677446326938679</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.098409394283737</v>
+        <v>3.205283101325984</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.70672269011854</v>
+        <v>-3.22504173716793</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.015363893922573</v>
+        <v>1.914909982145065</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.1186676503182</v>
+        <v>0.9225804391457315</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.769609984474657</v>
+        <v>3.758831364813423</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.135487216777383</v>
+        <v>3.24236092381963</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.732597088592565</v>
+        <v>-3.250916135641956</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.04209195702661</v>
+        <v>1.941638045249101</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.163579259029941</v>
+        <v>0.9674920478574727</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.833634772195348</v>
+        <v>3.822856152534114</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.132162572766928</v>
+        <v>3.239036279809175</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.725542398377392</v>
+        <v>-3.243861445426782</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.041589189102224</v>
+        <v>1.941135277324715</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.170633949245115</v>
+        <v>0.9745467380726465</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.834542942313997</v>
+        <v>3.823764322652764</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.14216872641167</v>
+        <v>3.249042433453917</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.698591174050904</v>
+        <v>-3.216910221100294</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.062375832477561</v>
+        <v>1.961921920700052</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.185514295272834</v>
+        <v>0.9894270841003656</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.853477303575371</v>
+        <v>3.842698683914136</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.32627185855663</v>
+        <v>3.433145565598877</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.83454418210722</v>
+        <v>-3.35286322915661</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.192097761399994</v>
+        <v>2.091643849622486</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.185514295272834</v>
+        <v>0.9894270841003656</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.03758043572033</v>
+        <v>4.026801816059097</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.318388553459623</v>
+        <v>3.42526226050187</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.856952299912092</v>
+        <v>-3.375271346961482</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.175251209181039</v>
+        <v>2.07479729740353</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.185514295272834</v>
+        <v>0.9894270841003656</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.029697130623323</v>
+        <v>4.01891851096209</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.32044255300926</v>
+        <v>3.427316260051507</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.885176535489693</v>
+        <v>-3.403495582539083</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.166015514499636</v>
+        <v>2.065561602722127</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.203491047724143</v>
+        <v>1.007403836551674</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.042537181643747</v>
+        <v>4.031758561982512</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.376696270731107</v>
+        <v>3.483569977773354</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.894617461378223</v>
+        <v>-3.412936508427613</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.218492861866071</v>
+        <v>2.118038950088562</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.325918165267534</v>
+        <v>1.129830954095066</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.172247169891628</v>
+        <v>4.161468550230394</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.379587365276408</v>
+        <v>3.486461072318655</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.946891068713864</v>
+        <v>-3.465210115763254</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.200474513477115</v>
+        <v>2.100020601699606</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.273644557931893</v>
+        <v>1.077557346759424</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.143774100035544</v>
+        <v>4.13299548037431</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.377699178170183</v>
+        <v>3.48457288521243</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.02322104631477</v>
+        <v>-3.54154009336416</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.168054335330528</v>
+        <v>2.067600423553019</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.273644557931893</v>
+        <v>1.077557346759424</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.141885912929319</v>
+        <v>4.131107293268085</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.372519407773046</v>
+        <v>3.479393114815293</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.225474766639123</v>
+        <v>-3.743793813688513</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.081973076803649</v>
+        <v>1.98151916502614</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.07139083760754</v>
+        <v>0.8753036264350709</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.01535391033757</v>
+        <v>4.004575290676335</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.370953417983198</v>
+        <v>3.477827125025445</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.387043192166378</v>
+        <v>-3.905362239215768</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.015779716802899</v>
+        <v>1.915325805025391</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9446079138096602</v>
+        <v>0.7485207026371915</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.937718166268994</v>
+        <v>3.92693954660776</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.384026824849117</v>
+        <v>3.490900531891364</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.495343854036498</v>
+        <v>-4.013662901085888</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.98553285892077</v>
+        <v>1.885078947143261</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9446079138096602</v>
+        <v>0.7485207026371915</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.950791573134913</v>
+        <v>3.940012953473679</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.376032021632057</v>
+        <v>3.482905728674304</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.588491325339864</v>
+        <v>-4.106810372389255</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.940279067182364</v>
+        <v>1.839825155404855</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8217787025271275</v>
+        <v>0.6256914913546587</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.869099243148333</v>
+        <v>3.858320623487099</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.374556062759059</v>
+        <v>3.481429769801306</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.616392112449337</v>
+        <v>-4.134711159498727</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.927642793465576</v>
+        <v>1.827188881688067</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7871817783841927</v>
+        <v>0.5910945672117239</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.846865129789574</v>
+        <v>3.83608651012834</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.371320506736257</v>
+        <v>3.478194213778504</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.738918215152231</v>
+        <v>-4.257237262201621</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.875396796361618</v>
+        <v>1.774942884584109</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6646556756812988</v>
+        <v>0.4685684645088301</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.770113912145037</v>
+        <v>3.759335292483803</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.438026466326761</v>
+        <v>3.544900173369008</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.96943271133782</v>
+        <v>-4.48775175838721</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.849896957477886</v>
+        <v>1.749443045700377</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4341411794957101</v>
+        <v>0.2380539683232413</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.698511174024187</v>
+        <v>3.687732554362953</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.578338185328608</v>
+        <v>3.685211892370855</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.318177796562264</v>
+        <v>-4.836496843611654</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.850710642389955</v>
+        <v>1.750256730612446</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3253932255768123</v>
+        <v>0.1293060144043435</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.773574120674696</v>
+        <v>3.762795501013461</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237091</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.647318454474248</v>
+        <v>3.754192161516495</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.472164214338404</v>
+        <v>-4.990483261387794</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.858096344425139</v>
+        <v>1.75764243264763</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3253932255768123</v>
+        <v>0.1293060144043435</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.842554389820335</v>
+        <v>3.831775770159101</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.633369656594369</v>
+        <v>3.740243363636616</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.421642310510738</v>
+        <v>-4.939961357560128</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.864356308076326</v>
+        <v>1.763902396298817</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3253932255768123</v>
+        <v>0.1293060144043435</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.828605591940456</v>
+        <v>3.817826972279222</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.645240145649783</v>
+        <v>3.75211385269203</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.674117464518463</v>
+        <v>-5.192436511567853</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.77523673552865</v>
+        <v>1.674782823751142</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3253932255768123</v>
+        <v>0.1293060144043435</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.84047608099587</v>
+        <v>3.829697461334636</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.646450680168726</v>
+        <v>3.753324387210974</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.967013220997875</v>
+        <v>-5.485332268047265</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.659288967455829</v>
+        <v>1.55883505567832</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3253932255768123</v>
+        <v>0.1293060144043435</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.841686615514814</v>
+        <v>3.83090799585358</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251944</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.650572422396048</v>
+        <v>3.757446129438295</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.153677349132683</v>
+        <v>-5.671996396182073</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.588745058429228</v>
+        <v>1.488291146651719</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2986542547522524</v>
+        <v>0.1025670435797836</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.8297649752474</v>
+        <v>3.818986355586166</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916199</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.645650275132237</v>
+        <v>3.752523982174484</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.299698036046645</v>
+        <v>-5.818017083096035</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.525414636399832</v>
+        <v>1.424960724622323</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2895711629583954</v>
+        <v>0.09348395178592667</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.819392972907275</v>
+        <v>3.808614353246041</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.807854331831281</v>
+        <v>3.914728038873529</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.39141204515623</v>
+        <v>-5.90973109220562</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.650933089455042</v>
+        <v>1.550479177677533</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2895711629583954</v>
+        <v>0.09348395178592667</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.981597029606319</v>
+        <v>3.970818409945085</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.802700969795096</v>
+        <v>3.909574676837343</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.423063704216199</v>
+        <v>-5.941382751265589</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.633119063794869</v>
+        <v>1.53266515201736</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2844027057139552</v>
+        <v>0.08831549454148646</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.973342593223469</v>
+        <v>3.962563973562235</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.812930387363587</v>
+        <v>3.919804094405834</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.504998522485082</v>
+        <v>-6.023317569534473</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.610574554055806</v>
+        <v>1.510120642278298</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.274467960126875</v>
+        <v>0.07838074895440628</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.977611163439712</v>
+        <v>3.966832543778478</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.821856025819489</v>
+        <v>3.928729732861736</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.60697464473349</v>
+        <v>-6.12529369178288</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.578709743612346</v>
+        <v>1.478255831834837</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1724918378784674</v>
+        <v>-0.0235953732940013</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.92535112854657</v>
+        <v>3.914572508885335</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.814008913063665</v>
+        <v>3.920882620105912</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.496968361256268</v>
+        <v>-6.015287408305658</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.61486514424741</v>
+        <v>1.514411232469902</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1956964097957427</v>
+        <v>-0.0003908013767260909</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.93142675894111</v>
+        <v>3.920648139279876</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.818258923785639</v>
+        <v>3.925132630827886</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.353908785515342</v>
+        <v>-5.872227832564732</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.676338985265755</v>
+        <v>1.575885073488246</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2037098363857219</v>
+        <v>0.007622625213253187</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.940484825617072</v>
+        <v>3.929706205955839</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.825519806668175</v>
+        <v>3.932393513710423</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.052462060043505</v>
+        <v>-5.570781107092895</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.804178558337026</v>
+        <v>1.703724646559518</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5051565618575592</v>
+        <v>0.3090693506850904</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.128613743782711</v>
+        <v>4.117835124121477</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.826490984420885</v>
+        <v>3.933364691463133</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.077052304278689</v>
+        <v>-5.595371351328079</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.795313638395663</v>
+        <v>1.694859726618154</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5051565618575592</v>
+        <v>0.3090693506850904</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.129584921535421</v>
+        <v>4.118806301874187</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.827333888800641</v>
+        <v>3.934207595842889</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.026013928272168</v>
+        <v>-5.544332975321558</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.816571893178026</v>
+        <v>1.716117981400518</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5051565618575592</v>
+        <v>0.3090693506850904</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.130427825915176</v>
+        <v>4.119649206253943</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.846371987674786</v>
+        <v>3.953245694717034</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.984874633405537</v>
+        <v>-5.503193680454928</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.852065709998824</v>
+        <v>1.751611798221316</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.54629585672419</v>
+        <v>0.3502086455517213</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.174149501709301</v>
+        <v>4.163370882048067</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.662555983798721</v>
+        <v>3.769429690840969</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.888239721386897</v>
+        <v>-5.406558768436287</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.706903670930215</v>
+        <v>1.606449759152706</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.64293076874283</v>
+        <v>0.4468435575703612</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.04831444504442</v>
+        <v>4.037535825383186</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.666058027872685</v>
+        <v>3.772931734914932</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.01882045591774</v>
+        <v>-5.53713950296713</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.658173421191842</v>
+        <v>1.557719509414333</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5123500342119874</v>
+        <v>0.3162628230395187</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.973468048399877</v>
+        <v>3.962689428738644</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833454</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.650484846948768</v>
+        <v>3.757358553991015</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.854324121726778</v>
+        <v>-5.372643168776168</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.708398773944309</v>
+        <v>1.6079448621668</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6768463684029493</v>
+        <v>0.4807591572304806</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.056592667990538</v>
+        <v>4.045814048329303</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.649672557385197</v>
+        <v>3.756546264427445</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.88169405441121</v>
+        <v>-5.4000131014606</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.696638511306966</v>
+        <v>1.596184599529457</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6768463684029493</v>
+        <v>0.4807591572304806</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.055780378426967</v>
+        <v>4.045001758765733</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147906</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.65954133651027</v>
+        <v>3.766415043552517</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.8920792493011</v>
+        <v>-5.41039829635049</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.702353212476083</v>
+        <v>1.601899300698574</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.66646117351306</v>
+        <v>0.4703739623405913</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.059418040618106</v>
+        <v>4.048639420956872</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.730378342286695</v>
+        <v>3.837252049328942</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.910667408023325</v>
+        <v>-5.428986455072715</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.765754954763618</v>
+        <v>1.665301042986109</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6478730147908347</v>
+        <v>0.4517858036183659</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.119102151161196</v>
+        <v>4.108323531499962</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.727247353104993</v>
+        <v>3.834121060147241</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.91096595471936</v>
+        <v>-5.429285001768751</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.762504546903502</v>
+        <v>1.662050635125993</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6475744680947988</v>
+        <v>0.45148725692233</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.115792033961873</v>
+        <v>4.105013414300639</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.731778248044385</v>
+        <v>3.838651955086632</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.810142821028933</v>
+        <v>-5.328461868078323</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.807364695319065</v>
+        <v>1.706910783541556</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6600386835791526</v>
+        <v>0.4639514724066838</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.127801458191876</v>
+        <v>4.117022838530643</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.731907501522928</v>
+        <v>3.838781208565175</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.619361460276526</v>
+        <v>-5.137680507325916</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.883806493098571</v>
+        <v>1.783352581321062</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.85082004433156</v>
+        <v>0.6547328331590911</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.242399528121864</v>
+        <v>4.231620908460631</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.711744347260525</v>
+        <v>3.818618054302772</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.600844606234705</v>
+        <v>-5.119163653284096</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.871050080452895</v>
+        <v>1.770596168675386</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8637501737567682</v>
+        <v>0.6676629625842994</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.229994451514586</v>
+        <v>4.219215831853352</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.746711283872583</v>
+        <v>3.85358499091483</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.545514018332943</v>
+        <v>-5.063833065382333</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.928149252225658</v>
+        <v>1.82769534044815</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9190807616585304</v>
+        <v>0.7229935504860615</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.298159740867701</v>
+        <v>4.287381121206468</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.740397851774021</v>
+        <v>3.847271558816268</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.53345989141998</v>
+        <v>-5.05177893846937</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.926657470892281</v>
+        <v>1.826203559114773</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9311348885714932</v>
+        <v>0.7350476773990243</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.299078784916917</v>
+        <v>4.288300165255682</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.742278481958157</v>
+        <v>3.849152189000404</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.574615010988201</v>
+        <v>-5.092934058037591</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.912076053249129</v>
+        <v>1.81162214147162</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8899797690032722</v>
+        <v>0.6938925578308034</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.27626634336012</v>
+        <v>4.265487723698886</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.755129507836039</v>
+        <v>3.862003214878286</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.471734421459608</v>
+        <v>-4.990053468508998</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.966079314938448</v>
+        <v>1.86562540316094</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9928603585318652</v>
+        <v>0.7967731473593963</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.350845722955158</v>
+        <v>4.340067103293924</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760311</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.775332178009633</v>
+        <v>3.882205885051881</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.703334814629109</v>
+        <v>-5.221653861678499</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.893641827844243</v>
+        <v>1.793187916066734</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9928603585318652</v>
+        <v>0.7967731473593963</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.371048393128753</v>
+        <v>4.360269773467518</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781702</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.775332178009633</v>
+        <v>3.882205885051881</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.721407322920721</v>
+        <v>-5.239726369970111</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.886412824527598</v>
+        <v>1.785958912750089</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9928603585318652</v>
+        <v>0.7967731473593963</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.371048393128753</v>
+        <v>4.360269773467518</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670068888082831</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.7355840916031</v>
+        <v>3.842457798645347</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.896514155497165</v>
+        <v>-5.414833202546555</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.776622005090487</v>
+        <v>1.676168093312978</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9928603585318652</v>
+        <v>0.7967731473593963</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.33130030672222</v>
+        <v>4.320521687060985</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.74260671060004</v>
+        <v>3.849480417642287</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.86522813495671</v>
+        <v>-5.3835471820061</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.796159032303609</v>
+        <v>1.6957051205261</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.024146379072321</v>
+        <v>0.8280591678998517</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.357094538043433</v>
+        <v>4.346315918382198</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.73059065867782</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.841777710172944</v>
+        <v>3.948651417215191</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.712202742843425</v>
+        <v>-5.230521789892816</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.956540188721827</v>
+        <v>1.856086276944318</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.177171771185605</v>
+        <v>0.9810845600131358</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.548080772884307</v>
+        <v>4.537302153223073</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741298518073879</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.029243935081237</v>
+        <v>4.136117642123484</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.740510056716696</v>
+        <v>-5.258829103766086</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.132683488080811</v>
+        <v>2.032229576303302</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.177171771185605</v>
+        <v>0.9810845600131358</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.7355469977926</v>
+        <v>4.724768378131365</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699135800903164</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.998646886435319</v>
+        <v>4.105520593477566</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.907103281830218</v>
+        <v>-5.425422328879608</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.035449149389485</v>
+        <v>1.934995237611976</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.010578546072082</v>
+        <v>0.8144913348996135</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.604994014078568</v>
+        <v>4.594215394417335</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708202704568379</v>
       </c>
       <c r="C2054" t="n">
-        <v>4.002323289097037</v>
+        <v>4.109196996139284</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.734038902447918</v>
+        <v>-5.252357949497308</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.108351303804122</v>
+        <v>2.007897392026613</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.010578546072082</v>
+        <v>0.8144913348996135</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.608670416740286</v>
+        <v>4.597891797079052</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.7406015866822</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.999941344220532</v>
+        <v>4.106815051262779</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.704792921992222</v>
+        <v>-5.223111969041612</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.117667751109896</v>
+        <v>2.017213839332387</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.010578546072082</v>
+        <v>0.8144913348996135</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.606288471863781</v>
+        <v>4.595509852202547</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.699424827539104</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.997234583378167</v>
+        <v>4.104108290420414</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.811718469870073</v>
+        <v>-5.336730645183295</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.07219077111639</v>
+        <v>1.969059608033349</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9036529981942308</v>
+        <v>0.7008726587579296</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.539426382294706</v>
+        <v>4.524631885675172</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689962785983734</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.998663385521401</v>
+        <v>4.105537092563648</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.956737028377321</v>
+        <v>-5.481749203690544</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.015612149856725</v>
+        <v>1.912480986773683</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7586344396869823</v>
+        <v>0.555854100250681</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.453844049333591</v>
+        <v>4.439049552714057</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.711872614969745</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.098594624779154</v>
+        <v>4.205468331821401</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.075078794162039</v>
+        <v>-5.600090969475262</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.068206682800591</v>
+        <v>1.965075519717549</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7693204782498724</v>
+        <v>0.5665401388135711</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.560186911729078</v>
+        <v>4.545392415109545</v>
       </c>
     </row>
     <row r="2059">
@@ -48905,19 +48905,19 @@
         <v>3.714899237073535</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.096380321905093</v>
+        <v>4.20325402894734</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.126489216482747</v>
+        <v>-5.65150139179597</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.045428210998247</v>
+        <v>1.942297047915205</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7693204782498724</v>
+        <v>0.5665401388135711</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.557972608855017</v>
+        <v>4.543178112235482</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.704778134720062</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.096283449979382</v>
+        <v>4.20315715702163</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.205908667690498</v>
+        <v>-5.730920843003721</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.013563558589436</v>
+        <v>1.910432395506394</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7693204782498724</v>
+        <v>0.5665401388135711</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.557875736929306</v>
+        <v>4.543081240309773</v>
       </c>
     </row>
     <row r="2061">
@@ -48951,19 +48951,19 @@
         <v>3.736825137581129</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.096277343537426</v>
+        <v>4.203151050579673</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.301371665607716</v>
+        <v>-5.826383840920939</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.975372252980592</v>
+        <v>1.87224108989755</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7693204782498724</v>
+        <v>0.5665401388135711</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.55786963048735</v>
+        <v>4.543075133867816</v>
       </c>
     </row>
     <row r="2062">
@@ -48974,19 +48974,19 @@
         <v>3.715393145500731</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.094373740100036</v>
+        <v>4.201247447142284</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.3413916636515</v>
+        <v>-5.866403838964723</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.957460650325689</v>
+        <v>1.854329487242647</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7293004802060885</v>
+        <v>0.5265201407697873</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.53195402822369</v>
+        <v>4.517159531604157</v>
       </c>
     </row>
     <row r="2063">
@@ -48997,19 +48997,19 @@
         <v>3.736109598636267</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.100107557847763</v>
+        <v>4.20698126489001</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.396760825783693</v>
+        <v>-5.921773001096916</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.941046803220539</v>
+        <v>1.837915640137497</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7293004802060885</v>
+        <v>0.5265201407697873</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.537687845971417</v>
+        <v>4.522893349351883</v>
       </c>
     </row>
     <row r="2064">
@@ -49020,19 +49020,19 @@
         <v>3.73684305539601</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.099645921190696</v>
+        <v>4.206519628232943</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.442198605614521</v>
+        <v>-5.967210780927743</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.92241005463114</v>
+        <v>1.819278891548099</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6864554895279289</v>
+        <v>0.4836751500916276</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.511519214907453</v>
+        <v>4.49672471828792</v>
       </c>
     </row>
     <row r="2065">
@@ -49043,19 +49043,19 @@
         <v>3.790292685396419</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.119520314041015</v>
+        <v>4.226394021083262</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.358973148766856</v>
+        <v>-5.883985324080079</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.975574630220525</v>
+        <v>1.872443467137483</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6864554895279289</v>
+        <v>0.4836751500916276</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.531393607757773</v>
+        <v>4.516599111138239</v>
       </c>
     </row>
     <row r="2066">
@@ -49066,19 +49066,19 @@
         <v>3.794507029299173</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.103221014565743</v>
+        <v>4.21009472160799</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.182682924161549</v>
+        <v>-5.707695099474772</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.029791420587376</v>
+        <v>1.926660257504334</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6864554895279289</v>
+        <v>0.4836751500916276</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.5150943082825</v>
+        <v>4.500299811662967</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.794725278590404</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.105651964029788</v>
+        <v>4.212525671072036</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.999471261028454</v>
+        <v>-5.524483436341677</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.10550703530466</v>
+        <v>2.002375872221618</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6864554895279289</v>
+        <v>0.4836751500916276</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.517525257746546</v>
+        <v>4.502730761127013</v>
       </c>
     </row>
     <row r="2068">
@@ -49112,19 +49112,19 @@
         <v>3.776866743146282</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.071443149877678</v>
+        <v>4.178316856919925</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.927749814014603</v>
+        <v>-5.452761989327826</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.099986799958089</v>
+        <v>1.996855636875047</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7581769365417795</v>
+        <v>0.5553965971054782</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.526349311802746</v>
+        <v>4.511554815183212</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676847</v>
+        <v>3.723809890676848</v>
       </c>
       <c r="C2069" t="n">
-        <v>4.018358895798849</v>
+        <v>4.125232602841097</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.147144682126132</v>
+        <v>-5.239733289919013</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.959144598634649</v>
+        <v>2.028982862559744</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6863446349011448</v>
+        <v>0.6002931599395317</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.430165676739537</v>
+        <v>4.485408498804816</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.861947350949959</v>
+        <v>3.783112736724433</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.398698097898717</v>
+        <v>4.122547043719776</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.147144682126132</v>
+        <v>-5.252821506611325</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.959144598634649</v>
+        <v>2.021062016761499</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6863446349011448</v>
+        <v>0.5872049432472196</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.391761894885085</v>
+        <v>4.474870009668108</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240828.xlsx
+++ b/tame_output/ON/bt/strategyON_20240828.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>23.3%</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>88.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.6%</t>
+          <t>91.5%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-79.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>107.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.6%</t>
+          <t>124.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-13.1%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.4%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>88.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>424.1%</t>
+          <t>420.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-686.9%</t>
+          <t>-677.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-174.1%</t>
+          <t>-179.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-25.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>117.4%</t>
+          <t>119.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-292.0%</t>
+          <t>-289.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-165.3%</t>
+          <t>-157.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>-3.2%</t>
         </is>
       </c>
     </row>
@@ -44420,19 +44420,19 @@
         <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.297551015812623</v>
+        <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
         <v>-5.737773607189072</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.002085148623247</v>
+        <v>0.8199746527542953</v>
       </c>
       <c r="F1864" t="n">
         <v>-0.739988619921459</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.853557843859748</v>
+        <v>2.671447347990797</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.292736448284083</v>
+        <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
         <v>-5.851534019211937</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.9517664162855608</v>
+        <v>0.7696559204166098</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.739988619921459</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.848743276331208</v>
+        <v>2.666632780462257</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.290730498892961</v>
+        <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
         <v>-6.267925893498934</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.7832037171796391</v>
+        <v>0.6010932213106881</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.739988619921459</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.846737326940086</v>
+        <v>2.664626831071135</v>
       </c>
     </row>
     <row r="1867">
@@ -44489,19 +44489,19 @@
         <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.30098918956164</v>
+        <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.629099523315922</v>
+        <v>-6.492834076881537</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.6489929559215231</v>
+        <v>0.521388638626326</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.739988619921459</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.856996017608765</v>
+        <v>2.674885521739814</v>
       </c>
     </row>
     <row r="1868">
@@ -44512,19 +44512,19 @@
         <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.297088754707335</v>
+        <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.972358042958941</v>
+        <v>-6.836092596524556</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.5077891132100105</v>
+        <v>0.3801847959148139</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.739988619921459</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.85309558275446</v>
+        <v>2.670985086885509</v>
       </c>
     </row>
     <row r="1869">
@@ -44535,19 +44535,19 @@
         <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.295493674762336</v>
+        <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.020560860201285</v>
+        <v>-6.8842954137669</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.4869129063680742</v>
+        <v>0.3593085890728771</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.739988619921459</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.85150050280946</v>
+        <v>2.669390006940509</v>
       </c>
     </row>
     <row r="1870">
@@ -44558,19 +44558,19 @@
         <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.299272650691544</v>
+        <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.317222202011482</v>
+        <v>-7.180956755577097</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.3720273455732035</v>
+        <v>0.2444230282780064</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.8087317556553376</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.814033597298342</v>
+        <v>2.631923101429391</v>
       </c>
     </row>
     <row r="1871">
@@ -44581,19 +44581,19 @@
         <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.295246346157141</v>
+        <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.503941910320785</v>
+        <v>-7.3676764638864</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2933131577150792</v>
+        <v>0.1657088404198821</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.8087317556553376</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.810007292763939</v>
+        <v>2.627896796894988</v>
       </c>
     </row>
     <row r="1872">
@@ -44604,19 +44604,19 @@
         <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.295144244835557</v>
+        <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.886943299063416</v>
+        <v>-7.750677852629031</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.1400105008964427</v>
+        <v>0.01240618360124568</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.8087317556553376</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.809905191442355</v>
+        <v>2.627794695573404</v>
       </c>
     </row>
     <row r="1873">
@@ -44627,19 +44627,19 @@
         <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.297715760806987</v>
+        <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.891429744264805</v>
+        <v>-7.75516429783042</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.1407874387873171</v>
+        <v>0.01318312149212053</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.8132182008567264</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.809784840292951</v>
+        <v>2.627674344424</v>
       </c>
     </row>
     <row r="1874">
@@ -44650,19 +44650,19 @@
         <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.303066064105037</v>
+        <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.250960066768808</v>
+        <v>-8.114694620334422</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.002325613083766331</v>
+        <v>-0.1252787042114303</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.8132182008567264</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.815135143591001</v>
+        <v>2.63302464772205</v>
       </c>
     </row>
     <row r="1875">
@@ -44673,19 +44673,19 @@
         <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.310982084062215</v>
+        <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.30130913022303</v>
+        <v>-8.165043683788644</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.009897992340744732</v>
+        <v>-0.1375023096359413</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.8635672643109484</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.792841725475646</v>
+        <v>2.610731229606695</v>
       </c>
     </row>
     <row r="1876">
@@ -44696,19 +44696,19 @@
         <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.314023834683983</v>
+        <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.398928407644426</v>
+        <v>-8.26266296121004</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.04590395268753467</v>
+        <v>-0.1735082699827308</v>
       </c>
       <c r="F1876" t="n">
         <v>-0.9611865417323451</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.737311909644577</v>
+        <v>2.555201413775626</v>
       </c>
     </row>
     <row r="1877">
@@ -44719,19 +44719,19 @@
         <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.316917391005556</v>
+        <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.452999907152785</v>
+        <v>-8.316734460718399</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.06463899616930568</v>
+        <v>-0.1922433134645023</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.015258041240704</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.707762566261133</v>
+        <v>2.525652070392182</v>
       </c>
     </row>
     <row r="1878">
@@ -44742,19 +44742,19 @@
         <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.322430588124198</v>
+        <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.657258082482649</v>
+        <v>-8.520992636048263</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1408290691826091</v>
+        <v>-0.2684333864778052</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.142896985854693</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.636692396611382</v>
+        <v>2.454581900742431</v>
       </c>
     </row>
     <row r="1879">
@@ -44765,19 +44765,19 @@
         <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.326913142608634</v>
+        <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.690910920991122</v>
+        <v>-8.554645474556736</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1498076501015624</v>
+        <v>-0.2774119673967586</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.243310353771731</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.580926930345596</v>
+        <v>2.398816434476645</v>
       </c>
     </row>
     <row r="1880">
@@ -44788,19 +44788,19 @@
         <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.342284844102055</v>
+        <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.82999703560998</v>
+        <v>-8.693731589175593</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1900703944556841</v>
+        <v>-0.3176747117508807</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.382396468390588</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.512846963067703</v>
+        <v>2.330736467198752</v>
       </c>
     </row>
     <row r="1881">
@@ -44811,19 +44811,19 @@
         <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.356840064849572</v>
+        <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.005121452996523</v>
+        <v>-8.868856006562137</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2455649406627844</v>
+        <v>-0.3731692579579811</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.557520885777131</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.422327533383293</v>
+        <v>2.240217037514342</v>
       </c>
     </row>
     <row r="1882">
@@ -44834,19 +44834,19 @@
         <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.349620899947976</v>
+        <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.239573547011013</v>
+        <v>-9.103308100576626</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3465649431701765</v>
+        <v>-0.4741692604653731</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.557520885777131</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.415108368481698</v>
+        <v>2.232997872612747</v>
       </c>
     </row>
     <row r="1883">
@@ -44857,19 +44857,19 @@
         <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.342948709174</v>
+        <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.343948278037459</v>
+        <v>-9.207682831603073</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3949870263547313</v>
+        <v>-0.5225913436499279</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.661895616803577</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.345811339091854</v>
+        <v>2.163700843222903</v>
       </c>
     </row>
     <row r="1884">
@@ -44880,19 +44880,19 @@
         <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.344064499012556</v>
+        <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.506461743736043</v>
+        <v>-9.370196297301657</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4588766227956085</v>
+        <v>-0.5864809400908051</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.759529047222264</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.288347070679198</v>
+        <v>2.106236574810247</v>
       </c>
     </row>
     <row r="1885">
@@ -44903,19 +44903,19 @@
         <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.346758227641671</v>
+        <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.632498537104333</v>
+        <v>-9.496233090669946</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5065976115138096</v>
+        <v>-0.6342019288090062</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.734277424412522</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.306191772994158</v>
+        <v>2.124081277125207</v>
       </c>
     </row>
     <row r="1886">
@@ -44926,19 +44926,19 @@
         <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.350748563328072</v>
+        <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.575426765208402</v>
+        <v>-9.439161318774016</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4797785670690367</v>
+        <v>-0.6073828843642328</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.734277424412522</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.310182108680559</v>
+        <v>2.128071612811608</v>
       </c>
     </row>
     <row r="1887">
@@ -44949,19 +44949,19 @@
         <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.34927333642933</v>
+        <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.717098606932522</v>
+        <v>-9.580833160498136</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5379225306574265</v>
+        <v>-0.6655268479526226</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.734277424412522</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.308706881781817</v>
+        <v>2.126596385912866</v>
       </c>
     </row>
     <row r="1888">
@@ -44972,19 +44972,19 @@
         <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.364326746594202</v>
+        <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.667507762507688</v>
+        <v>-9.531242316073302</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5030327827226202</v>
+        <v>-0.6306371000178168</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.684686579987688</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.35351479860159</v>
+        <v>2.171404302732639</v>
       </c>
     </row>
     <row r="1889">
@@ -44995,19 +44995,19 @@
         <v>3.676841549770576</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.351275612947519</v>
+        <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.518589428035831</v>
+        <v>-9.382323981601445</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4565165825805608</v>
+        <v>-0.584120899875757</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.653436989252515</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.359213419396011</v>
+        <v>2.17710292352706</v>
       </c>
     </row>
     <row r="1890">
@@ -45018,19 +45018,19 @@
         <v>3.685161381615279</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.360854685983728</v>
+        <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.292744275316419</v>
+        <v>-9.156478828882033</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3565994484565871</v>
+        <v>-0.4842037657517837</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.611510313665351</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.393948497784518</v>
+        <v>2.211838001915567</v>
       </c>
     </row>
     <row r="1891">
@@ -45041,19 +45041,19 @@
         <v>3.684843823812099</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.361993830539787</v>
+        <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.168165618978827</v>
+        <v>-9.031900172544441</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3056288413654915</v>
+        <v>-0.4332331586606881</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.611510313665351</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.395087642340576</v>
+        <v>2.212977146471625</v>
       </c>
     </row>
     <row r="1892">
@@ -45064,19 +45064,19 @@
         <v>3.710935533646213</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.364627604701894</v>
+        <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.143128937410317</v>
+        <v>-9.006863490975931</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2929803945759799</v>
+        <v>-0.4205847118711765</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.586181226114615</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.412918869033125</v>
+        <v>2.230808373164174</v>
       </c>
     </row>
     <row r="1893">
@@ -45087,19 +45087,19 @@
         <v>3.768951674611564</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.370361308940531</v>
+        <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.070995762122436</v>
+        <v>-8.93473031568805</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2583934202221911</v>
+        <v>-0.3859977375173873</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.586181226114615</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.418652573271762</v>
+        <v>2.236542077402811</v>
       </c>
     </row>
     <row r="1894">
@@ -45110,19 +45110,19 @@
         <v>3.728577929955324</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.360624046546666</v>
+        <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.999629369512789</v>
+        <v>-8.863363923078403</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2395841255721973</v>
+        <v>-0.3671884428673939</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.514814833504967</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.451735146443686</v>
+        <v>2.269624650574735</v>
       </c>
     </row>
     <row r="1895">
@@ -45133,19 +45133,19 @@
         <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.350740565233758</v>
+        <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.906170335527564</v>
+        <v>-8.769904889093178</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.212083993291015</v>
+        <v>-0.3396883105862116</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.514814833504967</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.441851665130778</v>
+        <v>2.259741169261827</v>
       </c>
     </row>
     <row r="1896">
@@ -45156,19 +45156,19 @@
         <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.348906004734384</v>
+        <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.895517153974133</v>
+        <v>-8.759251707539747</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2096572811690161</v>
+        <v>-0.3372615984642127</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.514814833504967</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.440017104631404</v>
+        <v>2.257906608762453</v>
       </c>
     </row>
     <row r="1897">
@@ -45179,19 +45179,19 @@
         <v>3.784684521311945</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.348605689760924</v>
+        <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.797610115297642</v>
+        <v>-8.661344668863256</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1707947806718808</v>
+        <v>-0.2983990979670774</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.446829083644411</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.480508239574277</v>
+        <v>2.298397743705326</v>
       </c>
     </row>
     <row r="1898">
@@ -45202,19 +45202,19 @@
         <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.349274195906417</v>
+        <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.773656574321684</v>
+        <v>-8.637391127887298</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1605448581360038</v>
+        <v>-0.2881491754312004</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.422875542668453</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.495548870305345</v>
+        <v>2.313438374436394</v>
       </c>
     </row>
     <row r="1899">
@@ -45225,19 +45225,19 @@
         <v>3.789311112017767</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.336013879744665</v>
+        <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.509596635998887</v>
+        <v>-8.373331189564501</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.06818119896863717</v>
+        <v>-0.1957855162638338</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.158815604345657</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.640724517137271</v>
+        <v>2.45861402126832</v>
       </c>
     </row>
     <row r="1900">
@@ -45248,19 +45248,19 @@
         <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.333226846084364</v>
+        <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.802517012494049</v>
+        <v>-7.83017114878342</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2118636167729973</v>
+        <v>0.01869146638829777</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.158815604345657</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.63793748347697</v>
+        <v>2.455826987608019</v>
       </c>
     </row>
     <row r="1901">
@@ -45271,19 +45271,19 @@
         <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.333570469972206</v>
+        <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.762332714127859</v>
+        <v>-7.78998685041723</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2282809600073148</v>
+        <v>0.03510880962261531</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.118631305979466</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.662391686384526</v>
+        <v>2.480281190515575</v>
       </c>
     </row>
     <row r="1902">
@@ -45294,19 +45294,19 @@
         <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.332937291192962</v>
+        <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.598932843188496</v>
+        <v>-7.626586979477867</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2930077296038167</v>
+        <v>0.09983557921911723</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.9552314350401039</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.7597984301689</v>
+        <v>2.577687934299949</v>
       </c>
     </row>
     <row r="1903">
@@ -45317,19 +45317,19 @@
         <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.340861720030815</v>
+        <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.365451620958898</v>
+        <v>-7.393105757248269</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3943246473335082</v>
+        <v>0.2011524969488088</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.7217502128105053</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.907811592344512</v>
+        <v>2.725701096475561</v>
       </c>
     </row>
     <row r="1904">
@@ -45340,19 +45340,19 @@
         <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.337969509717856</v>
+        <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.215785229951383</v>
+        <v>-7.243439366240754</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4512989934235554</v>
+        <v>0.2581268430388559</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.6288467215679694</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.960661476777074</v>
+        <v>2.778550980908123</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.23923029572501</v>
+        <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.083509756320496</v>
+        <v>-7.111163892609867</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4054699688830645</v>
+        <v>0.212297818498365</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.4965712479370827</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.941287546962761</v>
+        <v>2.75917705109381</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.242045356412647</v>
+        <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.927771423760754</v>
+        <v>-6.955425560050125</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4705803625945979</v>
+        <v>0.2774082122098984</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.3408329153773412</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.037545607186243</v>
+        <v>2.855435111317292</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.254951697636306</v>
+        <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.842806757031434</v>
+        <v>-6.870460893320805</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5174725705099847</v>
+        <v>0.3243004201252853</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.2558682486480216</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.101430748447493</v>
+        <v>2.919320252578542</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.126975768037087</v>
+        <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.948396746804539</v>
+        <v>-6.97605088309391</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3472606450015241</v>
+        <v>0.1540884946168246</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.361458238421126</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.910100824984412</v>
+        <v>2.727990329115461</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987899</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.175520109914173</v>
+        <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.880162162179111</v>
+        <v>-6.907816298468482</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4230988207287814</v>
+        <v>0.2299266703440823</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.34304291554859</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.96969436058502</v>
+        <v>2.787583864716069</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.058899301275766</v>
+        <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.732222120771512</v>
+        <v>-6.759876257060883</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.365654028653414</v>
+        <v>0.172481878268715</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.3227219996400324</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.865266101491747</v>
+        <v>2.683155605622796</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.050185315022288</v>
+        <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.679252598517524</v>
+        <v>-6.706906734806894</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3781278513015316</v>
+        <v>0.1849557009168321</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.2697524773860435</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.888333828590662</v>
+        <v>2.706223332721711</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.043224702927195</v>
+        <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.513464402557233</v>
+        <v>-6.541118538846604</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4374825175905546</v>
+        <v>0.2443103672058551</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.2697524773860435</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.881373216495569</v>
+        <v>2.699262720626618</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.057687057308338</v>
+        <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.480101196078464</v>
+        <v>-6.507755332367835</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4652901545632053</v>
+        <v>0.2721180041785058</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.2697524773860435</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.895835570876712</v>
+        <v>2.713725075007761</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.052219177767533</v>
+        <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.371842058955942</v>
+        <v>-6.399496195245313</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.503125929871409</v>
+        <v>0.3099537794867095</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.2697524773860435</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.890367691335907</v>
+        <v>2.708257195466956</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.04971727177811</v>
+        <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.248550924138812</v>
+        <v>-6.276205060428182</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5499404778088381</v>
+        <v>0.3567683274241387</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.146461342568913</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.961840466236763</v>
+        <v>2.779729970367812</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.057418250015435</v>
+        <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.19585405700752</v>
+        <v>-6.223508193296891</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5787202028986798</v>
+        <v>0.3855480525139803</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.09376447543762184</v>
       </c>
       <c r="G1916" t="n">
-        <v>3.001159564752862</v>
+        <v>2.819049068883911</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.74832840831809</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.053198958362486</v>
+        <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.952088615024076</v>
+        <v>-5.979742751313447</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6720070880391082</v>
+        <v>0.4788349376544088</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.09376447543762184</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.996940273099913</v>
+        <v>2.814829777230962</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.055323272282502</v>
+        <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.862312942647604</v>
+        <v>-5.889967078936975</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.710041670909713</v>
+        <v>0.5168695205250136</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.03216503052331182</v>
       </c>
       <c r="G1918" t="n">
-        <v>3.036024253968515</v>
+        <v>2.853913758099564</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.048065347266204</v>
+        <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.612462548698529</v>
+        <v>-5.6401166849879</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8027239034730451</v>
+        <v>0.6095517530883456</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.03216503052331182</v>
       </c>
       <c r="G1919" t="n">
-        <v>3.028766328952217</v>
+        <v>2.846655833083266</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.051664470786853</v>
+        <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.436570456231097</v>
+        <v>-5.464224592520468</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8766798639806668</v>
+        <v>0.6835077135959673</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.03216503052331182</v>
       </c>
       <c r="G1920" t="n">
-        <v>3.032365452472866</v>
+        <v>2.850254956603915</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.064991976841406</v>
+        <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.265123993208634</v>
+        <v>-5.292778129498005</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9585859552442058</v>
+        <v>0.7654138048595063</v>
       </c>
       <c r="F1921" t="n">
         <v>0.1392814324991513</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.148560836340898</v>
+        <v>2.966450340471947</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632777</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.064012454457703</v>
+        <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.185101706099513</v>
+        <v>-5.212755842388884</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9896153477041509</v>
+        <v>0.7964431973194519</v>
       </c>
       <c r="F1922" t="n">
         <v>0.2193037196082723</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.195594686222667</v>
+        <v>3.013484190353716</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.068707255512021</v>
+        <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.121465963865578</v>
+        <v>-5.149120100154949</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.019764445652042</v>
+        <v>0.8265922952673428</v>
       </c>
       <c r="F1923" t="n">
         <v>0.2829394618422068</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.238470932617345</v>
+        <v>3.056360436748394</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.049901514295816</v>
+        <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.027768645649183</v>
+        <v>-5.055422781938554</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.038437631722396</v>
+        <v>0.8452654813376963</v>
       </c>
       <c r="F1924" t="n">
         <v>0.2829394618422068</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.219665191401141</v>
+        <v>3.03755469553219</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.051644590920694</v>
+        <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.038271268714472</v>
+        <v>-5.065925405003843</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.035979659121158</v>
+        <v>0.8428075087364584</v>
       </c>
       <c r="F1925" t="n">
         <v>0.2724368387769179</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.215106694186845</v>
+        <v>3.032996198317894</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367681</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.055573904755514</v>
+        <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.97693122125607</v>
+        <v>-4.993682836832648</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.064444991939339</v>
+        <v>0.8756338498397565</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2724368387769179</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.219036008021665</v>
+        <v>3.036925512152714</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232699787996</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.056252488672854</v>
+        <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.959217534378205</v>
+        <v>-4.975969149954783</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.072209050607825</v>
+        <v>0.8833979085082424</v>
       </c>
       <c r="F1927" t="n">
         <v>0.2756181676738347</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.221623389277155</v>
+        <v>3.039512893408204</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.053250559892847</v>
+        <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.850412648898478</v>
+        <v>-4.867164264475056</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.112729076019709</v>
+        <v>0.9239179339201269</v>
       </c>
       <c r="F1928" t="n">
         <v>0.2756181676738347</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.218621460497149</v>
+        <v>3.036510964628198</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675934</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.054829596903462</v>
+        <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.630391850861467</v>
+        <v>-4.647143466438045</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.202316432245127</v>
+        <v>1.013505290145545</v>
       </c>
       <c r="F1929" t="n">
         <v>0.416838012741815</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.304932404548551</v>
+        <v>3.1228219086796</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539946</v>
+        <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.070723779705285</v>
+        <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.497524161798189</v>
+        <v>-4.514275777374768</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.271357690672262</v>
+        <v>1.08254654857268</v>
       </c>
       <c r="F1930" t="n">
         <v>0.416838012741815</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.320826587350374</v>
+        <v>3.138716091481423</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.071869624145587</v>
+        <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.377351078433691</v>
+        <v>-4.394102694010269</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.320572768458363</v>
+        <v>1.131761626358781</v>
       </c>
       <c r="F1931" t="n">
         <v>0.5370110961063139</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.394076281809375</v>
+        <v>3.211965785940424</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.081957726707027</v>
+        <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.242097717103714</v>
+        <v>-4.258849332680292</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.384762215551794</v>
+        <v>1.195951073452212</v>
       </c>
       <c r="F1932" t="n">
         <v>0.672264457436291</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.485316401168801</v>
+        <v>3.30320590529985</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
-        <v>3.067995218108452</v>
+        <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.301972544461406</v>
+        <v>-4.318724160037984</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.346849776010143</v>
+        <v>1.15803863391056</v>
       </c>
       <c r="F1933" t="n">
         <v>0.6123896300785989</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.435428996155612</v>
+        <v>3.253318500286661</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
-        <v>3.083284387342661</v>
+        <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.182152313550569</v>
+        <v>-4.198903929127147</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.410067037608686</v>
+        <v>1.221255895509104</v>
       </c>
       <c r="F1934" t="n">
         <v>0.6123896300785989</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.450718165389821</v>
+        <v>3.26860766952087</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.990928586665103</v>
+        <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.184622020012375</v>
+        <v>-4.201373635588953</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.316723354346405</v>
+        <v>1.127912212246823</v>
       </c>
       <c r="F1935" t="n">
         <v>0.6099199236167927</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.356880540835178</v>
+        <v>3.174770044966227</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003596</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.910190448150404</v>
+        <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.252992206336385</v>
+        <v>-4.269743821912964</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.208637141302103</v>
+        <v>1.01982599920252</v>
       </c>
       <c r="F1936" t="n">
         <v>0.6191956226530076</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.281707821742209</v>
+        <v>3.099597325873258</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.900627156782295</v>
+        <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.364864485962536</v>
+        <v>-4.381616101539114</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.154324938083534</v>
+        <v>0.9655137959839513</v>
       </c>
       <c r="F1937" t="n">
         <v>0.6191956226530076</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.2721445303741</v>
+        <v>3.090034034505149</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417699</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
-        <v>3.037657993474498</v>
+        <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.420384561855125</v>
+        <v>-4.437136177431704</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.2691477444187</v>
+        <v>1.080336602319118</v>
       </c>
       <c r="F1938" t="n">
         <v>0.6191956226530076</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.409175367066303</v>
+        <v>3.227064871197352</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205894</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
-        <v>3.042225225466285</v>
+        <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.438226695660378</v>
+        <v>-4.261661917639234</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.266578122888387</v>
+        <v>1.155093538227894</v>
       </c>
       <c r="F1939" t="n">
         <v>0.6191956226530076</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.41374259905809</v>
+        <v>3.231632103189139</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
-        <v>3.017967254227492</v>
+        <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.430302321075464</v>
+        <v>-4.25373754305432</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.245489901483559</v>
+        <v>1.134005316823066</v>
       </c>
       <c r="F1940" t="n">
         <v>0.6191956226530076</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.389484627819297</v>
+        <v>3.207374131950346</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.946505567628942</v>
+        <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.424024118505615</v>
+        <v>-4.247459340484471</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.176539495912949</v>
+        <v>1.065054911252456</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6254738252228567</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.321789862762656</v>
+        <v>3.139679366893705</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.956677954061075</v>
+        <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.364171499301892</v>
+        <v>-4.187606721280748</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.21065293002657</v>
+        <v>1.099168345366077</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6254738252228567</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.331962249194789</v>
+        <v>3.149851753325838</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.951624224634935</v>
+        <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.277928036275514</v>
+        <v>-4.10136325825437</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.240096585810982</v>
+        <v>1.128612001150489</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6254738252228567</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.326908519768649</v>
+        <v>3.144798023899698</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316044</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.94340000007946</v>
+        <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.323234855674494</v>
+        <v>-4.14667007765335</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.213749633495915</v>
+        <v>1.102265048835422</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5846636622136259</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.294198197407636</v>
+        <v>3.112087701538685</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.943951873112562</v>
+        <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.352267960376795</v>
+        <v>-4.175703182355651</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.202688264648097</v>
+        <v>1.091203679987603</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5846636622136259</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.294750070440738</v>
+        <v>3.112639574571787</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.873224565003928</v>
+        <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.259457478925936</v>
+        <v>-4.082892700904791</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.169085149119806</v>
+        <v>1.057600564459313</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6774741436644852</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.279709051202619</v>
+        <v>3.097598555333668</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560423</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.875098040928528</v>
+        <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.303846948255363</v>
+        <v>-4.127282170234219</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.153202837312636</v>
+        <v>1.041718252652143</v>
       </c>
       <c r="F1947" t="n">
         <v>0.6330846743350576</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.254948845529563</v>
+        <v>3.072838349660612</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.870173749440251</v>
+        <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.420388553360706</v>
+        <v>-4.243823775339561</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.101661903782222</v>
+        <v>0.9901773191217287</v>
       </c>
       <c r="F1948" t="n">
         <v>0.5165430692297148</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.18009959097808</v>
+        <v>2.997989095109129</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.875665045270919</v>
+        <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.460312647943278</v>
+        <v>-4.283747869922133</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.09118356177986</v>
+        <v>0.9796989771193672</v>
       </c>
       <c r="F1949" t="n">
         <v>0.5165430692297148</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.185590886808748</v>
+        <v>3.003480390939797</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.887162247039458</v>
+        <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.48809304584463</v>
+        <v>-4.311528267823486</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.091568604387858</v>
+        <v>0.980084019727365</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4887626713283617</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.180419849836475</v>
+        <v>2.998309353967524</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170532</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.725517967040111</v>
+        <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.606473718574769</v>
+        <v>-4.429908940553624</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8825720552964562</v>
+        <v>0.7710874706359629</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4215448191773855</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.978444858546543</v>
+        <v>2.796334362677592</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729264</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.845667627759317</v>
+        <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.7150877970181</v>
+        <v>-4.538523018996956</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9592760846383295</v>
+        <v>0.8477914999778362</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4215448191773855</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.098594519265748</v>
+        <v>2.916484023396797</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.86018065386164</v>
+        <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.679678758769957</v>
+        <v>-4.503113980748813</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9879527260399095</v>
+        <v>0.8764681413794162</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4215448191773855</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.113107545368071</v>
+        <v>2.93099704949912</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.857600095204008</v>
+        <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.641295096211806</v>
+        <v>-4.464730318190662</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.000725632405539</v>
+        <v>0.8892410477450454</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4599284817355367</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.133557184245331</v>
+        <v>2.95144668837638</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.85432912404931</v>
+        <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.46417876617664</v>
+        <v>-4.287613988155496</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.068301193264907</v>
+        <v>0.9568166086044139</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4599284817355367</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.130286213090633</v>
+        <v>2.948175717221682</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.855012515811223</v>
+        <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.509271011010186</v>
+        <v>-4.332706232989041</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.050947687093402</v>
+        <v>0.9394631024329085</v>
       </c>
       <c r="F1956" t="n">
         <v>0.3980324385661469</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.093831978950912</v>
+        <v>2.911721483081961</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.848799491117638</v>
+        <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.329895589771418</v>
+        <v>-4.153330811750274</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.116484830895323</v>
+        <v>1.00500024623483</v>
       </c>
       <c r="F1957" t="n">
         <v>0.5548091967368656</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.181685009159757</v>
+        <v>2.999574513290806</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982225</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.829606946449228</v>
+        <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.374909803292024</v>
+        <v>-4.19834502527088</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.079286600818671</v>
+        <v>0.9678020161581771</v>
       </c>
       <c r="F1958" t="n">
         <v>0.524460301422261</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.144283127302584</v>
+        <v>2.962172631433633</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.835298508788173</v>
+        <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.641914313564459</v>
+        <v>-4.465349535543315</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9781763590486425</v>
+        <v>0.8666917743881488</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3300972633793124</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.033356866815761</v>
+        <v>2.85124637094681</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.834502430684675</v>
+        <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.743112095001631</v>
+        <v>-4.566547316980488</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9369011683702748</v>
+        <v>0.8254165837097811</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2616884498339932</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.991515500585071</v>
+        <v>2.80940500471612</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.832102392238991</v>
+        <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.736601128387319</v>
+        <v>-4.560036350366175</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9371055165703166</v>
+        <v>0.8256209319098229</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2616884498339932</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.989115462139388</v>
+        <v>2.807004966270437</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.828627111447236</v>
+        <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.717563000680022</v>
+        <v>-4.540998222658878</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9412454868614804</v>
+        <v>0.8297609022009869</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2035048385027987</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.950730014548916</v>
+        <v>2.768619518679965</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.947921513081427</v>
+        <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.770078802954842</v>
+        <v>-4.593514024933699</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.039533567585743</v>
+        <v>0.928048982925249</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2035048385027987</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.070024416183106</v>
+        <v>2.887913920314155</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067861</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.94875484206756</v>
+        <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.78394556428876</v>
+        <v>-4.607380786267616</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.034820192038309</v>
+        <v>0.9233356073778154</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1656469217689757</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.048142995128946</v>
+        <v>2.866032499259995</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789118</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.954763372464486</v>
+        <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.73914139274883</v>
+        <v>-4.562576614727686</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.058750391051207</v>
+        <v>0.9472658063907133</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1656469217689757</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.054151525525872</v>
+        <v>2.872041029656921</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.852713593741686</v>
+        <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.591398422513827</v>
+        <v>-4.414833644492684</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.015797800422408</v>
+        <v>0.9043132157619138</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3334542790038589</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.052786161144001</v>
+        <v>2.87067566527505</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.780270426446463</v>
+        <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.675219643788526</v>
+        <v>-4.498654865767382</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9098261446173053</v>
+        <v>0.8735783487835154</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3334542790038589</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.980342993848778</v>
+        <v>2.873469286806531</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.780932774838121</v>
+        <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.669066937735741</v>
+        <v>-4.492502159714598</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9129495754300774</v>
+        <v>0.8767017795962875</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3396069850566432</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.984696965872107</v>
+        <v>2.87782325882986</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.780013251578231</v>
+        <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.685876235886243</v>
+        <v>-4.5093114578651</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9053063329099869</v>
+        <v>0.869058537076197</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3227976869061415</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.973691863721917</v>
+        <v>2.86681815667967</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798421</v>
+        <v>3.867362636798423</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.846348805375052</v>
+        <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.623578237110121</v>
+        <v>-4.447013459088978</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9965610862172567</v>
+        <v>0.9603132903834668</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3680919511805836</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.067203976083403</v>
+        <v>2.960330269041155</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.648640807089179</v>
+        <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.421788039444963</v>
+        <v>-4.24522326142382</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8795691669974468</v>
+        <v>0.8433213711636571</v>
       </c>
       <c r="F1971" t="n">
         <v>0.566110143349738</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.988306893099022</v>
+        <v>2.881433186056775</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.718931039411355</v>
+        <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.472674752131158</v>
+        <v>-4.296109974110014</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9295047142451442</v>
+        <v>0.8932569184113544</v>
       </c>
       <c r="F1972" t="n">
         <v>0.5152234306635435</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.028065097809481</v>
+        <v>2.921191390767234</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031954</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.733558775527398</v>
+        <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.386064009481351</v>
+        <v>-4.209499231460208</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9787767474211106</v>
+        <v>0.9425289515873208</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5938491618687017</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.089868272648619</v>
+        <v>2.982994565606372</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.73209475635207</v>
+        <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.446273307486636</v>
+        <v>-4.269708529465492</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9532290090436684</v>
+        <v>0.9169812132098785</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5336398638634172</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.05227867467012</v>
+        <v>2.945404967627873</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397789</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.730586374391998</v>
+        <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.369851261054709</v>
+        <v>-4.193286483033566</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9822894456563676</v>
+        <v>0.9460416498225777</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5336398638634172</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.050770292710049</v>
+        <v>2.943896585667802</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316244</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.730449241827435</v>
+        <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.32547812941614</v>
+        <v>-4.148913351394997</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9999015657472312</v>
+        <v>0.9636537699134413</v>
       </c>
       <c r="F1976" t="n">
         <v>0.5780129955019858</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.077257039128626</v>
+        <v>2.970383332086379</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.724843035966025</v>
+        <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.347958480275025</v>
+        <v>-4.171393702253882</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9853032195422677</v>
+        <v>0.9490554237084781</v>
       </c>
       <c r="F1977" t="n">
         <v>0.5780129955019858</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.071650833267217</v>
+        <v>2.96477712622497</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.73122479299383</v>
+        <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.300302749713969</v>
+        <v>-4.123737971692826</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.010747268794495</v>
+        <v>0.974499472960705</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6256687260630415</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.106626028631655</v>
+        <v>2.999752321589408</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569613</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.736117166368555</v>
+        <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.199784591215215</v>
+        <v>-4.023219813194071</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.055846905568721</v>
+        <v>1.019599109734932</v>
       </c>
       <c r="F1979" t="n">
         <v>0.726186884561796</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.171829297105632</v>
+        <v>3.064955590063385</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.722871838844427</v>
+        <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.183879261782862</v>
+        <v>-4.007314483761719</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.048963709817535</v>
+        <v>1.012715913983745</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6470742238525571</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.111116373155961</v>
+        <v>3.004242666113714</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932765</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.726969541455055</v>
+        <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.139040860174464</v>
+        <v>-3.962476082153321</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.070996773071523</v>
+        <v>1.034748977237733</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6516176567974266</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.117940135533511</v>
+        <v>3.011066428491264</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917047</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.731130481086133</v>
+        <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.158539316416472</v>
+        <v>-3.981974538395329</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.067358330205797</v>
+        <v>1.031110534372008</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6035330155175223</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.093250290396647</v>
+        <v>2.9863765833544</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405955</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.737010083613971</v>
+        <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.114336479330571</v>
+        <v>-3.937771701309428</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.090919067567995</v>
+        <v>1.054671271734205</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6477358526034227</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.125651595176024</v>
+        <v>3.018777888133777</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265638</v>
+        <v>3.83819962926564</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.735420084083218</v>
+        <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.121896145167618</v>
+        <v>-3.945331367146475</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.086305201702424</v>
+        <v>1.050057405868634</v>
       </c>
       <c r="F1984" t="n">
         <v>0.702539256613242</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.156943638051164</v>
+        <v>3.050069931008916</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284873</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.786667849266258</v>
+        <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.963604727628346</v>
+        <v>-3.787039949607203</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.200869533901172</v>
+        <v>1.164621738067382</v>
       </c>
       <c r="F1985" t="n">
         <v>0.702539256613242</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.208191403234203</v>
+        <v>3.101317696191956</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321017</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.785108553860511</v>
+        <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.75596272399387</v>
+        <v>-3.579397945972727</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.282367039949216</v>
+        <v>1.246119244115426</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9101812602477182</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.331217310009142</v>
+        <v>3.224343602966895</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475134</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.780056782098781</v>
+        <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.704930631271341</v>
+        <v>-3.528365853250199</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.297728105276497</v>
+        <v>1.261480309442707</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9612133529702461</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.356784793880929</v>
+        <v>3.249911086838682</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.797244186191486</v>
+        <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.639706450144136</v>
+        <v>-3.463141672122993</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.341005181820084</v>
+        <v>1.304757385986294</v>
       </c>
       <c r="F1988" t="n">
         <v>1.026437534097452</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.413106706649957</v>
+        <v>3.30623299960771</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.793205158490766</v>
+        <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.602279430073002</v>
+        <v>-3.425714652051859</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.351936962147818</v>
+        <v>1.315689166314028</v>
       </c>
       <c r="F1989" t="n">
         <v>1.031689072126633</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.412218601766746</v>
+        <v>3.305344894724499</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.794461950822007</v>
+        <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.62239108610771</v>
+        <v>-3.445826308086568</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.345149092065175</v>
+        <v>1.308901296231385</v>
       </c>
       <c r="F1990" t="n">
         <v>1.042716417124052</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.420091801096438</v>
+        <v>3.313218094054191</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.955019721843217</v>
+        <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.593977823007827</v>
+        <v>-3.417413044986684</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.517072168326339</v>
+        <v>1.480824372492549</v>
       </c>
       <c r="F1991" t="n">
         <v>0.9837408543776236</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.545264234469792</v>
+        <v>3.438390527427544</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.075132631061035</v>
+        <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.519195561982814</v>
+        <v>-3.342630783961671</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.667097981954162</v>
+        <v>1.630850186120371</v>
       </c>
       <c r="F1992" t="n">
         <v>1.058523115402636</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.710246500302616</v>
+        <v>3.603372793260369</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.066840607074893</v>
+        <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.493111477719006</v>
+        <v>-3.316546699697863</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.669239591673544</v>
+        <v>1.632991795839754</v>
       </c>
       <c r="F1993" t="n">
         <v>1.058523115402636</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.701954476316475</v>
+        <v>3.595080769274228</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.065033802658673</v>
+        <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.405233564609885</v>
+        <v>-3.228668786588743</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.702583952500972</v>
+        <v>1.666336156667181</v>
       </c>
       <c r="F1994" t="n">
         <v>1.174448757825987</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.769703057354266</v>
+        <v>3.662829350312018</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.082588208385464</v>
+        <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.396341103216602</v>
+        <v>-3.219776325195459</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.723695342785076</v>
+        <v>1.687447546951286</v>
       </c>
       <c r="F1995" t="n">
         <v>1.174448757825987</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.787257463081057</v>
+        <v>3.68038375603881</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945361</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.074443255790048</v>
+        <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.56481722018648</v>
+        <v>-3.388252442165337</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.648159943401709</v>
+        <v>1.611912147567919</v>
       </c>
       <c r="F1996" t="n">
         <v>1.146500922109406</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.762343809055692</v>
+        <v>3.655470102013445</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.05571295297791</v>
+        <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-3.11856102755704</v>
+        <v>-2.941996249535897</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.807932117641347</v>
+        <v>1.771684321807557</v>
       </c>
       <c r="F1997" t="n">
         <v>1.051782252439774</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.686782304441774</v>
+        <v>3.579908597399527</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.046376975474815</v>
+        <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-3.095839923873887</v>
+        <v>-2.919275145852745</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.807684581611512</v>
+        <v>1.771436785777722</v>
       </c>
       <c r="F1998" t="n">
         <v>1.051782252439774</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.677446326938679</v>
+        <v>3.570572619896432</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.205283101325984</v>
+        <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-3.22504173716793</v>
+        <v>-3.048476959146787</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.914909982145065</v>
+        <v>1.878662186311274</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9225804391457315</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.758831364813423</v>
+        <v>3.651957657771176</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.24236092381963</v>
+        <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-3.250916135641956</v>
+        <v>-3.074351357620813</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.941638045249101</v>
+        <v>1.905390249415311</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9674920478574727</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.822856152534114</v>
+        <v>3.715982445491867</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.239036279809175</v>
+        <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-3.243861445426782</v>
+        <v>-3.067296667405639</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.941135277324715</v>
+        <v>1.904887481490925</v>
       </c>
       <c r="F2001" t="n">
         <v>0.9745467380726465</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.823764322652764</v>
+        <v>3.716890615610517</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.249042433453917</v>
+        <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-3.216910221100294</v>
+        <v>-3.040345443079151</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.961921920700052</v>
+        <v>1.925674124866262</v>
       </c>
       <c r="F2002" t="n">
         <v>0.9894270841003656</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.842698683914136</v>
+        <v>3.735824976871889</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.433145565598877</v>
+        <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.35286322915661</v>
+        <v>-3.176298451135468</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.091643849622486</v>
+        <v>2.055396053788695</v>
       </c>
       <c r="F2003" t="n">
         <v>0.9894270841003656</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.026801816059097</v>
+        <v>3.919928109016849</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.42526226050187</v>
+        <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.375271346961482</v>
+        <v>-3.19870656894034</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.07479729740353</v>
+        <v>2.038549501569739</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9894270841003656</v>
+        <v>0.9887097968114151</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.01891851096209</v>
+        <v>3.911614431546472</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.427316260051507</v>
+        <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.403495582539083</v>
+        <v>-3.22693080451794</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.065561602722127</v>
+        <v>2.029313806888337</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.007403836551674</v>
+        <v>1.006686549262724</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.031758561982512</v>
+        <v>3.924454482566895</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.483569977773354</v>
+        <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.412936508427613</v>
+        <v>-3.23637173040647</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.118038950088562</v>
+        <v>2.081791154254772</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.129830954095066</v>
+        <v>1.129113666806115</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.161468550230394</v>
+        <v>4.054164470814777</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.486461072318655</v>
+        <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.465210115763254</v>
+        <v>-3.288645337742111</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.100020601699606</v>
+        <v>2.063772805865816</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.077557346759424</v>
+        <v>1.076840059470474</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.13299548037431</v>
+        <v>4.025691400958692</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.48457288521243</v>
+        <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.54154009336416</v>
+        <v>-3.364975315343017</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.067600423553019</v>
+        <v>2.031352627719229</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.077557346759424</v>
+        <v>1.076840059470474</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.131107293268085</v>
+        <v>4.023803213852467</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.479393114815293</v>
+        <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.743793813688513</v>
+        <v>-3.567229035667371</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.98151916502614</v>
+        <v>1.94527136919235</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8753036264350709</v>
+        <v>0.8745863391461202</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.004575290676335</v>
+        <v>3.897271211260718</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.477827125025445</v>
+        <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.905362239215768</v>
+        <v>-3.728797461194626</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.915325805025391</v>
+        <v>1.8790780091916</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7485207026371915</v>
+        <v>0.7478034153482408</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.92693954660776</v>
+        <v>3.819635467192143</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.490900531891364</v>
+        <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-4.013662901085888</v>
+        <v>-3.837098123064745</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.885078947143261</v>
+        <v>1.848831151309471</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7485207026371915</v>
+        <v>0.7478034153482408</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.940012953473679</v>
+        <v>3.832708874058061</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.482905728674304</v>
+        <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-4.106810372389255</v>
+        <v>-3.930245594368112</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.839825155404855</v>
+        <v>1.803577359571064</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6256914913546587</v>
+        <v>0.624974204065708</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.858320623487099</v>
+        <v>3.751016544071482</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.481429769801306</v>
+        <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-4.134711159498727</v>
+        <v>-3.958146381477585</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.827188881688067</v>
+        <v>1.790941085854277</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5910945672117239</v>
+        <v>0.5903772799227732</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.83608651012834</v>
+        <v>3.728782430712723</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.478194213778504</v>
+        <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-4.257237262201621</v>
+        <v>-4.080672484180479</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.774942884584109</v>
+        <v>1.738695088750319</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4685684645088301</v>
+        <v>0.4678511772198793</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.759335292483803</v>
+        <v>3.652031213068185</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.544900173369008</v>
+        <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.48775175838721</v>
+        <v>-4.311186980366068</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.749443045700377</v>
+        <v>1.713195249866587</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2380539683232413</v>
+        <v>0.2373366810342906</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.687732554362953</v>
+        <v>3.580428474947336</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.685211892370855</v>
+        <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.836496843611654</v>
+        <v>-4.659932065590511</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.750256730612446</v>
+        <v>1.714008934778656</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1293060144043435</v>
+        <v>0.1285887271153928</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.762795501013461</v>
+        <v>3.655491421597844</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237091</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.754192161516495</v>
+        <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.990483261387794</v>
+        <v>-4.813918483366652</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.75764243264763</v>
+        <v>1.72139463681384</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1293060144043435</v>
+        <v>0.1285887271153928</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.831775770159101</v>
+        <v>3.724471690743484</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.740243363636616</v>
+        <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.939961357560128</v>
+        <v>-4.763396579538986</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.763902396298817</v>
+        <v>1.727654600465027</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1293060144043435</v>
+        <v>0.1285887271153928</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.817826972279222</v>
+        <v>3.710522892863604</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609751</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.75211385269203</v>
+        <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-5.192436511567853</v>
+        <v>-5.01587173354671</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.674782823751142</v>
+        <v>1.638535027917351</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1293060144043435</v>
+        <v>0.1285887271153928</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.829697461334636</v>
+        <v>3.722393381919018</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.753324387210974</v>
+        <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.485332268047265</v>
+        <v>-5.308767490026122</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.55883505567832</v>
+        <v>1.52258725984453</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1293060144043435</v>
+        <v>0.1285887271153928</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.83090799585358</v>
+        <v>3.723603916437962</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.757446129438295</v>
+        <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.671996396182073</v>
+        <v>-5.49543161816093</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.488291146651719</v>
+        <v>1.452043350817928</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1025670435797836</v>
+        <v>0.1018497562908329</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.818986355586166</v>
+        <v>3.711682276170548</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916199</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.752523982174484</v>
+        <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.818017083096035</v>
+        <v>-5.641452305074893</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.424960724622323</v>
+        <v>1.388712928788533</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.09348395178592667</v>
+        <v>0.09276666449697596</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.808614353246041</v>
+        <v>3.701310273830423</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.914728038873529</v>
+        <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.90973109220562</v>
+        <v>-5.733166314184478</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.550479177677533</v>
+        <v>1.514231381843743</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.09348395178592667</v>
+        <v>0.09276666449697596</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.970818409945085</v>
+        <v>3.863514330529467</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.909574676837343</v>
+        <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.941382751265589</v>
+        <v>-5.764817973244448</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.53266515201736</v>
+        <v>1.496417356183569</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.08831549454148646</v>
+        <v>0.08759820725253575</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.962563973562235</v>
+        <v>3.855259894146617</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.919804094405834</v>
+        <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-6.023317569534473</v>
+        <v>-5.846752791513331</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.510120642278298</v>
+        <v>1.473872846444507</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.07838074895440628</v>
+        <v>0.07766346166545557</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.966832543778478</v>
+        <v>3.85952846436286</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.928729732861736</v>
+        <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-6.12529369178288</v>
+        <v>-5.948728913761738</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.478255831834837</v>
+        <v>1.442008036001047</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.0235953732940013</v>
+        <v>-0.02431266058295201</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.914572508885335</v>
+        <v>3.807268429469718</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.920882620105912</v>
+        <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-6.015287408305658</v>
+        <v>-5.838722630284517</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.514411232469902</v>
+        <v>1.478163436636111</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.0003908013767260909</v>
+        <v>-0.001108088665676799</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.920648139279876</v>
+        <v>3.813344059864259</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.925132630827886</v>
+        <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.872227832564732</v>
+        <v>-5.695663054543591</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.575885073488246</v>
+        <v>1.539637277654455</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.007622625213253187</v>
+        <v>0.006905337924302479</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.929706205955839</v>
+        <v>3.82240212654022</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.932393513710423</v>
+        <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.570781107092895</v>
+        <v>-5.394216329071753</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.703724646559518</v>
+        <v>1.667476850725726</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3090693506850904</v>
+        <v>0.3083520633961397</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.117835124121477</v>
+        <v>4.010531044705859</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.933364691463133</v>
+        <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.595371351328079</v>
+        <v>-5.418806573306937</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.694859726618154</v>
+        <v>1.658611930784363</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3090693506850904</v>
+        <v>0.3083520633961397</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.118806301874187</v>
+        <v>4.01150222245857</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.934207595842889</v>
+        <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.544332975321558</v>
+        <v>-5.367768197300417</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.716117981400518</v>
+        <v>1.679870185566727</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3090693506850904</v>
+        <v>0.3083520633961397</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.119649206253943</v>
+        <v>4.012345126838325</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.953245694717034</v>
+        <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.503193680454928</v>
+        <v>-5.326628902433786</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.751611798221316</v>
+        <v>1.715364002387525</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3502086455517213</v>
+        <v>0.3494913582627706</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.163370882048067</v>
+        <v>4.056066802632449</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.769429690840969</v>
+        <v>3.67845488013556</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.406558768436287</v>
+        <v>-5.229993990415146</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.606449759152706</v>
+        <v>1.586100859655754</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4468435575703612</v>
+        <v>0.4461262702814105</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.037535825383186</v>
+        <v>3.946130642304406</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.772931734914932</v>
+        <v>3.681956924209524</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.53713950296713</v>
+        <v>-5.360574724945988</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.557719509414333</v>
+        <v>1.537370609917381</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3162628230395187</v>
+        <v>0.315545535750568</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.962689428738644</v>
+        <v>3.871284245659865</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833454</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.757358553991015</v>
+        <v>3.666383743285606</v>
       </c>
       <c r="D2035" t="n">
-        <v>-5.372643168776168</v>
+        <v>-5.196078390755027</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.6079448621668</v>
+        <v>1.587595962669848</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4807591572304806</v>
+        <v>0.4800418699415299</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.045814048329303</v>
+        <v>3.954408865250524</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.756546264427445</v>
+        <v>3.665571453722036</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.4000131014606</v>
+        <v>-5.223448323439459</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.596184599529457</v>
+        <v>1.575835700032505</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4807591572304806</v>
+        <v>0.4800418699415299</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.045001758765733</v>
+        <v>3.953596575686954</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147906</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.766415043552517</v>
+        <v>3.675440232847108</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.41039829635049</v>
+        <v>-5.233833518329348</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.601899300698574</v>
+        <v>1.581550401201622</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4703739623405913</v>
+        <v>0.4696566750516405</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.048639420956872</v>
+        <v>3.957234237878093</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.837252049328942</v>
+        <v>3.746277238623533</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.428986455072715</v>
+        <v>-5.145515315729279</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.665301042986109</v>
+        <v>1.687714688018075</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.4517858036183659</v>
+        <v>0.5579748776517103</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.108323531499962</v>
+        <v>4.08106216521456</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.834121060147241</v>
+        <v>3.743146249441832</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.429285001768751</v>
+        <v>-5.145813862425315</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.662050635125993</v>
+        <v>1.684464280157959</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.45148725692233</v>
+        <v>0.5576763309556744</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.105013414300639</v>
+        <v>4.077752048015236</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.838651955086632</v>
+        <v>3.747677144381223</v>
       </c>
       <c r="D2040" t="n">
-        <v>-5.328461868078323</v>
+        <v>-5.044990728734887</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.706910783541556</v>
+        <v>1.729324428573521</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.4639514724066838</v>
+        <v>0.5701405464400282</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.117022838530643</v>
+        <v>4.08976147224524</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.838781208565175</v>
+        <v>3.747806397859767</v>
       </c>
       <c r="D2041" t="n">
-        <v>-5.137680507325916</v>
+        <v>-4.854209367982479</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.783352581321062</v>
+        <v>1.805766226353028</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.6547328331590911</v>
+        <v>0.7609219071924356</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.231620908460631</v>
+        <v>4.204359542175228</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.818618054302772</v>
+        <v>3.727643243597363</v>
       </c>
       <c r="D2042" t="n">
-        <v>-5.119163653284096</v>
+        <v>-4.835692513940659</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.770596168675386</v>
+        <v>1.793009813707352</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.6676629625842994</v>
+        <v>0.7738520366176438</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.219215831853352</v>
+        <v>4.191954465567949</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.85358499091483</v>
+        <v>3.762610180209422</v>
       </c>
       <c r="D2043" t="n">
-        <v>-5.063833065382333</v>
+        <v>-4.780361926038896</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.82769534044815</v>
+        <v>1.850108985480116</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7229935504860615</v>
+        <v>0.8291826245194059</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.287381121206468</v>
+        <v>4.260119754921066</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.847271558816268</v>
+        <v>3.756296748110859</v>
       </c>
       <c r="D2044" t="n">
-        <v>-5.05177893846937</v>
+        <v>-4.768307799125933</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.826203559114773</v>
+        <v>1.848617204146739</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7350476773990243</v>
+        <v>0.8412367514323688</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.288300165255682</v>
+        <v>4.261038798970281</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.849152189000404</v>
+        <v>3.758177378294995</v>
       </c>
       <c r="D2045" t="n">
-        <v>-5.092934058037591</v>
+        <v>-4.809462918694154</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.81162214147162</v>
+        <v>1.834035786503586</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.6938925578308034</v>
+        <v>0.8000816318641478</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.265487723698886</v>
+        <v>4.238226357413484</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.862003214878286</v>
+        <v>3.771028404172878</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.990053468508998</v>
+        <v>-4.706582329165562</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.86562540316094</v>
+        <v>1.888039048192906</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.7967731473593963</v>
+        <v>0.9029622213927407</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.340067103293924</v>
+        <v>4.312805737008523</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.646857607760311</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.882205885051881</v>
+        <v>3.791231074346472</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.221653861678499</v>
+        <v>-4.938182722335062</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.793187916066734</v>
+        <v>1.8156015610987</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.7967731473593963</v>
+        <v>0.9029622213927407</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.360269773467518</v>
+        <v>4.333008407182117</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666767386781702</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.882205885051881</v>
+        <v>3.791231074346472</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.239726369970111</v>
+        <v>-4.956255230626674</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.785958912750089</v>
+        <v>1.808372557782055</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.7967731473593963</v>
+        <v>0.9029622213927407</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.360269773467518</v>
+        <v>4.333008407182117</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670068888082831</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.842457798645347</v>
+        <v>3.751482987939939</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.414833202546555</v>
+        <v>-5.131362063203118</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.676168093312978</v>
+        <v>1.698581738344944</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.7967731473593963</v>
+        <v>0.9029622213927407</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.320521687060985</v>
+        <v>4.293260320775583</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.849480417642287</v>
+        <v>3.758505606936879</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.3835471820061</v>
+        <v>-5.100076042662663</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.6957051205261</v>
+        <v>1.718118765558066</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8280591678998517</v>
+        <v>0.9342482419331961</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.346315918382198</v>
+        <v>4.319054552096796</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.73059065867782</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.948651417215191</v>
+        <v>3.857676606509783</v>
       </c>
       <c r="D2051" t="n">
-        <v>-5.230521789892816</v>
+        <v>-4.947050650549379</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.856086276944318</v>
+        <v>1.878499921976284</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9810845600131358</v>
+        <v>1.08727363404648</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.537302153223073</v>
+        <v>4.510040786937672</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741298518073879</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.136117642123484</v>
+        <v>4.045142831418075</v>
       </c>
       <c r="D2052" t="n">
-        <v>-5.258829103766086</v>
+        <v>-4.975357964422649</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.032229576303302</v>
+        <v>2.054643221335268</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9810845600131358</v>
+        <v>1.08727363404648</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.724768378131365</v>
+        <v>4.697507011845963</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699135800903164</v>
       </c>
       <c r="C2053" t="n">
-        <v>4.105520593477566</v>
+        <v>4.014545782772157</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.425422328879608</v>
+        <v>-5.141951189536171</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.934995237611976</v>
+        <v>1.957408882643942</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8144913348996135</v>
+        <v>0.9206804089329579</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.594215394417335</v>
+        <v>4.566954028131932</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708202704568379</v>
       </c>
       <c r="C2054" t="n">
-        <v>4.109196996139284</v>
+        <v>4.018222185433875</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.252357949497308</v>
+        <v>-4.968886810153871</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.007897392026613</v>
+        <v>2.03031103705858</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8144913348996135</v>
+        <v>0.9206804089329579</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.597891797079052</v>
+        <v>4.57063043079365</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.7406015866822</v>
       </c>
       <c r="C2055" t="n">
-        <v>4.106815051262779</v>
+        <v>4.01584024055737</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.223111969041612</v>
+        <v>-4.939640829698175</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.017213839332387</v>
+        <v>2.039627484364353</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8144913348996135</v>
+        <v>0.9206804089329579</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.595509852202547</v>
+        <v>4.568248485917145</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.699424827539104</v>
       </c>
       <c r="C2056" t="n">
-        <v>4.104108290420414</v>
+        <v>4.013133479715005</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.336730645183295</v>
+        <v>-5.046566377576026</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.969059608033349</v>
+        <v>1.994150504370848</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7008726587579296</v>
+        <v>0.8137548610551065</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.524631885675172</v>
+        <v>4.501386396348069</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689962785983734</v>
       </c>
       <c r="C2057" t="n">
-        <v>4.105537092563648</v>
+        <v>4.01456228185824</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.481749203690544</v>
+        <v>-5.191584936083275</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.912480986773683</v>
+        <v>1.937571883111183</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.555854100250681</v>
+        <v>0.668736302547858</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.439049552714057</v>
+        <v>4.415804063386955</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.711872614969745</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.205468331821401</v>
+        <v>4.114493521115993</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.600090969475262</v>
+        <v>-5.309926701867992</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.965075519717549</v>
+        <v>1.990166416055049</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5665401388135711</v>
+        <v>0.6794223411107481</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.545392415109545</v>
+        <v>4.522146925782442</v>
       </c>
     </row>
     <row r="2059">
@@ -48905,19 +48905,19 @@
         <v>3.714899237073535</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.20325402894734</v>
+        <v>4.112279218241931</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.65150139179597</v>
+        <v>-5.3613371241887</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.942297047915205</v>
+        <v>1.967387944252704</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5665401388135711</v>
+        <v>0.6794223411107481</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.543178112235482</v>
+        <v>4.519932622908381</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.704778134720062</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.20315715702163</v>
+        <v>4.112182346316221</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.730920843003721</v>
+        <v>-5.440756575396452</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.910432395506394</v>
+        <v>1.935523291843893</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5665401388135711</v>
+        <v>0.6794223411107481</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.543081240309773</v>
+        <v>4.51983575098267</v>
       </c>
     </row>
     <row r="2061">
@@ -48951,19 +48951,19 @@
         <v>3.736825137581129</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.203151050579673</v>
+        <v>4.112176239874264</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.826383840920939</v>
+        <v>-5.536219573313669</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.87224108989755</v>
+        <v>1.897331986235049</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5665401388135711</v>
+        <v>0.6794223411107481</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.543075133867816</v>
+        <v>4.519829644540714</v>
       </c>
     </row>
     <row r="2062">
@@ -48974,19 +48974,19 @@
         <v>3.715393145500731</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.201247447142284</v>
+        <v>4.110272636436875</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.866403838964723</v>
+        <v>-5.576239571357453</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.854329487242647</v>
+        <v>1.879420383580146</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.5265201407697873</v>
+        <v>0.6394023430669642</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.517159531604157</v>
+        <v>4.493914042277054</v>
       </c>
     </row>
     <row r="2063">
@@ -48997,19 +48997,19 @@
         <v>3.736109598636267</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.20698126489001</v>
+        <v>4.116006454184602</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.921773001096916</v>
+        <v>-5.631608733489647</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.837915640137497</v>
+        <v>1.863006536474995</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.5265201407697873</v>
+        <v>0.6394023430669642</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.522893349351883</v>
+        <v>4.499647860024781</v>
       </c>
     </row>
     <row r="2064">
@@ -49020,19 +49020,19 @@
         <v>3.73684305539601</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.206519628232943</v>
+        <v>4.115544817527534</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.967210780927743</v>
+        <v>-5.677046513320474</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.819278891548099</v>
+        <v>1.844369787885597</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.4836751500916276</v>
+        <v>0.5965573523888046</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.49672471828792</v>
+        <v>4.473479228960817</v>
       </c>
     </row>
     <row r="2065">
@@ -49043,19 +49043,19 @@
         <v>3.790292685396419</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.226394021083262</v>
+        <v>4.135419210377853</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.883985324080079</v>
+        <v>-5.59382105647281</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.872443467137483</v>
+        <v>1.897534363474982</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.4836751500916276</v>
+        <v>0.5965573523888046</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.516599111138239</v>
+        <v>4.493353621811136</v>
       </c>
     </row>
     <row r="2066">
@@ -49066,19 +49066,19 @@
         <v>3.794507029299173</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.21009472160799</v>
+        <v>4.11911991090258</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.707695099474772</v>
+        <v>-5.417530831867502</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.926660257504334</v>
+        <v>1.951751153841832</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.4836751500916276</v>
+        <v>0.5965573523888046</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.500299811662967</v>
+        <v>4.477054322335864</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.794725278590404</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.212525671072036</v>
+        <v>4.121550860366626</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.524483436341677</v>
+        <v>-5.234319168734407</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.002375872221618</v>
+        <v>2.027466768559116</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.4836751500916276</v>
+        <v>0.5965573523888046</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.502730761127013</v>
+        <v>4.479485271799909</v>
       </c>
     </row>
     <row r="2068">
@@ -49112,19 +49112,19 @@
         <v>3.776866743146282</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.178316856919925</v>
+        <v>4.087342046214515</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.452761989327826</v>
+        <v>-5.162597721720556</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.996855636875047</v>
+        <v>2.021946533212545</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.5553965971054782</v>
+        <v>0.6682787994026552</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.511554815183212</v>
+        <v>4.488309325856108</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676848</v>
+        <v>3.723809890676846</v>
       </c>
       <c r="C2069" t="n">
-        <v>4.125232602841097</v>
+        <v>4.034257792135687</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.239733289919013</v>
+        <v>-5.291976504360334</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.028982862559744</v>
+        <v>1.917110766077806</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6002931599395317</v>
+        <v>0.6261770266954518</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.485408498804816</v>
+        <v>4.409964008152959</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.783112736724433</v>
+        <v>3.514243607419752</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.122547043719776</v>
+        <v>4.031572233014367</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.252821506611325</v>
+        <v>-5.157916874885356</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.021062016761499</v>
+        <v>1.968049058746477</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5872049432472196</v>
+        <v>0.6611993251782827</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.474870009668108</v>
+        <v>4.428291828121337</v>
       </c>
     </row>
   </sheetData>
